--- a/Month YEAR - Body Motions.xlsx
+++ b/Month YEAR - Body Motions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyayas/VALD Automator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D341DE7-1F84-1B4C-9446-D521A65A3CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414C0AF1-7EE3-BD45-AC8A-E8B524C6DAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,8 +34,8 @@
     <sheet name="Tabuk" sheetId="20" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">REPORT!$B$1:$B$322</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">REPORT!$A$1:$D$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">REPORT!$B$1:$B$323</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">REPORT!$A$1:$D$177</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'REPORT 2'!$A$1:$G$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'REPORT 2'!$1:$6</definedName>
   </definedNames>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="171">
   <si>
     <t>REPORT DATE:</t>
   </si>
@@ -598,6 +598,9 @@
   <si>
     <t xml:space="preserve">رقم العميل
 </t>
+  </si>
+  <si>
+    <t>Safaa Karim</t>
   </si>
 </sst>
 </file>
@@ -18196,7 +18199,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O322"/>
+  <dimension ref="A1:O323"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="50.83203125" defaultRowHeight="50" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.83203125" style="1" customWidth="1"/>
@@ -18597,7 +18600,7 @@
     <row r="20" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="65"/>
       <c r="B20" s="43" t="s">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="C20" s="24">
         <f ca="1">IFERROR(
@@ -18620,7 +18623,7 @@
     <row r="21" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="65"/>
       <c r="B21" s="43" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="C21" s="24">
         <f ca="1">IFERROR(
@@ -18643,7 +18646,7 @@
     <row r="22" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="65"/>
       <c r="B22" s="43" t="s">
-        <v>31</v>
+        <v>155</v>
       </c>
       <c r="C22" s="24">
         <f ca="1">IFERROR(
@@ -18666,7 +18669,7 @@
     <row r="23" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="65"/>
       <c r="B23" s="43" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C23" s="24">
         <f ca="1">IFERROR(
@@ -18686,19 +18689,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="63"/>
-      <c r="B24" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="26">
+    <row r="24" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="65"/>
+      <c r="B24" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="24">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A24) &amp; "'!C:C"), B24),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D24" s="87" cm="1">
+      <c r="D24" s="73" cm="1">
         <f t="array" aca="1" ref="D24" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A24&lt;&gt;""),$A$7:A24) &amp; "'!C:C"), $B24,
@@ -18710,20 +18713,18 @@
       </c>
     </row>
     <row r="25" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="24">
+      <c r="A25" s="63"/>
+      <c r="B25" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="26">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A25) &amp; "'!C:C"), B25),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D25" s="88" cm="1">
+      <c r="D25" s="87" cm="1">
         <f t="array" aca="1" ref="D25" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A25&lt;&gt;""),$A$7:A25) &amp; "'!C:C"), $B25,
@@ -18735,9 +18736,11 @@
       </c>
     </row>
     <row r="26" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
+      <c r="A26" s="57" t="s">
+        <v>56</v>
+      </c>
       <c r="B26" s="29" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C26" s="24">
         <f ca="1">IFERROR(
@@ -18746,7 +18749,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D26" s="73" cm="1">
+      <c r="D26" s="88" cm="1">
         <f t="array" aca="1" ref="D26" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A26&lt;&gt;""),$A$7:A26) &amp; "'!C:C"), $B26,
@@ -18760,7 +18763,7 @@
     <row r="27" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="28"/>
       <c r="B27" s="29" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C27" s="24">
         <f ca="1">IFERROR(
@@ -18783,7 +18786,7 @@
     <row r="28" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="28"/>
       <c r="B28" s="29" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C28" s="24">
         <f ca="1">IFERROR(
@@ -18806,7 +18809,7 @@
     <row r="29" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="28"/>
       <c r="B29" s="29" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="C29" s="24">
         <f ca="1">IFERROR(
@@ -18827,9 +18830,9 @@
       </c>
     </row>
     <row r="30" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="38"/>
-      <c r="B30" s="43" t="s">
-        <v>158</v>
+      <c r="A30" s="28"/>
+      <c r="B30" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="C30" s="24">
         <f ca="1">IFERROR(
@@ -18852,7 +18855,7 @@
     <row r="31" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="38"/>
       <c r="B31" s="43" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="C31" s="24">
         <f ca="1">IFERROR(
@@ -18875,16 +18878,16 @@
     <row r="32" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="38"/>
       <c r="B32" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="26">
+        <v>84</v>
+      </c>
+      <c r="C32" s="24">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A32) &amp; "'!C:C"), B32),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D32" s="87" cm="1">
+      <c r="D32" s="73" cm="1">
         <f t="array" aca="1" ref="D32" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A32&lt;&gt;""),$A$7:A32) &amp; "'!C:C"), $B32,
@@ -18896,20 +18899,18 @@
       </c>
     </row>
     <row r="33" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="69" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="47">
+      <c r="A33" s="38"/>
+      <c r="B33" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="26">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A33) &amp; "'!C:C"), B33),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D33" s="88" cm="1">
+      <c r="D33" s="87" cm="1">
         <f t="array" aca="1" ref="D33" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A33&lt;&gt;""),$A$7:A33) &amp; "'!C:C"), $B33,
@@ -18921,18 +18922,20 @@
       </c>
     </row>
     <row r="34" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="70"/>
-      <c r="B34" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="28">
+      <c r="A34" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A34) &amp; "'!C:C"), B34),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D34" s="73" cm="1">
+      <c r="D34" s="88" cm="1">
         <f t="array" aca="1" ref="D34" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A34&lt;&gt;""),$A$7:A34) &amp; "'!C:C"), $B34,
@@ -18946,7 +18949,7 @@
     <row r="35" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="70"/>
       <c r="B35" s="25" t="s">
-        <v>165</v>
+        <v>76</v>
       </c>
       <c r="C35" s="28">
         <f ca="1">IFERROR(
@@ -18969,7 +18972,7 @@
     <row r="36" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="70"/>
       <c r="B36" s="25" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="C36" s="28">
         <f ca="1">IFERROR(
@@ -18990,9 +18993,9 @@
       </c>
     </row>
     <row r="37" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="29" t="s">
-        <v>35</v>
+      <c r="A37" s="70"/>
+      <c r="B37" s="25" t="s">
+        <v>16</v>
       </c>
       <c r="C37" s="28">
         <f ca="1">IFERROR(
@@ -19015,7 +19018,7 @@
     <row r="38" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="28"/>
       <c r="B38" s="29" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="C38" s="28">
         <f ca="1">IFERROR(
@@ -19038,7 +19041,7 @@
     <row r="39" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="28"/>
       <c r="B39" s="29" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C39" s="28">
         <f ca="1">IFERROR(
@@ -19059,18 +19062,18 @@
       </c>
     </row>
     <row r="40" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="80"/>
-      <c r="B40" s="75" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="26">
+      <c r="A40" s="28"/>
+      <c r="B40" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A40) &amp; "'!C:C"), B40),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D40" s="87" cm="1">
+      <c r="D40" s="73" cm="1">
         <f t="array" aca="1" ref="D40" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A40&lt;&gt;""),$A$7:A40) &amp; "'!C:C"), $B40,
@@ -19082,20 +19085,18 @@
       </c>
     </row>
     <row r="41" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="84" t="s">
-        <v>93</v>
-      </c>
-      <c r="B41" s="83" t="s">
-        <v>138</v>
-      </c>
-      <c r="C41" s="82">
+      <c r="A41" s="80"/>
+      <c r="B41" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="26">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A41) &amp; "'!C:C"), B41),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D41" s="88" cm="1">
+      <c r="D41" s="87" cm="1">
         <f t="array" aca="1" ref="D41" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A41&lt;&gt;""),$A$7:A41) &amp; "'!C:C"), $B41,
@@ -19107,18 +19108,20 @@
       </c>
     </row>
     <row r="42" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="31"/>
-      <c r="B42" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="C42" s="28">
+      <c r="A42" s="84" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="83" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" s="82">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A42) &amp; "'!C:C"), B42),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D42" s="73" cm="1">
+      <c r="D42" s="88" cm="1">
         <f t="array" aca="1" ref="D42" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A42&lt;&gt;""),$A$7:A42) &amp; "'!C:C"), $B42,
@@ -19130,9 +19133,9 @@
       </c>
     </row>
     <row r="43" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="73"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C43" s="28">
         <f ca="1">IFERROR(
@@ -19152,10 +19155,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
+    <row r="44" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="73"/>
       <c r="B44" s="29" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="C44" s="28">
         <f ca="1">IFERROR(
@@ -19175,10 +19178,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="28"/>
       <c r="B45" s="29" t="s">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="C45" s="28">
         <f ca="1">IFERROR(
@@ -19201,7 +19204,7 @@
     <row r="46" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="28"/>
       <c r="B46" s="29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C46" s="28">
         <f ca="1">IFERROR(
@@ -19222,18 +19225,18 @@
       </c>
     </row>
     <row r="47" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="80"/>
-      <c r="B47" s="75" t="s">
-        <v>133</v>
-      </c>
-      <c r="C47" s="80">
+      <c r="A47" s="28"/>
+      <c r="B47" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A47) &amp; "'!C:C"), B47),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D47" s="87" cm="1">
+      <c r="D47" s="73" cm="1">
         <f t="array" aca="1" ref="D47" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A47&lt;&gt;""),$A$7:A47) &amp; "'!C:C"), $B47,
@@ -19245,20 +19248,18 @@
       </c>
     </row>
     <row r="48" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="57" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="C48" s="28">
+      <c r="A48" s="80"/>
+      <c r="B48" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="C48" s="80">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A48) &amp; "'!C:C"), B48),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D48" s="88" cm="1">
+      <c r="D48" s="87" cm="1">
         <f t="array" aca="1" ref="D48" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A48&lt;&gt;""),$A$7:A48) &amp; "'!C:C"), $B48,
@@ -19270,9 +19271,11 @@
       </c>
     </row>
     <row r="49" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="57"/>
+      <c r="A49" s="57" t="s">
+        <v>92</v>
+      </c>
       <c r="B49" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C49" s="28">
         <f ca="1">IFERROR(
@@ -19281,7 +19284,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D49" s="73" cm="1">
+      <c r="D49" s="88" cm="1">
         <f t="array" aca="1" ref="D49" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A49&lt;&gt;""),$A$7:A49) &amp; "'!C:C"), $B49,
@@ -19295,7 +19298,7 @@
     <row r="50" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="57"/>
       <c r="B50" s="29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C50" s="28">
         <f ca="1">IFERROR(
@@ -19316,9 +19319,9 @@
       </c>
     </row>
     <row r="51" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="31"/>
+      <c r="A51" s="57"/>
       <c r="B51" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C51" s="28">
         <f ca="1">IFERROR(
@@ -19341,7 +19344,7 @@
     <row r="52" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="31"/>
       <c r="B52" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C52" s="28">
         <f ca="1">IFERROR(
@@ -19362,9 +19365,9 @@
       </c>
     </row>
     <row r="53" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="65"/>
-      <c r="B53" s="43" t="s">
-        <v>127</v>
+      <c r="A53" s="31"/>
+      <c r="B53" s="29" t="s">
+        <v>128</v>
       </c>
       <c r="C53" s="28">
         <f ca="1">IFERROR(
@@ -19385,18 +19388,18 @@
       </c>
     </row>
     <row r="54" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="81"/>
-      <c r="B54" s="75" t="s">
-        <v>126</v>
-      </c>
-      <c r="C54" s="80">
+      <c r="A54" s="65"/>
+      <c r="B54" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A54) &amp; "'!C:C"), B54),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D54" s="87" cm="1">
+      <c r="D54" s="73" cm="1">
         <f t="array" aca="1" ref="D54" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A54&lt;&gt;""),$A$7:A54) &amp; "'!C:C"), $B54,
@@ -19408,20 +19411,18 @@
       </c>
     </row>
     <row r="55" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="57" t="s">
-        <v>91</v>
-      </c>
-      <c r="B55" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="C55" s="28">
+      <c r="A55" s="81"/>
+      <c r="B55" s="75" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="80">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A55) &amp; "'!C:C"), B55),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D55" s="88" cm="1">
+      <c r="D55" s="87" cm="1">
         <f t="array" aca="1" ref="D55" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A55&lt;&gt;""),$A$7:A55) &amp; "'!C:C"), $B55,
@@ -19433,9 +19434,11 @@
       </c>
     </row>
     <row r="56" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="62"/>
+      <c r="A56" s="57" t="s">
+        <v>91</v>
+      </c>
       <c r="B56" s="29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C56" s="28">
         <f ca="1">IFERROR(
@@ -19444,7 +19447,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D56" s="73" cm="1">
+      <c r="D56" s="88" cm="1">
         <f t="array" aca="1" ref="D56" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A56&lt;&gt;""),$A$7:A56) &amp; "'!C:C"), $B56,
@@ -19458,7 +19461,7 @@
     <row r="57" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="62"/>
       <c r="B57" s="29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C57" s="28">
         <f ca="1">IFERROR(
@@ -19481,7 +19484,7 @@
     <row r="58" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="62"/>
       <c r="B58" s="29" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="C58" s="28">
         <f ca="1">IFERROR(
@@ -19502,9 +19505,9 @@
       </c>
     </row>
     <row r="59" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="28"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="29" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="C59" s="28">
         <f ca="1">IFERROR(
@@ -19525,18 +19528,18 @@
       </c>
     </row>
     <row r="60" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="26"/>
-      <c r="B60" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="C60" s="26">
+      <c r="A60" s="28"/>
+      <c r="B60" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A60) &amp; "'!C:C"), B60),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D60" s="87" cm="1">
+      <c r="D60" s="73" cm="1">
         <f t="array" aca="1" ref="D60" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A60&lt;&gt;""),$A$7:A60) &amp; "'!C:C"), $B60,
@@ -19548,20 +19551,18 @@
       </c>
     </row>
     <row r="61" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="71" t="s">
-        <v>53</v>
-      </c>
-      <c r="B61" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="47">
+      <c r="A61" s="26"/>
+      <c r="B61" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" s="26">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A61) &amp; "'!C:C"), B61),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D61" s="88" cm="1">
+      <c r="D61" s="87" cm="1">
         <f t="array" aca="1" ref="D61" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A61&lt;&gt;""),$A$7:A61) &amp; "'!C:C"), $B61,
@@ -19573,18 +19574,20 @@
       </c>
     </row>
     <row r="62" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="62"/>
-      <c r="B62" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="C62" s="28">
+      <c r="A62" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="B62" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A62) &amp; "'!C:C"), B62),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D62" s="73" cm="1">
+      <c r="D62" s="88" cm="1">
         <f t="array" aca="1" ref="D62" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A62&lt;&gt;""),$A$7:A62) &amp; "'!C:C"), $B62,
@@ -19598,7 +19601,7 @@
     <row r="63" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="62"/>
       <c r="B63" s="29" t="s">
-        <v>156</v>
+        <v>66</v>
       </c>
       <c r="C63" s="28">
         <f ca="1">IFERROR(
@@ -19621,7 +19624,7 @@
     <row r="64" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="62"/>
       <c r="B64" s="29" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="C64" s="28">
         <f ca="1">IFERROR(
@@ -19644,7 +19647,7 @@
     <row r="65" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="62"/>
       <c r="B65" s="29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C65" s="28">
         <f ca="1">IFERROR(
@@ -19665,9 +19668,9 @@
       </c>
     </row>
     <row r="66" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="28"/>
+      <c r="A66" s="62"/>
       <c r="B66" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C66" s="28">
         <f ca="1">IFERROR(
@@ -19688,9 +19691,9 @@
       </c>
     </row>
     <row r="67" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="38"/>
-      <c r="B67" s="43" t="s">
-        <v>82</v>
+      <c r="A67" s="28"/>
+      <c r="B67" s="29" t="s">
+        <v>34</v>
       </c>
       <c r="C67" s="28">
         <f ca="1">IFERROR(
@@ -19711,9 +19714,9 @@
       </c>
     </row>
     <row r="68" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="28"/>
-      <c r="B68" s="29" t="s">
-        <v>11</v>
+      <c r="A68" s="38"/>
+      <c r="B68" s="43" t="s">
+        <v>82</v>
       </c>
       <c r="C68" s="28">
         <f ca="1">IFERROR(
@@ -19722,7 +19725,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D68" s="87" cm="1">
+      <c r="D68" s="73" cm="1">
         <f t="array" aca="1" ref="D68" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A68&lt;&gt;""),$A$7:A68) &amp; "'!C:C"), $B68,
@@ -19734,11 +19737,11 @@
       </c>
     </row>
     <row r="69" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="90"/>
-      <c r="B69" s="91" t="s">
-        <v>18</v>
-      </c>
-      <c r="C69" s="90">
+      <c r="A69" s="28"/>
+      <c r="B69" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A69) &amp; "'!C:C"), B69),
    0
@@ -19755,33 +19758,20 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
     </row>
     <row r="70" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="71" t="s">
-        <v>54</v>
-      </c>
-      <c r="B70" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C70" s="47">
+      <c r="A70" s="90"/>
+      <c r="B70" s="91" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="90">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A70) &amp; "'!C:C"), B70),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D70" s="88" cm="1">
+      <c r="D70" s="87" cm="1">
         <f t="array" aca="1" ref="D70" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A70&lt;&gt;""),$A$7:A70) &amp; "'!C:C"), $B70,
@@ -19791,20 +19781,33 @@
 0)</f>
         <v>0</v>
       </c>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
     </row>
     <row r="71" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="28"/>
-      <c r="B71" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="28">
+      <c r="A71" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="B71" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A71) &amp; "'!C:C"), B71),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D71" s="73" cm="1">
+      <c r="D71" s="88" cm="1">
         <f t="array" aca="1" ref="D71" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A71&lt;&gt;""),$A$7:A71) &amp; "'!C:C"), $B71,
@@ -19818,7 +19821,7 @@
     <row r="72" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="28"/>
       <c r="B72" s="29" t="s">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="C72" s="28">
         <f ca="1">IFERROR(
@@ -19841,7 +19844,7 @@
     <row r="73" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="28"/>
       <c r="B73" s="29" t="s">
-        <v>17</v>
+        <v>163</v>
       </c>
       <c r="C73" s="28">
         <f ca="1">IFERROR(
@@ -19864,7 +19867,7 @@
     <row r="74" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="28"/>
       <c r="B74" s="29" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C74" s="28">
         <f ca="1">IFERROR(
@@ -19886,8 +19889,8 @@
     </row>
     <row r="75" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="28"/>
-      <c r="B75" s="92" t="s">
-        <v>161</v>
+      <c r="B75" s="29" t="s">
+        <v>12</v>
       </c>
       <c r="C75" s="28">
         <f ca="1">IFERROR(
@@ -19907,10 +19910,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="28"/>
-      <c r="B76" s="29" t="s">
-        <v>73</v>
+      <c r="B76" s="92" t="s">
+        <v>161</v>
       </c>
       <c r="C76" s="28">
         <f ca="1">IFERROR(
@@ -19919,7 +19922,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D76" s="87" cm="1">
+      <c r="D76" s="73" cm="1">
         <f t="array" aca="1" ref="D76" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A76&lt;&gt;""),$A$7:A76) &amp; "'!C:C"), $B76,
@@ -19930,19 +19933,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="24"/>
-      <c r="B77" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C77" s="24">
+    <row r="77" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="28"/>
+      <c r="B77" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A77) &amp; "'!C:C"), B77),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D77" s="73" cm="1">
+      <c r="D77" s="87" cm="1">
         <f t="array" aca="1" ref="D77" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A77&lt;&gt;""),$A$7:A77) &amp; "'!C:C"), $B77,
@@ -19954,20 +19957,18 @@
       </c>
     </row>
     <row r="78" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="72" t="s">
-        <v>55</v>
-      </c>
-      <c r="B78" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="C78" s="45">
+      <c r="A78" s="24"/>
+      <c r="B78" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C78" s="24">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A78) &amp; "'!C:C"), B78),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D78" s="88" cm="1">
+      <c r="D78" s="73" cm="1">
         <f t="array" aca="1" ref="D78" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A78&lt;&gt;""),$A$7:A78) &amp; "'!C:C"), $B78,
@@ -19977,31 +19978,22 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
-      <c r="M78" s="1"/>
-      <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
     </row>
     <row r="79" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="28"/>
-      <c r="B79" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C79" s="28">
+      <c r="A79" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="B79" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C79" s="45">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A79) &amp; "'!C:C"), B79),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D79" s="73" cm="1">
+      <c r="D79" s="88" cm="1">
         <f t="array" aca="1" ref="D79" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A79&lt;&gt;""),$A$7:A79) &amp; "'!C:C"), $B79,
@@ -20026,7 +20018,7 @@
     <row r="80" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="28"/>
       <c r="B80" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C80" s="28">
         <f ca="1">IFERROR(
@@ -20060,7 +20052,7 @@
     <row r="81" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="28"/>
       <c r="B81" s="29" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C81" s="28">
         <f ca="1">IFERROR(
@@ -20079,11 +20071,22 @@
 0)</f>
         <v>0</v>
       </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="O81" s="1"/>
     </row>
     <row r="82" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="28"/>
       <c r="B82" s="29" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C82" s="28">
         <f ca="1">IFERROR(
@@ -20102,22 +20105,11 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
     </row>
     <row r="83" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="28"/>
       <c r="B83" s="29" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="C83" s="28">
         <f ca="1">IFERROR(
@@ -20151,7 +20143,7 @@
     <row r="84" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="28"/>
       <c r="B84" s="29" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="C84" s="28">
         <f ca="1">IFERROR(
@@ -20182,10 +20174,10 @@
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
     </row>
-    <row r="85" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="28"/>
       <c r="B85" s="29" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="C85" s="28">
         <f ca="1">IFERROR(
@@ -20204,22 +20196,31 @@
 0)</f>
         <v>0</v>
       </c>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+      <c r="O85" s="1"/>
     </row>
     <row r="86" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="B86" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="C86" s="47">
+      <c r="A86" s="28"/>
+      <c r="B86" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C86" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A86) &amp; "'!C:C"), B86),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D86" s="88" cm="1">
+      <c r="D86" s="73" cm="1">
         <f t="array" aca="1" ref="D86" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A86&lt;&gt;""),$A$7:A86) &amp; "'!C:C"), $B86,
@@ -20231,18 +20232,20 @@
       </c>
     </row>
     <row r="87" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="31"/>
-      <c r="B87" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C87" s="28">
+      <c r="A87" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="B87" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A87) &amp; "'!C:C"), B87),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D87" s="73" cm="1">
+      <c r="D87" s="88" cm="1">
         <f t="array" aca="1" ref="D87" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A87&lt;&gt;""),$A$7:A87) &amp; "'!C:C"), $B87,
@@ -20256,7 +20259,7 @@
     <row r="88" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="31"/>
       <c r="B88" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C88" s="28">
         <f ca="1">IFERROR(
@@ -20279,7 +20282,7 @@
     <row r="89" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="31"/>
       <c r="B89" s="30" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C89" s="28">
         <f ca="1">IFERROR(
@@ -20302,7 +20305,7 @@
     <row r="90" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="31"/>
       <c r="B90" s="30" t="s">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="C90" s="28">
         <f ca="1">IFERROR(
@@ -20325,7 +20328,7 @@
     <row r="91" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="31"/>
       <c r="B91" s="30" t="s">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="C91" s="28">
         <f ca="1">IFERROR(
@@ -20348,7 +20351,7 @@
     <row r="92" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="31"/>
       <c r="B92" s="30" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C92" s="28">
         <f ca="1">IFERROR(
@@ -20369,9 +20372,9 @@
       </c>
     </row>
     <row r="93" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="65"/>
-      <c r="B93" s="66" t="s">
-        <v>83</v>
+      <c r="A93" s="31"/>
+      <c r="B93" s="30" t="s">
+        <v>38</v>
       </c>
       <c r="C93" s="28">
         <f ca="1">IFERROR(
@@ -20392,18 +20395,18 @@
       </c>
     </row>
     <row r="94" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="81"/>
-      <c r="B94" s="85" t="s">
-        <v>80</v>
-      </c>
-      <c r="C94" s="80">
+      <c r="A94" s="65"/>
+      <c r="B94" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="C94" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A94) &amp; "'!C:C"), B94),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D94" s="87" cm="1">
+      <c r="D94" s="73" cm="1">
         <f t="array" aca="1" ref="D94" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A94&lt;&gt;""),$A$7:A94) &amp; "'!C:C"), $B94,
@@ -20415,20 +20418,18 @@
       </c>
     </row>
     <row r="95" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="B95" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="C95" s="24">
+      <c r="A95" s="81"/>
+      <c r="B95" s="85" t="s">
+        <v>80</v>
+      </c>
+      <c r="C95" s="80">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A95) &amp; "'!C:C"), B95),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D95" s="88" cm="1">
+      <c r="D95" s="87" cm="1">
         <f t="array" aca="1" ref="D95" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A95&lt;&gt;""),$A$7:A95) &amp; "'!C:C"), $B95,
@@ -20440,18 +20441,20 @@
       </c>
     </row>
     <row r="96" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="73"/>
+      <c r="A96" s="24" t="s">
+        <v>88</v>
+      </c>
       <c r="B96" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="C96" s="28">
+        <v>104</v>
+      </c>
+      <c r="C96" s="24">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A96) &amp; "'!C:C"), B96),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D96" s="73" cm="1">
+      <c r="D96" s="88" cm="1">
         <f t="array" aca="1" ref="D96" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A96&lt;&gt;""),$A$7:A96) &amp; "'!C:C"), $B96,
@@ -20463,9 +20466,9 @@
       </c>
     </row>
     <row r="97" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="28"/>
+      <c r="A97" s="73"/>
       <c r="B97" s="29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C97" s="28">
         <f ca="1">IFERROR(
@@ -20488,7 +20491,7 @@
     <row r="98" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="28"/>
       <c r="B98" s="29" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="C98" s="28">
         <f ca="1">IFERROR(
@@ -20511,7 +20514,7 @@
     <row r="99" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="28"/>
       <c r="B99" s="29" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="C99" s="28">
         <f ca="1">IFERROR(
@@ -20532,18 +20535,18 @@
       </c>
     </row>
     <row r="100" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="80"/>
-      <c r="B100" s="75" t="s">
-        <v>100</v>
-      </c>
-      <c r="C100" s="80">
+      <c r="A100" s="28"/>
+      <c r="B100" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C100" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A100) &amp; "'!C:C"), B100),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D100" s="87" cm="1">
+      <c r="D100" s="73" cm="1">
         <f t="array" aca="1" ref="D100" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A100&lt;&gt;""),$A$7:A100) &amp; "'!C:C"), $B100,
@@ -20555,20 +20558,18 @@
       </c>
     </row>
     <row r="101" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="B101" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C101" s="24">
+      <c r="A101" s="80"/>
+      <c r="B101" s="75" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" s="80">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A101) &amp; "'!C:C"), B101),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D101" s="88" cm="1">
+      <c r="D101" s="87" cm="1">
         <f t="array" aca="1" ref="D101" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A101&lt;&gt;""),$A$7:A101) &amp; "'!C:C"), $B101,
@@ -20580,18 +20581,20 @@
       </c>
     </row>
     <row r="102" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="28"/>
-      <c r="B102" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="C102" s="28">
+      <c r="A102" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C102" s="24">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A102) &amp; "'!C:C"), B102),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D102" s="73" cm="1">
+      <c r="D102" s="88" cm="1">
         <f t="array" aca="1" ref="D102" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A102&lt;&gt;""),$A$7:A102) &amp; "'!C:C"), $B102,
@@ -20605,7 +20608,7 @@
     <row r="103" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="28"/>
       <c r="B103" s="29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C103" s="28">
         <f ca="1">IFERROR(
@@ -20628,7 +20631,7 @@
     <row r="104" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="28"/>
       <c r="B104" s="29" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="C104" s="28">
         <f ca="1">IFERROR(
@@ -20651,7 +20654,7 @@
     <row r="105" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="28"/>
       <c r="B105" s="29" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="C105" s="28">
         <f ca="1">IFERROR(
@@ -20674,7 +20677,7 @@
     <row r="106" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="28"/>
       <c r="B106" s="29" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C106" s="28">
         <f ca="1">IFERROR(
@@ -20697,7 +20700,7 @@
     <row r="107" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="28"/>
       <c r="B107" s="29" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C107" s="28">
         <f ca="1">IFERROR(
@@ -20720,7 +20723,7 @@
     <row r="108" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="28"/>
       <c r="B108" s="29" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="C108" s="28">
         <f ca="1">IFERROR(
@@ -20743,7 +20746,7 @@
     <row r="109" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="28"/>
       <c r="B109" s="29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C109" s="28">
         <f ca="1">IFERROR(
@@ -20764,9 +20767,9 @@
       </c>
     </row>
     <row r="110" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="31"/>
-      <c r="B110" s="30" t="s">
-        <v>113</v>
+      <c r="A110" s="28"/>
+      <c r="B110" s="29" t="s">
+        <v>114</v>
       </c>
       <c r="C110" s="28">
         <f ca="1">IFERROR(
@@ -20789,7 +20792,7 @@
     <row r="111" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="31"/>
       <c r="B111" s="30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C111" s="28">
         <f ca="1">IFERROR(
@@ -20810,18 +20813,18 @@
       </c>
     </row>
     <row r="112" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="79"/>
-      <c r="B112" s="78" t="s">
-        <v>111</v>
-      </c>
-      <c r="C112" s="77">
+      <c r="A112" s="31"/>
+      <c r="B112" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="C112" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A112) &amp; "'!C:C"), B112),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D112" s="87" cm="1">
+      <c r="D112" s="73" cm="1">
         <f t="array" aca="1" ref="D112" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A112&lt;&gt;""),$A$7:A112) &amp; "'!C:C"), $B112,
@@ -20833,20 +20836,18 @@
       </c>
     </row>
     <row r="113" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="B113" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="C113" s="24">
+      <c r="A113" s="79"/>
+      <c r="B113" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="C113" s="77">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A113) &amp; "'!C:C"), B113),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D113" s="88" cm="1">
+      <c r="D113" s="87" cm="1">
         <f t="array" aca="1" ref="D113" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A113&lt;&gt;""),$A$7:A113) &amp; "'!C:C"), $B113,
@@ -20858,18 +20859,20 @@
       </c>
     </row>
     <row r="114" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="28"/>
-      <c r="B114" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="C114" s="28">
+      <c r="A114" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B114" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C114" s="24">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A114) &amp; "'!C:C"), B114),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D114" s="73" cm="1">
+      <c r="D114" s="88" cm="1">
         <f t="array" aca="1" ref="D114" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A114&lt;&gt;""),$A$7:A114) &amp; "'!C:C"), $B114,
@@ -20883,7 +20886,7 @@
     <row r="115" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="28"/>
       <c r="B115" s="29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C115" s="28">
         <f ca="1">IFERROR(
@@ -20906,7 +20909,7 @@
     <row r="116" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="28"/>
       <c r="B116" s="29" t="s">
-        <v>162</v>
+        <v>108</v>
       </c>
       <c r="C116" s="28">
         <f ca="1">IFERROR(
@@ -20929,7 +20932,7 @@
     <row r="117" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="28"/>
       <c r="B117" s="29" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="C117" s="28">
         <f ca="1">IFERROR(
@@ -20952,7 +20955,7 @@
     <row r="118" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="28"/>
       <c r="B118" s="29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C118" s="28">
         <f ca="1">IFERROR(
@@ -20973,18 +20976,18 @@
       </c>
     </row>
     <row r="119" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="76"/>
-      <c r="B119" s="75" t="s">
-        <v>105</v>
-      </c>
-      <c r="C119" s="74">
+      <c r="A119" s="28"/>
+      <c r="B119" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C119" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A119) &amp; "'!C:C"), B119),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D119" s="87" cm="1">
+      <c r="D119" s="73" cm="1">
         <f t="array" aca="1" ref="D119" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A119&lt;&gt;""),$A$7:A119) &amp; "'!C:C"), $B119,
@@ -20996,20 +20999,18 @@
       </c>
     </row>
     <row r="120" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="69" t="s">
-        <v>87</v>
-      </c>
-      <c r="B120" s="66" t="s">
-        <v>99</v>
-      </c>
-      <c r="C120" s="47">
+      <c r="A120" s="76"/>
+      <c r="B120" s="75" t="s">
+        <v>105</v>
+      </c>
+      <c r="C120" s="74">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A120) &amp; "'!C:C"), B120),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D120" s="88" cm="1">
+      <c r="D120" s="87" cm="1">
         <f t="array" aca="1" ref="D120" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A120&lt;&gt;""),$A$7:A120) &amp; "'!C:C"), $B120,
@@ -21021,18 +21022,20 @@
       </c>
     </row>
     <row r="121" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="73"/>
-      <c r="B121" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="C121" s="28">
+      <c r="A121" s="69" t="s">
+        <v>87</v>
+      </c>
+      <c r="B121" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="C121" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A121) &amp; "'!C:C"), B121),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D121" s="73" cm="1">
+      <c r="D121" s="88" cm="1">
         <f t="array" aca="1" ref="D121" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A121&lt;&gt;""),$A$7:A121) &amp; "'!C:C"), $B121,
@@ -21044,9 +21047,9 @@
       </c>
     </row>
     <row r="122" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="28"/>
+      <c r="A122" s="73"/>
       <c r="B122" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C122" s="28">
         <f ca="1">IFERROR(
@@ -21067,11 +21070,11 @@
       </c>
     </row>
     <row r="123" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="24"/>
-      <c r="B123" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C123" s="24">
+      <c r="A123" s="28"/>
+      <c r="B123" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C123" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A123) &amp; "'!C:C"), B123),
    0
@@ -21090,11 +21093,11 @@
       </c>
     </row>
     <row r="124" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="38"/>
-      <c r="B124" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="C124" s="28">
+      <c r="A124" s="24"/>
+      <c r="B124" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C124" s="24">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A124) &amp; "'!C:C"), B124),
    0
@@ -21113,9 +21116,9 @@
       </c>
     </row>
     <row r="125" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="28"/>
-      <c r="B125" s="29" t="s">
-        <v>94</v>
+      <c r="A125" s="38"/>
+      <c r="B125" s="43" t="s">
+        <v>95</v>
       </c>
       <c r="C125" s="28">
         <f ca="1">IFERROR(
@@ -21124,7 +21127,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D125" s="87" cm="1">
+      <c r="D125" s="73" cm="1">
         <f t="array" aca="1" ref="D125" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A125&lt;&gt;""),$A$7:A125) &amp; "'!C:C"), $B125,
@@ -21136,20 +21139,18 @@
       </c>
     </row>
     <row r="126" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="B126" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="C126" s="47">
+      <c r="A126" s="28"/>
+      <c r="B126" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C126" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A126) &amp; "'!C:C"), B126),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D126" s="88" cm="1">
+      <c r="D126" s="87" cm="1">
         <f t="array" aca="1" ref="D126" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A126&lt;&gt;""),$A$7:A126) &amp; "'!C:C"), $B126,
@@ -21161,18 +21162,20 @@
       </c>
     </row>
     <row r="127" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="31"/>
-      <c r="B127" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="C127" s="28">
+      <c r="A127" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="B127" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="C127" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A127) &amp; "'!C:C"), B127),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D127" s="73" cm="1">
+      <c r="D127" s="88" cm="1">
         <f t="array" aca="1" ref="D127" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A127&lt;&gt;""),$A$7:A127) &amp; "'!C:C"), $B127,
@@ -21186,7 +21189,7 @@
     <row r="128" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="31"/>
       <c r="B128" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C128" s="28">
         <f ca="1">IFERROR(
@@ -21207,11 +21210,11 @@
       </c>
     </row>
     <row r="129" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="65"/>
-      <c r="B129" s="66" t="s">
-        <v>122</v>
-      </c>
-      <c r="C129" s="38">
+      <c r="A129" s="31"/>
+      <c r="B129" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="C129" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A129) &amp; "'!C:C"), B129),
    0
@@ -21230,11 +21233,11 @@
       </c>
     </row>
     <row r="130" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="31"/>
-      <c r="B130" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="C130" s="28">
+      <c r="A130" s="65"/>
+      <c r="B130" s="66" t="s">
+        <v>122</v>
+      </c>
+      <c r="C130" s="38">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A130) &amp; "'!C:C"), B130),
    0
@@ -21253,9 +21256,9 @@
       </c>
     </row>
     <row r="131" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="73"/>
-      <c r="B131" s="29" t="s">
-        <v>152</v>
+      <c r="A131" s="31"/>
+      <c r="B131" s="30" t="s">
+        <v>151</v>
       </c>
       <c r="C131" s="28">
         <f ca="1">IFERROR(
@@ -21264,7 +21267,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D131" s="87" cm="1">
+      <c r="D131" s="73" cm="1">
         <f t="array" aca="1" ref="D131" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A131&lt;&gt;""),$A$7:A131) &amp; "'!C:C"), $B131,
@@ -21276,20 +21279,18 @@
       </c>
     </row>
     <row r="132" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="69" t="s">
-        <v>140</v>
-      </c>
-      <c r="B132" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="C132" s="47">
+      <c r="A132" s="73"/>
+      <c r="B132" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="C132" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A132) &amp; "'!C:C"), B132),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D132" s="88" cm="1">
+      <c r="D132" s="87" cm="1">
         <f t="array" aca="1" ref="D132" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A132&lt;&gt;""),$A$7:A132) &amp; "'!C:C"), $B132,
@@ -21301,18 +21302,20 @@
       </c>
     </row>
     <row r="133" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="31"/>
-      <c r="B133" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C133" s="28">
+      <c r="A133" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="C133" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A133) &amp; "'!C:C"), B133),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D133" s="73" cm="1">
+      <c r="D133" s="88" cm="1">
         <f t="array" aca="1" ref="D133" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A133&lt;&gt;""),$A$7:A133) &amp; "'!C:C"), $B133,
@@ -21326,7 +21329,7 @@
     <row r="134" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="31"/>
       <c r="B134" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C134" s="28">
         <f ca="1">IFERROR(
@@ -21347,11 +21350,11 @@
       </c>
     </row>
     <row r="135" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="65"/>
-      <c r="B135" s="66" t="s">
-        <v>144</v>
-      </c>
-      <c r="C135" s="38">
+      <c r="A135" s="31"/>
+      <c r="B135" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="C135" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A135) &amp; "'!C:C"), B135),
    0
@@ -21370,11 +21373,11 @@
       </c>
     </row>
     <row r="136" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="31"/>
-      <c r="B136" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="C136" s="28">
+      <c r="A136" s="65"/>
+      <c r="B136" s="66" t="s">
+        <v>144</v>
+      </c>
+      <c r="C136" s="38">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A136) &amp; "'!C:C"), B136),
    0
@@ -21393,9 +21396,9 @@
       </c>
     </row>
     <row r="137" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="73"/>
-      <c r="B137" s="29" t="s">
-        <v>146</v>
+      <c r="A137" s="31"/>
+      <c r="B137" s="30" t="s">
+        <v>145</v>
       </c>
       <c r="C137" s="28">
         <f ca="1">IFERROR(
@@ -21416,9 +21419,9 @@
       </c>
     </row>
     <row r="138" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="28"/>
+      <c r="A138" s="73"/>
       <c r="B138" s="29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C138" s="28">
         <f ca="1">IFERROR(
@@ -21439,19 +21442,36 @@
       </c>
     </row>
     <row r="139" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="39"/>
-      <c r="B139" s="40"/>
-      <c r="C139" s="41"/>
-      <c r="D139" s="22"/>
+      <c r="A139" s="28"/>
+      <c r="B139" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C139" s="28">
+        <f ca="1">IFERROR(
+   COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A139) &amp; "'!C:C"), B139),
+   0
+)</f>
+        <v>0</v>
+      </c>
+      <c r="D139" s="73" cm="1">
+        <f t="array" aca="1" ref="D139" ca="1">IFERROR(
+  COUNTIFS(
+    INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A139&lt;&gt;""),$A$7:A139) &amp; "'!C:C"), $B139,
+    INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A139&lt;&gt;""),$A$7:A139) &amp; "'!E:E"), "&gt;=" &amp; ($B$3-6),
+    INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A139&lt;&gt;""),$A$7:A139) &amp; "'!E:E"), "&lt;=" &amp; $B$3
+  ),
+0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="140" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="41"/>
-      <c r="B140" s="42"/>
+      <c r="A140" s="39"/>
+      <c r="B140" s="40"/>
       <c r="C140" s="41"/>
       <c r="D140" s="22"/>
     </row>
     <row r="141" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="39"/>
+      <c r="A141" s="41"/>
       <c r="B141" s="42"/>
       <c r="C141" s="41"/>
       <c r="D141" s="22"/>
@@ -21464,7 +21484,7 @@
     </row>
     <row r="143" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="39"/>
-      <c r="B143" s="40"/>
+      <c r="B143" s="42"/>
       <c r="C143" s="41"/>
       <c r="D143" s="22"/>
     </row>
@@ -21475,25 +21495,25 @@
       <c r="D144" s="22"/>
     </row>
     <row r="145" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="41"/>
+      <c r="A145" s="39"/>
       <c r="B145" s="40"/>
       <c r="C145" s="41"/>
       <c r="D145" s="22"/>
     </row>
     <row r="146" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="39"/>
+      <c r="A146" s="41"/>
       <c r="B146" s="40"/>
       <c r="C146" s="41"/>
       <c r="D146" s="22"/>
     </row>
     <row r="147" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="41"/>
+      <c r="A147" s="39"/>
       <c r="B147" s="40"/>
       <c r="C147" s="41"/>
       <c r="D147" s="22"/>
     </row>
     <row r="148" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="39"/>
+      <c r="A148" s="41"/>
       <c r="B148" s="40"/>
       <c r="C148" s="41"/>
       <c r="D148" s="22"/>
@@ -21553,13 +21573,13 @@
       <c r="D157" s="22"/>
     </row>
     <row r="158" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="41"/>
-      <c r="B158" s="42"/>
+      <c r="A158" s="39"/>
+      <c r="B158" s="40"/>
       <c r="C158" s="41"/>
       <c r="D158" s="22"/>
     </row>
     <row r="159" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="39"/>
+      <c r="A159" s="41"/>
       <c r="B159" s="42"/>
       <c r="C159" s="41"/>
       <c r="D159" s="22"/>
@@ -21572,7 +21592,7 @@
     </row>
     <row r="161" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="39"/>
-      <c r="B161" s="40"/>
+      <c r="B161" s="42"/>
       <c r="C161" s="41"/>
       <c r="D161" s="22"/>
     </row>
@@ -21583,25 +21603,25 @@
       <c r="D162" s="22"/>
     </row>
     <row r="163" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="41"/>
+      <c r="A163" s="39"/>
       <c r="B163" s="40"/>
       <c r="C163" s="41"/>
       <c r="D163" s="22"/>
     </row>
     <row r="164" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="39"/>
+      <c r="A164" s="41"/>
       <c r="B164" s="40"/>
       <c r="C164" s="41"/>
       <c r="D164" s="22"/>
     </row>
     <row r="165" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="41"/>
+      <c r="A165" s="39"/>
       <c r="B165" s="40"/>
       <c r="C165" s="41"/>
       <c r="D165" s="22"/>
     </row>
     <row r="166" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="39"/>
+      <c r="A166" s="41"/>
       <c r="B166" s="40"/>
       <c r="C166" s="41"/>
       <c r="D166" s="22"/>
@@ -21649,8 +21669,8 @@
       <c r="D173" s="22"/>
     </row>
     <row r="174" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="41"/>
-      <c r="B174" s="42"/>
+      <c r="A174" s="39"/>
+      <c r="B174" s="40"/>
       <c r="C174" s="41"/>
       <c r="D174" s="22"/>
     </row>
@@ -21799,9 +21819,9 @@
       <c r="D198" s="22"/>
     </row>
     <row r="199" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="23"/>
-      <c r="B199" s="21"/>
-      <c r="C199" s="21"/>
+      <c r="A199" s="41"/>
+      <c r="B199" s="42"/>
+      <c r="C199" s="41"/>
       <c r="D199" s="22"/>
     </row>
     <row r="200" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
@@ -22012,6 +22032,7 @@
       <c r="A234" s="23"/>
       <c r="B234" s="21"/>
       <c r="C234" s="21"/>
+      <c r="D234" s="22"/>
     </row>
     <row r="235" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="23"/>
@@ -22029,7 +22050,7 @@
       <c r="C237" s="21"/>
     </row>
     <row r="238" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="21"/>
+      <c r="A238" s="23"/>
       <c r="B238" s="21"/>
       <c r="C238" s="21"/>
     </row>
@@ -22121,6 +22142,7 @@
     <row r="256" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="21"/>
       <c r="B256" s="21"/>
+      <c r="C256" s="21"/>
     </row>
     <row r="257" spans="1:2" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="21"/>
@@ -22385,6 +22407,10 @@
     <row r="322" spans="1:2" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="21"/>
       <c r="B322" s="21"/>
+    </row>
+    <row r="323" spans="1:2" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="21"/>
+      <c r="B323" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -22394,7 +22420,7 @@
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="12" max="3" man="1"/>
-    <brk id="119" max="3" man="1"/>
+    <brk id="120" max="3" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>

--- a/Month YEAR - Body Motions.xlsx
+++ b/Month YEAR - Body Motions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyayas/VALD Automator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414C0AF1-7EE3-BD45-AC8A-E8B524C6DAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36805066-0B4E-3246-836F-C1256E05F41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1713,12 +1713,7 @@
         <v>86</v>
       </c>
       <c r="B7" s="37">
-        <f t="shared" ref="B7:B17" ca="1" si="0">IFERROR(
-  COUNTIFS(
-    INDIRECT("'" &amp; $A7 &amp; "'!D:D"), "&gt;=" &amp; $B$3-7,
-    INDIRECT("'" &amp; $A7 &amp; "'!D:D"), "&lt;=" &amp; $B$3
-  ),
-0)</f>
+        <f t="shared" ref="B7:B23" ca="1" si="0">IFERROR(COUNTIFS(INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&gt;=" &amp; $B$3-7, INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&lt;=" &amp; $B$3),0)</f>
         <v>0</v>
       </c>
       <c r="C7" s="36" cm="1">
@@ -1794,12 +1789,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="37">
-        <f ca="1">IFERROR(
-  COUNTIFS(
-    INDIRECT("'" &amp; $A10 &amp; "'!D:D"), "&gt;=" &amp; $B$3-7,
-    INDIRECT("'" &amp; $A10 &amp; "'!D:D"), "&lt;=" &amp; $B$3
-  ),
-0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C10" s="36" cm="1">
@@ -1817,12 +1807,7 @@
         <v>93</v>
       </c>
       <c r="B11" s="37">
-        <f ca="1">IFERROR(
-  COUNTIFS(
-    INDIRECT("'" &amp; $A11 &amp; "'!D:D"), "&gt;=" &amp; $B$3-7,
-    INDIRECT("'" &amp; $A11 &amp; "'!D:D"), "&lt;=" &amp; $B$3
-  ),
-0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C11" s="36" cm="1">
@@ -1841,12 +1826,7 @@
         <v>92</v>
       </c>
       <c r="B12" s="37">
-        <f ca="1">IFERROR(
-  COUNTIFS(
-    INDIRECT("'" &amp; $A12 &amp; "'!D:D"), "&gt;=" &amp; $B$3-7,
-    INDIRECT("'" &amp; $A12 &amp; "'!D:D"), "&lt;=" &amp; $B$3
-  ),
-0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C12" s="36" cm="1">
@@ -1864,12 +1844,7 @@
         <v>91</v>
       </c>
       <c r="B13" s="37">
-        <f ca="1">IFERROR(
-  COUNTIFS(
-    INDIRECT("'" &amp; $A13 &amp; "'!D:D"), "&gt;=" &amp; $B$3-7,
-    INDIRECT("'" &amp; $A13 &amp; "'!D:D"), "&lt;=" &amp; $B$3
-  ),
-0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C13" s="36" cm="1">
@@ -1887,12 +1862,7 @@
         <v>53</v>
       </c>
       <c r="B14" s="37">
-        <f ca="1">IFERROR(
-  COUNTIFS(
-    INDIRECT("'" &amp; $A14 &amp; "'!D:D"), "&gt;=" &amp; $B$3-7,
-    INDIRECT("'" &amp; $A14 &amp; "'!D:D"), "&lt;=" &amp; $B$3
-  ),
-0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C14" s="36" cm="1">
@@ -1975,12 +1945,7 @@
         <v>88</v>
       </c>
       <c r="B18" s="37">
-        <f t="shared" ref="B18:B23" ca="1" si="1">IFERROR(
-  COUNTIFS(
-    INDIRECT("'" &amp; $A18 &amp; "'!D:D"), "&gt;=" &amp; $B$3-7,
-    INDIRECT("'" &amp; $A18 &amp; "'!D:D"), "&lt;=" &amp; $B$3
-  ),
-0)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C18" s="36" cm="1">
@@ -1998,7 +1963,7 @@
         <v>90</v>
       </c>
       <c r="B19" s="37">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C19" s="36" cm="1">
@@ -2016,7 +1981,7 @@
         <v>89</v>
       </c>
       <c r="B20" s="37">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C20" s="36" cm="1">
@@ -2034,7 +1999,7 @@
         <v>87</v>
       </c>
       <c r="B21" s="37">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C21" s="36" cm="1">
@@ -2052,7 +2017,7 @@
         <v>139</v>
       </c>
       <c r="B22" s="37">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C22" s="36" cm="1">
@@ -2070,7 +2035,7 @@
         <v>140</v>
       </c>
       <c r="B23" s="37">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="C23" s="36" cm="1">

--- a/Month YEAR - Body Motions.xlsx
+++ b/Month YEAR - Body Motions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyayas/VALD Automator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E30D2D9-CAAF-2D48-BD93-DF30F377277F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1ADDFA9-9865-FC40-9242-BD5A611C24E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT 2" sheetId="10" r:id="rId1"/>
@@ -35,8 +35,8 @@
     <sheet name="Tabuk" sheetId="20" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">REPORT!$B$1:$B$362</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">REPORT!$A$1:$D$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">REPORT!$B$1:$B$363</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">REPORT!$A$1:$D$217</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'REPORT 2'!$A$1:$G$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'REPORT 2'!$1:$6</definedName>
   </definedNames>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="211">
   <si>
     <t>REPORT DATE:</t>
   </si>
@@ -719,6 +719,9 @@
   </si>
   <si>
     <t>Amal Al-Fahat Ghazi Al-Ruwaili</t>
+  </si>
+  <si>
+    <t>Wyssal Ben Dhieb</t>
   </si>
 </sst>
 </file>
@@ -1459,17 +1462,17 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -18306,7 +18309,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7051E0-986F-8244-A07B-F9D8BD0E96B4}">
-  <dimension ref="A1:W362"/>
+  <dimension ref="A1:W363"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="50.83203125" defaultRowHeight="50" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.83203125" style="1" customWidth="1"/>
@@ -19619,7 +19622,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D59" s="112" cm="1">
+      <c r="D59" s="110" cm="1">
         <f t="array" aca="1" ref="D59" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A59&lt;&gt;""),$A$7:A59) &amp; "'!C:C"), $B59,
@@ -19644,7 +19647,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D60" s="111" cm="1">
+      <c r="D60" s="109" cm="1">
         <f t="array" aca="1" ref="D60" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A60&lt;&gt;""),$A$7:A60) &amp; "'!C:C"), $B60,
@@ -21173,7 +21176,7 @@
     <row r="123" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="24"/>
       <c r="B123" s="29" t="s">
-        <v>102</v>
+        <v>210</v>
       </c>
       <c r="C123" s="28">
         <f ca="1">IFERROR(
@@ -21194,9 +21197,9 @@
       </c>
     </row>
     <row r="124" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="73"/>
+      <c r="A124" s="24"/>
       <c r="B124" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C124" s="28">
         <f ca="1">IFERROR(
@@ -21217,9 +21220,9 @@
       </c>
     </row>
     <row r="125" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="28"/>
+      <c r="A125" s="73"/>
       <c r="B125" s="29" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C125" s="28">
         <f ca="1">IFERROR(
@@ -21242,7 +21245,7 @@
     <row r="126" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="28"/>
       <c r="B126" s="29" t="s">
-        <v>104</v>
+        <v>199</v>
       </c>
       <c r="C126" s="28">
         <f ca="1">IFERROR(
@@ -21265,7 +21268,7 @@
     <row r="127" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="28"/>
       <c r="B127" s="29" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C127" s="28">
         <f ca="1">IFERROR(
@@ -21286,18 +21289,18 @@
       </c>
     </row>
     <row r="128" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="80"/>
-      <c r="B128" s="75" t="s">
-        <v>159</v>
-      </c>
-      <c r="C128" s="80">
+      <c r="A128" s="28"/>
+      <c r="B128" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="C128" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A128) &amp; "'!C:C"), B128),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D128" s="87" cm="1">
+      <c r="D128" s="73" cm="1">
         <f t="array" aca="1" ref="D128" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A128&lt;&gt;""),$A$7:A128) &amp; "'!C:C"), $B128,
@@ -21309,20 +21312,18 @@
       </c>
     </row>
     <row r="129" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="69" t="s">
-        <v>208</v>
-      </c>
-      <c r="B129" s="48" t="s">
-        <v>209</v>
-      </c>
-      <c r="C129" s="47">
+      <c r="A129" s="80"/>
+      <c r="B129" s="75" t="s">
+        <v>159</v>
+      </c>
+      <c r="C129" s="80">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A129) &amp; "'!C:C"), B129),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D129" s="88" cm="1">
+      <c r="D129" s="87" cm="1">
         <f t="array" aca="1" ref="D129" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A129&lt;&gt;""),$A$7:A129) &amp; "'!C:C"), $B129,
@@ -21334,18 +21335,20 @@
       </c>
     </row>
     <row r="130" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="31"/>
-      <c r="B130" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C130" s="28">
+      <c r="A130" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="B130" s="48" t="s">
+        <v>209</v>
+      </c>
+      <c r="C130" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A130) &amp; "'!C:C"), B130),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D130" s="73" cm="1">
+      <c r="D130" s="88" cm="1">
         <f t="array" aca="1" ref="D130" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A130&lt;&gt;""),$A$7:A130) &amp; "'!C:C"), $B130,
@@ -21359,7 +21362,7 @@
     <row r="131" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="31"/>
       <c r="B131" s="30" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="C131" s="28">
         <f ca="1">IFERROR(
@@ -21380,11 +21383,11 @@
       </c>
     </row>
     <row r="132" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="65"/>
-      <c r="B132" s="66" t="s">
-        <v>135</v>
-      </c>
-      <c r="C132" s="38">
+      <c r="A132" s="31"/>
+      <c r="B132" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C132" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A132) &amp; "'!C:C"), B132),
    0
@@ -21403,18 +21406,18 @@
       </c>
     </row>
     <row r="133" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="81"/>
-      <c r="B133" s="85" t="s">
-        <v>131</v>
-      </c>
-      <c r="C133" s="80">
+      <c r="A133" s="65"/>
+      <c r="B133" s="66" t="s">
+        <v>135</v>
+      </c>
+      <c r="C133" s="38">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A133) &amp; "'!C:C"), B133),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D133" s="112" cm="1">
+      <c r="D133" s="73" cm="1">
         <f t="array" aca="1" ref="D133" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A133&lt;&gt;""),$A$7:A133) &amp; "'!C:C"), $B133,
@@ -21426,20 +21429,18 @@
       </c>
     </row>
     <row r="134" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="B134" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="C134" s="24">
+      <c r="A134" s="81"/>
+      <c r="B134" s="85" t="s">
+        <v>131</v>
+      </c>
+      <c r="C134" s="80">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A134) &amp; "'!C:C"), B134),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D134" s="111" cm="1">
+      <c r="D134" s="110" cm="1">
         <f t="array" aca="1" ref="D134" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A134&lt;&gt;""),$A$7:A134) &amp; "'!C:C"), $B134,
@@ -21451,18 +21452,20 @@
       </c>
     </row>
     <row r="135" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="28"/>
-      <c r="B135" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="C135" s="28">
+      <c r="A135" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B135" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C135" s="24">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A135) &amp; "'!C:C"), B135),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D135" s="73" cm="1">
+      <c r="D135" s="109" cm="1">
         <f t="array" aca="1" ref="D135" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A135&lt;&gt;""),$A$7:A135) &amp; "'!C:C"), $B135,
@@ -21476,7 +21479,7 @@
     <row r="136" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="28"/>
       <c r="B136" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C136" s="28">
         <f ca="1">IFERROR(
@@ -21499,7 +21502,7 @@
     <row r="137" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="28"/>
       <c r="B137" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C137" s="28">
         <f ca="1">IFERROR(
@@ -21522,7 +21525,7 @@
     <row r="138" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="28"/>
       <c r="B138" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C138" s="28">
         <f ca="1">IFERROR(
@@ -21545,7 +21548,7 @@
     <row r="139" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="28"/>
       <c r="B139" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C139" s="28">
         <f ca="1">IFERROR(
@@ -21568,7 +21571,7 @@
     <row r="140" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="28"/>
       <c r="B140" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C140" s="28">
         <f ca="1">IFERROR(
@@ -21591,7 +21594,7 @@
     <row r="141" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="28"/>
       <c r="B141" s="29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C141" s="28">
         <f ca="1">IFERROR(
@@ -21614,7 +21617,7 @@
     <row r="142" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="28"/>
       <c r="B142" s="29" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C142" s="28">
         <f ca="1">IFERROR(
@@ -21637,7 +21640,7 @@
     <row r="143" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="28"/>
       <c r="B143" s="29" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="C143" s="28">
         <f ca="1">IFERROR(
@@ -21658,9 +21661,9 @@
       </c>
     </row>
     <row r="144" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="31"/>
-      <c r="B144" s="30" t="s">
-        <v>160</v>
+      <c r="A144" s="28"/>
+      <c r="B144" s="29" t="s">
+        <v>153</v>
       </c>
       <c r="C144" s="28">
         <f ca="1">IFERROR(
@@ -21683,7 +21686,7 @@
     <row r="145" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="31"/>
       <c r="B145" s="30" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C145" s="28">
         <f ca="1">IFERROR(
@@ -21704,18 +21707,18 @@
       </c>
     </row>
     <row r="146" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="79"/>
-      <c r="B146" s="78" t="s">
-        <v>201</v>
-      </c>
-      <c r="C146" s="77">
+      <c r="A146" s="31"/>
+      <c r="B146" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C146" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A146) &amp; "'!C:C"), B146),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D146" s="87" cm="1">
+      <c r="D146" s="73" cm="1">
         <f t="array" aca="1" ref="D146" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A146&lt;&gt;""),$A$7:A146) &amp; "'!C:C"), $B146,
@@ -21727,20 +21730,18 @@
       </c>
     </row>
     <row r="147" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="B147" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C147" s="24">
+      <c r="A147" s="79"/>
+      <c r="B147" s="78" t="s">
+        <v>201</v>
+      </c>
+      <c r="C147" s="77">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A147) &amp; "'!C:C"), B147),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D147" s="88" cm="1">
+      <c r="D147" s="87" cm="1">
         <f t="array" aca="1" ref="D147" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A147&lt;&gt;""),$A$7:A147) &amp; "'!C:C"), $B147,
@@ -21752,18 +21753,20 @@
       </c>
     </row>
     <row r="148" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="28"/>
-      <c r="B148" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="C148" s="28">
+      <c r="A148" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B148" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C148" s="24">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A148) &amp; "'!C:C"), B148),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D148" s="73" cm="1">
+      <c r="D148" s="88" cm="1">
         <f t="array" aca="1" ref="D148" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A148&lt;&gt;""),$A$7:A148) &amp; "'!C:C"), $B148,
@@ -21777,7 +21780,7 @@
     <row r="149" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="28"/>
       <c r="B149" s="29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C149" s="28">
         <f ca="1">IFERROR(
@@ -21800,7 +21803,7 @@
     <row r="150" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="28"/>
       <c r="B150" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C150" s="28">
         <f ca="1">IFERROR(
@@ -21823,7 +21826,7 @@
     <row r="151" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="28"/>
       <c r="B151" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C151" s="28">
         <f ca="1">IFERROR(
@@ -21846,7 +21849,7 @@
     <row r="152" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="28"/>
       <c r="B152" s="29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C152" s="28">
         <f ca="1">IFERROR(
@@ -21867,18 +21870,18 @@
       </c>
     </row>
     <row r="153" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="76"/>
-      <c r="B153" s="75" t="s">
-        <v>162</v>
-      </c>
-      <c r="C153" s="74">
+      <c r="A153" s="28"/>
+      <c r="B153" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C153" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A153) &amp; "'!C:C"), B153),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D153" s="87" cm="1">
+      <c r="D153" s="73" cm="1">
         <f t="array" aca="1" ref="D153" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A153&lt;&gt;""),$A$7:A153) &amp; "'!C:C"), $B153,
@@ -21890,20 +21893,18 @@
       </c>
     </row>
     <row r="154" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="69" t="s">
-        <v>87</v>
-      </c>
-      <c r="B154" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="C154" s="47">
+      <c r="A154" s="76"/>
+      <c r="B154" s="75" t="s">
+        <v>162</v>
+      </c>
+      <c r="C154" s="74">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A154) &amp; "'!C:C"), B154),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D154" s="88" cm="1">
+      <c r="D154" s="87" cm="1">
         <f t="array" aca="1" ref="D154" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A154&lt;&gt;""),$A$7:A154) &amp; "'!C:C"), $B154,
@@ -21915,18 +21916,20 @@
       </c>
     </row>
     <row r="155" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="73"/>
-      <c r="B155" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="C155" s="28">
+      <c r="A155" s="69" t="s">
+        <v>87</v>
+      </c>
+      <c r="B155" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="C155" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A155) &amp; "'!C:C"), B155),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D155" s="73" cm="1">
+      <c r="D155" s="88" cm="1">
         <f t="array" aca="1" ref="D155" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A155&lt;&gt;""),$A$7:A155) &amp; "'!C:C"), $B155,
@@ -21940,7 +21943,7 @@
     <row r="156" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="73"/>
       <c r="B156" s="29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C156" s="28">
         <f ca="1">IFERROR(
@@ -21963,7 +21966,7 @@
     <row r="157" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="73"/>
       <c r="B157" s="29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C157" s="28">
         <f ca="1">IFERROR(
@@ -21986,7 +21989,7 @@
     <row r="158" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="73"/>
       <c r="B158" s="29" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="C158" s="28">
         <f ca="1">IFERROR(
@@ -22007,9 +22010,9 @@
       </c>
     </row>
     <row r="159" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="28"/>
+      <c r="A159" s="73"/>
       <c r="B159" s="29" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="C159" s="28">
         <f ca="1">IFERROR(
@@ -22030,9 +22033,9 @@
       </c>
     </row>
     <row r="160" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="24"/>
-      <c r="B160" s="25" t="s">
-        <v>203</v>
+      <c r="A160" s="28"/>
+      <c r="B160" s="29" t="s">
+        <v>99</v>
       </c>
       <c r="C160" s="28">
         <f ca="1">IFERROR(
@@ -22055,7 +22058,7 @@
     <row r="161" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="24"/>
       <c r="B161" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C161" s="28">
         <f ca="1">IFERROR(
@@ -22078,9 +22081,9 @@
     <row r="162" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="24"/>
       <c r="B162" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="C162" s="24">
+        <v>204</v>
+      </c>
+      <c r="C162" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A162) &amp; "'!C:C"), B162),
    0
@@ -22099,11 +22102,11 @@
       </c>
     </row>
     <row r="163" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="38"/>
-      <c r="B163" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="C163" s="28">
+      <c r="A163" s="24"/>
+      <c r="B163" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="C163" s="24">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A163) &amp; "'!C:C"), B163),
    0
@@ -22122,9 +22125,9 @@
       </c>
     </row>
     <row r="164" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="28"/>
-      <c r="B164" s="29" t="s">
-        <v>206</v>
+      <c r="A164" s="38"/>
+      <c r="B164" s="43" t="s">
+        <v>95</v>
       </c>
       <c r="C164" s="28">
         <f ca="1">IFERROR(
@@ -22133,7 +22136,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D164" s="87" cm="1">
+      <c r="D164" s="73" cm="1">
         <f t="array" aca="1" ref="D164" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A164&lt;&gt;""),$A$7:A164) &amp; "'!C:C"), $B164,
@@ -22145,20 +22148,18 @@
       </c>
     </row>
     <row r="165" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="B165" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="C165" s="47">
+      <c r="A165" s="28"/>
+      <c r="B165" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C165" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A165) &amp; "'!C:C"), B165),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D165" s="88" cm="1">
+      <c r="D165" s="87" cm="1">
         <f t="array" aca="1" ref="D165" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A165&lt;&gt;""),$A$7:A165) &amp; "'!C:C"), $B165,
@@ -22170,18 +22171,20 @@
       </c>
     </row>
     <row r="166" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="31"/>
-      <c r="B166" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="C166" s="28">
+      <c r="A166" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="B166" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="C166" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A166) &amp; "'!C:C"), B166),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D166" s="73" cm="1">
+      <c r="D166" s="88" cm="1">
         <f t="array" aca="1" ref="D166" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A166&lt;&gt;""),$A$7:A166) &amp; "'!C:C"), $B166,
@@ -22195,7 +22198,7 @@
     <row r="167" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="31"/>
       <c r="B167" s="30" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="C167" s="28">
         <f ca="1">IFERROR(
@@ -22216,11 +22219,11 @@
       </c>
     </row>
     <row r="168" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="65"/>
-      <c r="B168" s="66" t="s">
-        <v>150</v>
-      </c>
-      <c r="C168" s="38">
+      <c r="A168" s="31"/>
+      <c r="B168" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="C168" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A168) &amp; "'!C:C"), B168),
    0
@@ -22239,11 +22242,11 @@
       </c>
     </row>
     <row r="169" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="31"/>
-      <c r="B169" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="C169" s="28">
+      <c r="A169" s="65"/>
+      <c r="B169" s="66" t="s">
+        <v>150</v>
+      </c>
+      <c r="C169" s="38">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A169) &amp; "'!C:C"), B169),
    0
@@ -22262,9 +22265,9 @@
       </c>
     </row>
     <row r="170" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="73"/>
-      <c r="B170" s="29" t="s">
-        <v>148</v>
+      <c r="A170" s="31"/>
+      <c r="B170" s="30" t="s">
+        <v>149</v>
       </c>
       <c r="C170" s="28">
         <f ca="1">IFERROR(
@@ -22273,7 +22276,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D170" s="87" cm="1">
+      <c r="D170" s="73" cm="1">
         <f t="array" aca="1" ref="D170" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A170&lt;&gt;""),$A$7:A170) &amp; "'!C:C"), $B170,
@@ -22285,20 +22288,18 @@
       </c>
     </row>
     <row r="171" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="69" t="s">
-        <v>140</v>
-      </c>
-      <c r="B171" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="C171" s="47">
+      <c r="A171" s="73"/>
+      <c r="B171" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="C171" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A171) &amp; "'!C:C"), B171),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D171" s="88" cm="1">
+      <c r="D171" s="87" cm="1">
         <f t="array" aca="1" ref="D171" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A171&lt;&gt;""),$A$7:A171) &amp; "'!C:C"), $B171,
@@ -22310,18 +22311,20 @@
       </c>
     </row>
     <row r="172" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="31"/>
-      <c r="B172" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="C172" s="28">
+      <c r="A172" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="B172" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="C172" s="47">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A172) &amp; "'!C:C"), B172),
    0
 )</f>
         <v>0</v>
       </c>
-      <c r="D172" s="73" cm="1">
+      <c r="D172" s="88" cm="1">
         <f t="array" aca="1" ref="D172" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A172&lt;&gt;""),$A$7:A172) &amp; "'!C:C"), $B172,
@@ -22335,7 +22338,7 @@
     <row r="173" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="31"/>
       <c r="B173" s="30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C173" s="28">
         <f ca="1">IFERROR(
@@ -22356,9 +22359,9 @@
       </c>
     </row>
     <row r="174" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="65"/>
-      <c r="B174" s="66" t="s">
-        <v>144</v>
+      <c r="A174" s="31"/>
+      <c r="B174" s="30" t="s">
+        <v>145</v>
       </c>
       <c r="C174" s="28">
         <f ca="1">IFERROR(
@@ -22381,9 +22384,9 @@
     <row r="175" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="65"/>
       <c r="B175" s="66" t="s">
-        <v>143</v>
-      </c>
-      <c r="C175" s="38">
+        <v>144</v>
+      </c>
+      <c r="C175" s="28">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A175) &amp; "'!C:C"), B175),
    0
@@ -22402,11 +22405,11 @@
       </c>
     </row>
     <row r="176" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="31"/>
-      <c r="B176" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C176" s="28">
+      <c r="A176" s="65"/>
+      <c r="B176" s="66" t="s">
+        <v>143</v>
+      </c>
+      <c r="C176" s="38">
         <f ca="1">IFERROR(
    COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A176) &amp; "'!C:C"), B176),
    0
@@ -22425,9 +22428,9 @@
       </c>
     </row>
     <row r="177" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="73"/>
-      <c r="B177" s="29" t="s">
-        <v>141</v>
+      <c r="A177" s="31"/>
+      <c r="B177" s="30" t="s">
+        <v>142</v>
       </c>
       <c r="C177" s="28">
         <f ca="1">IFERROR(
@@ -22448,9 +22451,9 @@
       </c>
     </row>
     <row r="178" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="28"/>
+      <c r="A178" s="73"/>
       <c r="B178" s="29" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="C178" s="28">
         <f ca="1">IFERROR(
@@ -22471,19 +22474,36 @@
       </c>
     </row>
     <row r="179" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="39"/>
-      <c r="B179" s="40"/>
-      <c r="C179" s="41"/>
-      <c r="D179" s="22"/>
+      <c r="A179" s="28"/>
+      <c r="B179" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C179" s="28">
+        <f ca="1">IFERROR(
+   COUNTIF(INDIRECT("'" &amp; LOOKUP("zzz",$A$7:A179) &amp; "'!C:C"), B179),
+   0
+)</f>
+        <v>0</v>
+      </c>
+      <c r="D179" s="73" cm="1">
+        <f t="array" aca="1" ref="D179" ca="1">IFERROR(
+  COUNTIFS(
+    INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A179&lt;&gt;""),$A$7:A179) &amp; "'!C:C"), $B179,
+    INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A179&lt;&gt;""),$A$7:A179) &amp; "'!E:E"), "&gt;=" &amp; ($B$3-6),
+    INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A179&lt;&gt;""),$A$7:A179) &amp; "'!E:E"), "&lt;=" &amp; $B$3
+  ),
+0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="180" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="41"/>
-      <c r="B180" s="42"/>
+      <c r="A180" s="39"/>
+      <c r="B180" s="40"/>
       <c r="C180" s="41"/>
       <c r="D180" s="22"/>
     </row>
     <row r="181" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="39"/>
+      <c r="A181" s="41"/>
       <c r="B181" s="42"/>
       <c r="C181" s="41"/>
       <c r="D181" s="22"/>
@@ -22496,7 +22516,7 @@
     </row>
     <row r="183" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="39"/>
-      <c r="B183" s="40"/>
+      <c r="B183" s="42"/>
       <c r="C183" s="41"/>
       <c r="D183" s="22"/>
     </row>
@@ -22507,25 +22527,25 @@
       <c r="D184" s="22"/>
     </row>
     <row r="185" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="41"/>
+      <c r="A185" s="39"/>
       <c r="B185" s="40"/>
       <c r="C185" s="41"/>
       <c r="D185" s="22"/>
     </row>
     <row r="186" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="39"/>
+      <c r="A186" s="41"/>
       <c r="B186" s="40"/>
       <c r="C186" s="41"/>
       <c r="D186" s="22"/>
     </row>
     <row r="187" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="41"/>
+      <c r="A187" s="39"/>
       <c r="B187" s="40"/>
       <c r="C187" s="41"/>
       <c r="D187" s="22"/>
     </row>
     <row r="188" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="39"/>
+      <c r="A188" s="41"/>
       <c r="B188" s="40"/>
       <c r="C188" s="41"/>
       <c r="D188" s="22"/>
@@ -22585,13 +22605,13 @@
       <c r="D197" s="22"/>
     </row>
     <row r="198" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="41"/>
-      <c r="B198" s="42"/>
+      <c r="A198" s="39"/>
+      <c r="B198" s="40"/>
       <c r="C198" s="41"/>
       <c r="D198" s="22"/>
     </row>
     <row r="199" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="39"/>
+      <c r="A199" s="41"/>
       <c r="B199" s="42"/>
       <c r="C199" s="41"/>
       <c r="D199" s="22"/>
@@ -22604,7 +22624,7 @@
     </row>
     <row r="201" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="39"/>
-      <c r="B201" s="40"/>
+      <c r="B201" s="42"/>
       <c r="C201" s="41"/>
       <c r="D201" s="22"/>
     </row>
@@ -22615,25 +22635,25 @@
       <c r="D202" s="22"/>
     </row>
     <row r="203" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="41"/>
+      <c r="A203" s="39"/>
       <c r="B203" s="40"/>
       <c r="C203" s="41"/>
       <c r="D203" s="22"/>
     </row>
     <row r="204" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="39"/>
+      <c r="A204" s="41"/>
       <c r="B204" s="40"/>
       <c r="C204" s="41"/>
       <c r="D204" s="22"/>
     </row>
     <row r="205" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="41"/>
+      <c r="A205" s="39"/>
       <c r="B205" s="40"/>
       <c r="C205" s="41"/>
       <c r="D205" s="22"/>
     </row>
     <row r="206" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="39"/>
+      <c r="A206" s="41"/>
       <c r="B206" s="40"/>
       <c r="C206" s="41"/>
       <c r="D206" s="22"/>
@@ -22681,8 +22701,8 @@
       <c r="D213" s="22"/>
     </row>
     <row r="214" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="41"/>
-      <c r="B214" s="42"/>
+      <c r="A214" s="39"/>
+      <c r="B214" s="40"/>
       <c r="C214" s="41"/>
       <c r="D214" s="22"/>
     </row>
@@ -22831,9 +22851,9 @@
       <c r="D238" s="22"/>
     </row>
     <row r="239" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="23"/>
-      <c r="B239" s="21"/>
-      <c r="C239" s="21"/>
+      <c r="A239" s="41"/>
+      <c r="B239" s="42"/>
+      <c r="C239" s="41"/>
       <c r="D239" s="22"/>
     </row>
     <row r="240" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
@@ -23044,6 +23064,7 @@
       <c r="A274" s="23"/>
       <c r="B274" s="21"/>
       <c r="C274" s="21"/>
+      <c r="D274" s="22"/>
     </row>
     <row r="275" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="23"/>
@@ -23061,7 +23082,7 @@
       <c r="C277" s="21"/>
     </row>
     <row r="278" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="21"/>
+      <c r="A278" s="23"/>
       <c r="B278" s="21"/>
       <c r="C278" s="21"/>
     </row>
@@ -23070,29 +23091,10 @@
       <c r="B279" s="21"/>
       <c r="C279" s="21"/>
     </row>
-    <row r="280" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="21"/>
       <c r="B280" s="21"/>
       <c r="C280" s="21"/>
-      <c r="E280" s="1"/>
-      <c r="F280" s="1"/>
-      <c r="G280" s="1"/>
-      <c r="H280" s="1"/>
-      <c r="I280" s="1"/>
-      <c r="J280" s="1"/>
-      <c r="K280" s="1"/>
-      <c r="L280" s="1"/>
-      <c r="M280" s="1"/>
-      <c r="N280" s="1"/>
-      <c r="O280" s="1"/>
-      <c r="P280" s="1"/>
-      <c r="Q280" s="1"/>
-      <c r="R280" s="1"/>
-      <c r="S280" s="1"/>
-      <c r="T280" s="1"/>
-      <c r="U280" s="1"/>
-      <c r="V280" s="1"/>
-      <c r="W280" s="1"/>
     </row>
     <row r="281" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="21"/>
@@ -23454,9 +23456,29 @@
       <c r="V295" s="1"/>
       <c r="W295" s="1"/>
     </row>
-    <row r="296" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="21"/>
       <c r="B296" s="21"/>
+      <c r="C296" s="21"/>
+      <c r="E296" s="1"/>
+      <c r="F296" s="1"/>
+      <c r="G296" s="1"/>
+      <c r="H296" s="1"/>
+      <c r="I296" s="1"/>
+      <c r="J296" s="1"/>
+      <c r="K296" s="1"/>
+      <c r="L296" s="1"/>
+      <c r="M296" s="1"/>
+      <c r="N296" s="1"/>
+      <c r="O296" s="1"/>
+      <c r="P296" s="1"/>
+      <c r="Q296" s="1"/>
+      <c r="R296" s="1"/>
+      <c r="S296" s="1"/>
+      <c r="T296" s="1"/>
+      <c r="U296" s="1"/>
+      <c r="V296" s="1"/>
+      <c r="W296" s="1"/>
     </row>
     <row r="297" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="21"/>
@@ -23721,6 +23743,10 @@
     <row r="362" spans="1:2" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="21"/>
       <c r="B362" s="21"/>
+    </row>
+    <row r="363" spans="1:2" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A363" s="21"/>
+      <c r="B363" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -23730,7 +23756,7 @@
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="19" max="3" man="1"/>
-    <brk id="153" max="3" man="1"/>
+    <brk id="154" max="3" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>
@@ -27176,9 +27202,9 @@
       <c r="C31" s="98"/>
       <c r="D31" s="104"/>
       <c r="E31" s="104"/>
-      <c r="F31" s="109"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="110"/>
+      <c r="F31" s="111"/>
+      <c r="G31" s="112"/>
+      <c r="H31" s="112"/>
     </row>
     <row r="32" spans="1:8" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="102"/>

--- a/Month YEAR - Body Motions.xlsx
+++ b/Month YEAR - Body Motions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyayas/VALD Automator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1ADDFA9-9865-FC40-9242-BD5A611C24E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1603B5A5-D37C-A841-8713-9E5D7D4854C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,14 +25,15 @@
     <sheet name="JED - Al Basateen" sheetId="3" r:id="rId10"/>
     <sheet name="JED - Al Faisaliyah" sheetId="1" r:id="rId11"/>
     <sheet name="JED - Al Naeem" sheetId="4" r:id="rId12"/>
-    <sheet name="DMM - Al Faisaliyah" sheetId="2" r:id="rId13"/>
-    <sheet name="DMM - Al Jalawiah" sheetId="18" r:id="rId14"/>
-    <sheet name="DMM - Al Nada" sheetId="23" r:id="rId15"/>
-    <sheet name="ALQ - Buraidah" sheetId="16" r:id="rId16"/>
-    <sheet name="ALQ - Unaizah" sheetId="17" r:id="rId17"/>
-    <sheet name="Al Ahsaa" sheetId="19" r:id="rId18"/>
-    <sheet name="AlUla" sheetId="21" r:id="rId19"/>
-    <sheet name="Tabuk" sheetId="20" r:id="rId20"/>
+    <sheet name="JED - Obhor" sheetId="24" r:id="rId13"/>
+    <sheet name="DMM - Al Faisaliyah" sheetId="2" r:id="rId14"/>
+    <sheet name="DMM - Al Jalawiah" sheetId="18" r:id="rId15"/>
+    <sheet name="DMM - Al Nada" sheetId="23" r:id="rId16"/>
+    <sheet name="ALQ - Buraidah" sheetId="16" r:id="rId17"/>
+    <sheet name="ALQ - Unaizah" sheetId="17" r:id="rId18"/>
+    <sheet name="Al Ahsaa" sheetId="19" r:id="rId19"/>
+    <sheet name="AlUla" sheetId="21" r:id="rId20"/>
+    <sheet name="Tabuk" sheetId="20" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">REPORT!$B$1:$B$363</definedName>
@@ -83,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="212">
   <si>
     <t>REPORT DATE:</t>
   </si>
@@ -722,6 +723,9 @@
   </si>
   <si>
     <t>Wyssal Ben Dhieb</t>
+  </si>
+  <si>
+    <t>JED - Obhor</t>
   </si>
 </sst>
 </file>
@@ -1761,7 +1765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
@@ -1796,7 +1800,7 @@
         <v>154</v>
       </c>
       <c r="D3" s="89">
-        <f ca="1">SUM(C7:C24)</f>
+        <f ca="1">SUM(C7:C25)</f>
         <v>0</v>
       </c>
     </row>
@@ -1840,7 +1844,7 @@
         <v>86</v>
       </c>
       <c r="B7" s="37">
-        <f t="shared" ref="B7:B24" ca="1" si="0">IFERROR(COUNTIFS(INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&gt;=" &amp; $B$3-7, INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&lt;=" &amp; $B$3),0)</f>
+        <f t="shared" ref="B7:B25" ca="1" si="0">IFERROR(COUNTIFS(INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&gt;=" &amp; $B$3-7, INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&lt;=" &amp; $B$3),0)</f>
         <v>0</v>
       </c>
       <c r="C7" s="36" cm="1">
@@ -2050,8 +2054,8 @@
       <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="31" t="s">
-        <v>57</v>
+      <c r="A17" s="57" t="s">
+        <v>211</v>
       </c>
       <c r="B17" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2062,14 +2066,14 @@
         <v>0</v>
       </c>
       <c r="D17" s="36">
-        <f ca="1">C17+86</f>
-        <v>86</v>
+        <f ca="1">C17+0</f>
+        <v>0</v>
       </c>
       <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="57" t="s">
-        <v>88</v>
+      <c r="A18" s="31" t="s">
+        <v>57</v>
       </c>
       <c r="B18" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2080,14 +2084,14 @@
         <v>0</v>
       </c>
       <c r="D18" s="36">
-        <f ca="1">C18+38</f>
-        <v>38</v>
+        <f ca="1">C18+86</f>
+        <v>86</v>
       </c>
       <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="57" t="s">
-        <v>208</v>
+        <v>88</v>
       </c>
       <c r="B19" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2098,14 +2102,14 @@
         <v>0</v>
       </c>
       <c r="D19" s="36">
-        <f ca="1">C19+0</f>
-        <v>0</v>
+        <f ca="1">C19+38</f>
+        <v>38</v>
       </c>
       <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="58" t="s">
-        <v>90</v>
+      <c r="A20" s="57" t="s">
+        <v>208</v>
       </c>
       <c r="B20" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2116,14 +2120,14 @@
         <v>0</v>
       </c>
       <c r="D20" s="36">
-        <f ca="1">C20+29</f>
-        <v>29</v>
+        <f ca="1">C20+0</f>
+        <v>0</v>
       </c>
       <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="31" t="s">
-        <v>89</v>
+      <c r="A21" s="58" t="s">
+        <v>90</v>
       </c>
       <c r="B21" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2134,14 +2138,14 @@
         <v>0</v>
       </c>
       <c r="D21" s="36">
-        <f ca="1">C21+20</f>
-        <v>20</v>
+        <f ca="1">C21+29</f>
+        <v>29</v>
       </c>
       <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="57" t="s">
-        <v>87</v>
+      <c r="A22" s="31" t="s">
+        <v>89</v>
       </c>
       <c r="B22" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2152,14 +2156,14 @@
         <v>0</v>
       </c>
       <c r="D22" s="36">
-        <f ca="1">C22+48</f>
-        <v>48</v>
+        <f ca="1">C22+20</f>
+        <v>20</v>
       </c>
       <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="31" t="s">
-        <v>139</v>
+      <c r="A23" s="57" t="s">
+        <v>87</v>
       </c>
       <c r="B23" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2170,14 +2174,14 @@
         <v>0</v>
       </c>
       <c r="D23" s="36">
-        <f ca="1">C23+16</f>
-        <v>16</v>
+        <f ca="1">C23+48</f>
+        <v>48</v>
       </c>
       <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="57" t="s">
-        <v>140</v>
+      <c r="A24" s="31" t="s">
+        <v>139</v>
       </c>
       <c r="B24" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2188,16 +2192,27 @@
         <v>0</v>
       </c>
       <c r="D24" s="36">
-        <f ca="1">C24+11</f>
+        <f ca="1">C24+16</f>
+        <v>16</v>
+      </c>
+      <c r="E24" s="17"/>
+    </row>
+    <row r="25" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="37">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C25" s="36" cm="1">
+        <f t="array" aca="1" ref="C25" ca="1">INDIRECT("'" &amp; A25 &amp; "'!D3")</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="36">
+        <f ca="1">C25+11</f>
         <v>11</v>
       </c>
-      <c r="E24" s="17"/>
-    </row>
-    <row r="25" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
       <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -2522,11 +2537,12 @@
       <c r="D71" s="35"/>
       <c r="E71" s="17"/>
     </row>
-    <row r="72" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="35"/>
       <c r="D72" s="35"/>
+      <c r="E72" s="17"/>
     </row>
     <row r="73" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="17"/>
@@ -2545,6 +2561,12 @@
       <c r="B75" s="17"/>
       <c r="C75" s="35"/>
       <c r="D75" s="35"/>
+    </row>
+    <row r="76" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A76" s="17"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -7327,6 +7349,1555 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{682DEFF1-D972-214F-8BEA-A9100E335D9D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q188"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="60.33203125" style="95" customWidth="1"/>
+    <col min="2" max="2" width="60.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="64.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="66.1640625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="86.33203125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="100" customWidth="1"/>
+    <col min="7" max="7" width="5.33203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="33">
+        <v>46113</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <f>COUNTA(E7:E13508)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:17" ht="47.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="96"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+    </row>
+    <row r="8" spans="1:17" s="101" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="96"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="100"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="100"/>
+      <c r="M8" s="100"/>
+      <c r="N8" s="100"/>
+      <c r="O8" s="100"/>
+      <c r="P8" s="100"/>
+      <c r="Q8" s="100"/>
+    </row>
+    <row r="9" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="96"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+    </row>
+    <row r="10" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="96"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+    </row>
+    <row r="11" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="96"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="M11" s="101"/>
+      <c r="N11" s="101"/>
+      <c r="O11" s="101"/>
+      <c r="P11" s="101"/>
+      <c r="Q11" s="101"/>
+    </row>
+    <row r="12" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="96"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+    </row>
+    <row r="13" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="96"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+    </row>
+    <row r="14" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="96"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+    </row>
+    <row r="15" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="96"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+    </row>
+    <row r="16" spans="1:17" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="102"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="100"/>
+    </row>
+    <row r="17" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="102"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="100"/>
+    </row>
+    <row r="18" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="102"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="100"/>
+    </row>
+    <row r="19" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="102"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="100"/>
+    </row>
+    <row r="20" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="102"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="100"/>
+    </row>
+    <row r="21" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="102"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="100"/>
+    </row>
+    <row r="22" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="102"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="100"/>
+    </row>
+    <row r="23" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="102"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="100"/>
+    </row>
+    <row r="24" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="102"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="100"/>
+    </row>
+    <row r="25" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="102"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="100"/>
+    </row>
+    <row r="26" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="102"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="100"/>
+    </row>
+    <row r="27" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="102"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="100"/>
+    </row>
+    <row r="28" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="102"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="100"/>
+    </row>
+    <row r="29" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="102"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="100"/>
+    </row>
+    <row r="30" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="102"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="100"/>
+    </row>
+    <row r="31" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="102"/>
+      <c r="B31" s="103"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="100"/>
+    </row>
+    <row r="32" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="102"/>
+      <c r="B32" s="103"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="100"/>
+    </row>
+    <row r="33" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="102"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="100"/>
+    </row>
+    <row r="34" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="102"/>
+      <c r="B34" s="103"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="100"/>
+    </row>
+    <row r="35" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="102"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="100"/>
+    </row>
+    <row r="36" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="102"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="104"/>
+      <c r="E36" s="104"/>
+      <c r="F36" s="100"/>
+    </row>
+    <row r="37" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="102"/>
+      <c r="B37" s="103"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="100"/>
+    </row>
+    <row r="38" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="102"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="100"/>
+    </row>
+    <row r="39" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="102"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="100"/>
+    </row>
+    <row r="40" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="102"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="108"/>
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="100"/>
+    </row>
+    <row r="41" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="102"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="107"/>
+      <c r="D41" s="104"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="100"/>
+    </row>
+    <row r="42" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="102"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="108"/>
+      <c r="D42" s="104"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="100"/>
+    </row>
+    <row r="43" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="102"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="100"/>
+    </row>
+    <row r="44" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="102"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="108"/>
+      <c r="D44" s="104"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="100"/>
+    </row>
+    <row r="45" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="102"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="108"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="100"/>
+    </row>
+    <row r="46" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="102"/>
+      <c r="B46" s="103"/>
+      <c r="C46" s="108"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="100"/>
+    </row>
+    <row r="47" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="102"/>
+      <c r="B47" s="103"/>
+      <c r="C47" s="108"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="100"/>
+    </row>
+    <row r="48" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="102"/>
+      <c r="B48" s="103"/>
+      <c r="C48" s="108"/>
+      <c r="D48" s="104"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="100"/>
+    </row>
+    <row r="49" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="102"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="108"/>
+      <c r="D49" s="104"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="100"/>
+    </row>
+    <row r="50" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="102"/>
+      <c r="B50" s="103"/>
+      <c r="C50" s="108"/>
+      <c r="D50" s="104"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="100"/>
+    </row>
+    <row r="51" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="102"/>
+      <c r="B51" s="103"/>
+      <c r="C51" s="108"/>
+      <c r="D51" s="104"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="100"/>
+    </row>
+    <row r="52" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="102"/>
+      <c r="B52" s="103"/>
+      <c r="C52" s="108"/>
+      <c r="D52" s="104"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="100"/>
+    </row>
+    <row r="53" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="102"/>
+      <c r="B53" s="103"/>
+      <c r="C53" s="108"/>
+      <c r="D53" s="104"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="100"/>
+    </row>
+    <row r="54" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="102"/>
+      <c r="B54" s="103"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="104"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="100"/>
+    </row>
+    <row r="55" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="102"/>
+      <c r="B55" s="103"/>
+      <c r="C55" s="108"/>
+      <c r="D55" s="104"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="100"/>
+    </row>
+    <row r="56" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="102"/>
+      <c r="B56" s="103"/>
+      <c r="C56" s="108"/>
+      <c r="D56" s="104"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="100"/>
+    </row>
+    <row r="57" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="102"/>
+      <c r="B57" s="103"/>
+      <c r="C57" s="108"/>
+      <c r="D57" s="104"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="100"/>
+    </row>
+    <row r="58" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="102"/>
+      <c r="B58" s="103"/>
+      <c r="C58" s="108"/>
+      <c r="D58" s="104"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="100"/>
+    </row>
+    <row r="59" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="102"/>
+      <c r="B59" s="103"/>
+      <c r="C59" s="108"/>
+      <c r="D59" s="104"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="100"/>
+    </row>
+    <row r="60" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="102"/>
+      <c r="B60" s="103"/>
+      <c r="C60" s="108"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="100"/>
+    </row>
+    <row r="61" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="102"/>
+      <c r="B61" s="103"/>
+      <c r="C61" s="108"/>
+      <c r="D61" s="104"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="100"/>
+    </row>
+    <row r="62" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="102"/>
+      <c r="B62" s="103"/>
+      <c r="C62" s="108"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="100"/>
+    </row>
+    <row r="63" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="102"/>
+      <c r="B63" s="103"/>
+      <c r="C63" s="108"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="100"/>
+    </row>
+    <row r="64" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="102"/>
+      <c r="B64" s="103"/>
+      <c r="C64" s="108"/>
+      <c r="D64" s="104"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="100"/>
+    </row>
+    <row r="65" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="102"/>
+      <c r="B65" s="103"/>
+      <c r="C65" s="108"/>
+      <c r="D65" s="104"/>
+      <c r="E65" s="104"/>
+      <c r="F65" s="100"/>
+    </row>
+    <row r="66" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="96"/>
+      <c r="B66" s="97"/>
+      <c r="C66" s="98"/>
+      <c r="D66" s="99"/>
+      <c r="E66" s="99"/>
+      <c r="F66" s="100"/>
+    </row>
+    <row r="67" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="96"/>
+      <c r="B67" s="97"/>
+      <c r="C67" s="98"/>
+      <c r="D67" s="99"/>
+      <c r="E67" s="99"/>
+      <c r="F67" s="100"/>
+    </row>
+    <row r="68" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="96"/>
+      <c r="B68" s="97"/>
+      <c r="C68" s="98"/>
+      <c r="D68" s="99"/>
+      <c r="E68" s="99"/>
+      <c r="F68" s="100"/>
+    </row>
+    <row r="69" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="96"/>
+      <c r="B69" s="97"/>
+      <c r="C69" s="98"/>
+      <c r="D69" s="99"/>
+      <c r="E69" s="99"/>
+      <c r="F69" s="100"/>
+    </row>
+    <row r="70" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="96"/>
+      <c r="B70" s="97"/>
+      <c r="C70" s="98"/>
+      <c r="D70" s="99"/>
+      <c r="E70" s="99"/>
+      <c r="F70" s="100"/>
+    </row>
+    <row r="71" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="96"/>
+      <c r="B71" s="97"/>
+      <c r="C71" s="98"/>
+      <c r="D71" s="99"/>
+      <c r="E71" s="99"/>
+      <c r="F71" s="100"/>
+    </row>
+    <row r="72" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="96"/>
+      <c r="B72" s="97"/>
+      <c r="C72" s="98"/>
+      <c r="D72" s="99"/>
+      <c r="E72" s="99"/>
+      <c r="F72" s="100"/>
+    </row>
+    <row r="73" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="96"/>
+      <c r="B73" s="97"/>
+      <c r="C73" s="98"/>
+      <c r="D73" s="99"/>
+      <c r="E73" s="99"/>
+      <c r="F73" s="100"/>
+    </row>
+    <row r="74" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="96"/>
+      <c r="B74" s="97"/>
+      <c r="C74" s="98"/>
+      <c r="D74" s="99"/>
+      <c r="E74" s="99"/>
+      <c r="F74" s="100"/>
+    </row>
+    <row r="75" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="102"/>
+      <c r="B75" s="103"/>
+      <c r="C75" s="98"/>
+      <c r="D75" s="99"/>
+      <c r="E75" s="99"/>
+      <c r="F75" s="100"/>
+    </row>
+    <row r="76" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="102"/>
+      <c r="B76" s="103"/>
+      <c r="C76" s="98"/>
+      <c r="D76" s="99"/>
+      <c r="E76" s="99"/>
+      <c r="F76" s="100"/>
+    </row>
+    <row r="77" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="102"/>
+      <c r="B77" s="103"/>
+      <c r="C77" s="98"/>
+      <c r="D77" s="104"/>
+      <c r="E77" s="104"/>
+      <c r="F77" s="100"/>
+    </row>
+    <row r="78" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="102"/>
+      <c r="B78" s="103"/>
+      <c r="C78" s="98"/>
+      <c r="D78" s="104"/>
+      <c r="E78" s="104"/>
+      <c r="F78" s="100"/>
+    </row>
+    <row r="79" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="102"/>
+      <c r="B79" s="103"/>
+      <c r="C79" s="98"/>
+      <c r="D79" s="104"/>
+      <c r="E79" s="104"/>
+      <c r="F79" s="100"/>
+    </row>
+    <row r="80" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="102"/>
+      <c r="B80" s="103"/>
+      <c r="C80" s="98"/>
+      <c r="D80" s="104"/>
+      <c r="E80" s="104"/>
+      <c r="F80" s="100"/>
+    </row>
+    <row r="81" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="102"/>
+      <c r="B81" s="103"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="104"/>
+      <c r="E81" s="104"/>
+      <c r="F81" s="100"/>
+    </row>
+    <row r="82" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="102"/>
+      <c r="B82" s="103"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="104"/>
+      <c r="E82" s="104"/>
+      <c r="F82" s="100"/>
+    </row>
+    <row r="83" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="102"/>
+      <c r="B83" s="103"/>
+      <c r="C83" s="105"/>
+      <c r="D83" s="104"/>
+      <c r="E83" s="104"/>
+      <c r="F83" s="100"/>
+    </row>
+    <row r="84" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="102"/>
+      <c r="B84" s="103"/>
+      <c r="C84" s="98"/>
+      <c r="D84" s="104"/>
+      <c r="E84" s="104"/>
+      <c r="F84" s="100"/>
+    </row>
+    <row r="85" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="102"/>
+      <c r="B85" s="103"/>
+      <c r="C85" s="105"/>
+      <c r="D85" s="104"/>
+      <c r="E85" s="104"/>
+      <c r="F85" s="100"/>
+    </row>
+    <row r="86" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="102"/>
+      <c r="B86" s="103"/>
+      <c r="C86" s="105"/>
+      <c r="D86" s="104"/>
+      <c r="E86" s="104"/>
+      <c r="F86" s="100"/>
+    </row>
+    <row r="87" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="102"/>
+      <c r="B87" s="103"/>
+      <c r="C87" s="98"/>
+      <c r="D87" s="104"/>
+      <c r="E87" s="104"/>
+      <c r="F87" s="100"/>
+    </row>
+    <row r="88" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="102"/>
+      <c r="B88" s="103"/>
+      <c r="C88" s="98"/>
+      <c r="D88" s="104"/>
+      <c r="E88" s="104"/>
+      <c r="F88" s="100"/>
+    </row>
+    <row r="89" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="102"/>
+      <c r="B89" s="103"/>
+      <c r="C89" s="107"/>
+      <c r="D89" s="104"/>
+      <c r="E89" s="104"/>
+      <c r="F89" s="100"/>
+    </row>
+    <row r="90" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="102"/>
+      <c r="B90" s="103"/>
+      <c r="C90" s="98"/>
+      <c r="D90" s="104"/>
+      <c r="E90" s="104"/>
+      <c r="F90" s="100"/>
+    </row>
+    <row r="91" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="102"/>
+      <c r="B91" s="103"/>
+      <c r="C91" s="107"/>
+      <c r="D91" s="104"/>
+      <c r="E91" s="104"/>
+      <c r="F91" s="100"/>
+    </row>
+    <row r="92" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="102"/>
+      <c r="B92" s="103"/>
+      <c r="C92" s="105"/>
+      <c r="D92" s="104"/>
+      <c r="E92" s="104"/>
+      <c r="F92" s="100"/>
+    </row>
+    <row r="93" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="102"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="105"/>
+      <c r="D93" s="104"/>
+      <c r="E93" s="104"/>
+      <c r="F93" s="100"/>
+    </row>
+    <row r="94" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="102"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="105"/>
+      <c r="D94" s="104"/>
+      <c r="E94" s="104"/>
+      <c r="F94" s="100"/>
+    </row>
+    <row r="95" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="102"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="105"/>
+      <c r="D95" s="104"/>
+      <c r="E95" s="104"/>
+      <c r="F95" s="100"/>
+    </row>
+    <row r="96" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="102"/>
+      <c r="B96" s="103"/>
+      <c r="C96" s="105"/>
+      <c r="D96" s="104"/>
+      <c r="E96" s="104"/>
+      <c r="F96" s="100"/>
+    </row>
+    <row r="97" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="102"/>
+      <c r="B97" s="103"/>
+      <c r="C97" s="98"/>
+      <c r="D97" s="104"/>
+      <c r="E97" s="104"/>
+      <c r="F97" s="100"/>
+    </row>
+    <row r="98" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="102"/>
+      <c r="B98" s="103"/>
+      <c r="C98" s="98"/>
+      <c r="D98" s="104"/>
+      <c r="E98" s="104"/>
+      <c r="F98" s="100"/>
+    </row>
+    <row r="99" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="102"/>
+      <c r="B99" s="103"/>
+      <c r="C99" s="108"/>
+      <c r="D99" s="104"/>
+      <c r="E99" s="104"/>
+      <c r="F99" s="100"/>
+    </row>
+    <row r="100" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="102"/>
+      <c r="B100" s="103"/>
+      <c r="C100" s="107"/>
+      <c r="D100" s="104"/>
+      <c r="E100" s="104"/>
+      <c r="F100" s="100"/>
+    </row>
+    <row r="101" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="102"/>
+      <c r="B101" s="103"/>
+      <c r="C101" s="108"/>
+      <c r="D101" s="104"/>
+      <c r="E101" s="104"/>
+      <c r="F101" s="100"/>
+    </row>
+    <row r="102" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="102"/>
+      <c r="B102" s="103"/>
+      <c r="C102" s="108"/>
+      <c r="D102" s="104"/>
+      <c r="E102" s="104"/>
+      <c r="F102" s="100"/>
+    </row>
+    <row r="103" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="102"/>
+      <c r="B103" s="103"/>
+      <c r="C103" s="108"/>
+      <c r="D103" s="104"/>
+      <c r="E103" s="104"/>
+      <c r="F103" s="100"/>
+    </row>
+    <row r="104" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="102"/>
+      <c r="B104" s="103"/>
+      <c r="C104" s="108"/>
+      <c r="D104" s="104"/>
+      <c r="E104" s="104"/>
+      <c r="F104" s="100"/>
+    </row>
+    <row r="105" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="102"/>
+      <c r="B105" s="103"/>
+      <c r="C105" s="108"/>
+      <c r="D105" s="104"/>
+      <c r="E105" s="104"/>
+      <c r="F105" s="100"/>
+    </row>
+    <row r="106" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A106" s="102"/>
+      <c r="B106" s="103"/>
+      <c r="C106" s="108"/>
+      <c r="D106" s="104"/>
+      <c r="E106" s="104"/>
+      <c r="F106" s="100"/>
+    </row>
+    <row r="107" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="102"/>
+      <c r="B107" s="103"/>
+      <c r="C107" s="108"/>
+      <c r="D107" s="104"/>
+      <c r="E107" s="104"/>
+      <c r="F107" s="100"/>
+    </row>
+    <row r="108" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A108" s="102"/>
+      <c r="B108" s="103"/>
+      <c r="C108" s="108"/>
+      <c r="D108" s="104"/>
+      <c r="E108" s="104"/>
+      <c r="F108" s="100"/>
+    </row>
+    <row r="109" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A109" s="102"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="108"/>
+      <c r="D109" s="104"/>
+      <c r="E109" s="104"/>
+      <c r="F109" s="100"/>
+    </row>
+    <row r="110" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A110" s="102"/>
+      <c r="B110" s="103"/>
+      <c r="C110" s="108"/>
+      <c r="D110" s="104"/>
+      <c r="E110" s="104"/>
+      <c r="F110" s="100"/>
+    </row>
+    <row r="111" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A111" s="102"/>
+      <c r="B111" s="103"/>
+      <c r="C111" s="108"/>
+      <c r="D111" s="104"/>
+      <c r="E111" s="104"/>
+      <c r="F111" s="100"/>
+    </row>
+    <row r="112" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A112" s="102"/>
+      <c r="B112" s="103"/>
+      <c r="C112" s="108"/>
+      <c r="D112" s="104"/>
+      <c r="E112" s="104"/>
+      <c r="F112" s="100"/>
+    </row>
+    <row r="113" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A113" s="102"/>
+      <c r="B113" s="103"/>
+      <c r="C113" s="108"/>
+      <c r="D113" s="104"/>
+      <c r="E113" s="104"/>
+      <c r="F113" s="100"/>
+    </row>
+    <row r="114" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="102"/>
+      <c r="B114" s="103"/>
+      <c r="C114" s="108"/>
+      <c r="D114" s="104"/>
+      <c r="E114" s="104"/>
+      <c r="F114" s="100"/>
+    </row>
+    <row r="115" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A115" s="102"/>
+      <c r="B115" s="103"/>
+      <c r="C115" s="108"/>
+      <c r="D115" s="104"/>
+      <c r="E115" s="104"/>
+      <c r="F115" s="100"/>
+    </row>
+    <row r="116" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A116" s="102"/>
+      <c r="B116" s="103"/>
+      <c r="C116" s="108"/>
+      <c r="D116" s="104"/>
+      <c r="E116" s="104"/>
+      <c r="F116" s="100"/>
+    </row>
+    <row r="117" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A117" s="102"/>
+      <c r="B117" s="103"/>
+      <c r="C117" s="108"/>
+      <c r="D117" s="104"/>
+      <c r="E117" s="104"/>
+      <c r="F117" s="100"/>
+    </row>
+    <row r="118" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A118" s="102"/>
+      <c r="B118" s="103"/>
+      <c r="C118" s="108"/>
+      <c r="D118" s="104"/>
+      <c r="E118" s="104"/>
+      <c r="F118" s="100"/>
+    </row>
+    <row r="119" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A119" s="102"/>
+      <c r="B119" s="103"/>
+      <c r="C119" s="108"/>
+      <c r="D119" s="104"/>
+      <c r="E119" s="104"/>
+      <c r="F119" s="100"/>
+    </row>
+    <row r="120" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A120" s="102"/>
+      <c r="B120" s="103"/>
+      <c r="C120" s="108"/>
+      <c r="D120" s="104"/>
+      <c r="E120" s="104"/>
+      <c r="F120" s="100"/>
+    </row>
+    <row r="121" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A121" s="102"/>
+      <c r="B121" s="103"/>
+      <c r="C121" s="108"/>
+      <c r="D121" s="104"/>
+      <c r="E121" s="104"/>
+      <c r="F121" s="100"/>
+    </row>
+    <row r="122" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A122" s="102"/>
+      <c r="B122" s="103"/>
+      <c r="C122" s="108"/>
+      <c r="D122" s="104"/>
+      <c r="E122" s="104"/>
+      <c r="F122" s="100"/>
+    </row>
+    <row r="123" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A123" s="102"/>
+      <c r="B123" s="103"/>
+      <c r="C123" s="108"/>
+      <c r="D123" s="104"/>
+      <c r="E123" s="104"/>
+      <c r="F123" s="100"/>
+    </row>
+    <row r="124" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A124" s="102"/>
+      <c r="B124" s="103"/>
+      <c r="C124" s="108"/>
+      <c r="D124" s="104"/>
+      <c r="E124" s="104"/>
+      <c r="F124" s="100"/>
+    </row>
+    <row r="125" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A125" s="96"/>
+      <c r="B125" s="97"/>
+      <c r="C125" s="98"/>
+      <c r="D125" s="99"/>
+      <c r="E125" s="99"/>
+      <c r="F125" s="100"/>
+    </row>
+    <row r="126" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A126" s="96"/>
+      <c r="B126" s="97"/>
+      <c r="C126" s="98"/>
+      <c r="D126" s="99"/>
+      <c r="E126" s="99"/>
+      <c r="F126" s="100"/>
+    </row>
+    <row r="127" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A127" s="96"/>
+      <c r="B127" s="97"/>
+      <c r="C127" s="98"/>
+      <c r="D127" s="99"/>
+      <c r="E127" s="99"/>
+      <c r="F127" s="100"/>
+    </row>
+    <row r="128" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A128" s="96"/>
+      <c r="B128" s="97"/>
+      <c r="C128" s="98"/>
+      <c r="D128" s="99"/>
+      <c r="E128" s="99"/>
+      <c r="F128" s="100"/>
+    </row>
+    <row r="129" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A129" s="96"/>
+      <c r="B129" s="97"/>
+      <c r="C129" s="98"/>
+      <c r="D129" s="99"/>
+      <c r="E129" s="99"/>
+      <c r="F129" s="100"/>
+    </row>
+    <row r="130" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="96"/>
+      <c r="B130" s="97"/>
+      <c r="C130" s="98"/>
+      <c r="D130" s="99"/>
+      <c r="E130" s="99"/>
+      <c r="F130" s="100"/>
+    </row>
+    <row r="131" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A131" s="96"/>
+      <c r="B131" s="97"/>
+      <c r="C131" s="98"/>
+      <c r="D131" s="99"/>
+      <c r="E131" s="99"/>
+      <c r="F131" s="100"/>
+    </row>
+    <row r="132" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A132" s="96"/>
+      <c r="B132" s="97"/>
+      <c r="C132" s="98"/>
+      <c r="D132" s="99"/>
+      <c r="E132" s="99"/>
+      <c r="F132" s="100"/>
+    </row>
+    <row r="133" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A133" s="96"/>
+      <c r="B133" s="97"/>
+      <c r="C133" s="98"/>
+      <c r="D133" s="99"/>
+      <c r="E133" s="99"/>
+      <c r="F133" s="100"/>
+    </row>
+    <row r="134" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A134" s="102"/>
+      <c r="B134" s="103"/>
+      <c r="C134" s="98"/>
+      <c r="D134" s="99"/>
+      <c r="E134" s="99"/>
+      <c r="F134" s="100"/>
+    </row>
+    <row r="135" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A135" s="102"/>
+      <c r="B135" s="103"/>
+      <c r="C135" s="98"/>
+      <c r="D135" s="99"/>
+      <c r="E135" s="99"/>
+      <c r="F135" s="100"/>
+    </row>
+    <row r="136" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A136" s="102"/>
+      <c r="B136" s="103"/>
+      <c r="C136" s="98"/>
+      <c r="D136" s="104"/>
+      <c r="E136" s="104"/>
+      <c r="F136" s="100"/>
+    </row>
+    <row r="137" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A137" s="102"/>
+      <c r="B137" s="103"/>
+      <c r="C137" s="98"/>
+      <c r="D137" s="104"/>
+      <c r="E137" s="104"/>
+      <c r="F137" s="100"/>
+    </row>
+    <row r="138" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A138" s="102"/>
+      <c r="B138" s="103"/>
+      <c r="C138" s="98"/>
+      <c r="D138" s="104"/>
+      <c r="E138" s="104"/>
+      <c r="F138" s="100"/>
+    </row>
+    <row r="139" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A139" s="102"/>
+      <c r="B139" s="103"/>
+      <c r="C139" s="98"/>
+      <c r="D139" s="104"/>
+      <c r="E139" s="104"/>
+      <c r="F139" s="100"/>
+    </row>
+    <row r="140" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A140" s="102"/>
+      <c r="B140" s="103"/>
+      <c r="C140" s="98"/>
+      <c r="D140" s="104"/>
+      <c r="E140" s="104"/>
+      <c r="F140" s="100"/>
+    </row>
+    <row r="141" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A141" s="102"/>
+      <c r="B141" s="103"/>
+      <c r="C141" s="98"/>
+      <c r="D141" s="104"/>
+      <c r="E141" s="104"/>
+      <c r="F141" s="100"/>
+    </row>
+    <row r="142" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A142" s="102"/>
+      <c r="B142" s="103"/>
+      <c r="C142" s="105"/>
+      <c r="D142" s="104"/>
+      <c r="E142" s="104"/>
+      <c r="F142" s="100"/>
+    </row>
+    <row r="143" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A143" s="102"/>
+      <c r="B143" s="103"/>
+      <c r="C143" s="98"/>
+      <c r="D143" s="104"/>
+      <c r="E143" s="104"/>
+      <c r="F143" s="100"/>
+    </row>
+    <row r="144" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A144" s="102"/>
+      <c r="B144" s="103"/>
+      <c r="C144" s="105"/>
+      <c r="D144" s="104"/>
+      <c r="E144" s="104"/>
+      <c r="F144" s="100"/>
+    </row>
+    <row r="145" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A145" s="102"/>
+      <c r="B145" s="103"/>
+      <c r="C145" s="105"/>
+      <c r="D145" s="104"/>
+      <c r="E145" s="104"/>
+      <c r="F145" s="100"/>
+    </row>
+    <row r="146" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A146" s="102"/>
+      <c r="B146" s="103"/>
+      <c r="C146" s="98"/>
+      <c r="D146" s="104"/>
+      <c r="E146" s="104"/>
+      <c r="F146" s="100"/>
+    </row>
+    <row r="147" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A147" s="102"/>
+      <c r="B147" s="103"/>
+      <c r="C147" s="98"/>
+      <c r="D147" s="104"/>
+      <c r="E147" s="104"/>
+      <c r="F147" s="100"/>
+    </row>
+    <row r="148" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A148" s="102"/>
+      <c r="B148" s="103"/>
+      <c r="C148" s="107"/>
+      <c r="D148" s="104"/>
+      <c r="E148" s="104"/>
+      <c r="F148" s="100"/>
+    </row>
+    <row r="149" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A149" s="102"/>
+      <c r="B149" s="103"/>
+      <c r="C149" s="98"/>
+      <c r="D149" s="104"/>
+      <c r="E149" s="104"/>
+      <c r="F149" s="100"/>
+    </row>
+    <row r="150" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A150" s="102"/>
+      <c r="B150" s="103"/>
+      <c r="C150" s="107"/>
+      <c r="D150" s="104"/>
+      <c r="E150" s="104"/>
+      <c r="F150" s="100"/>
+    </row>
+    <row r="151" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A151" s="102"/>
+      <c r="B151" s="103"/>
+      <c r="C151" s="105"/>
+      <c r="D151" s="104"/>
+      <c r="E151" s="104"/>
+      <c r="F151" s="100"/>
+    </row>
+    <row r="152" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A152" s="102"/>
+      <c r="B152" s="103"/>
+      <c r="C152" s="105"/>
+      <c r="D152" s="104"/>
+      <c r="E152" s="104"/>
+      <c r="F152" s="100"/>
+    </row>
+    <row r="153" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A153" s="102"/>
+      <c r="B153" s="103"/>
+      <c r="C153" s="105"/>
+      <c r="D153" s="104"/>
+      <c r="E153" s="104"/>
+      <c r="F153" s="100"/>
+    </row>
+    <row r="154" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A154" s="102"/>
+      <c r="B154" s="103"/>
+      <c r="C154" s="105"/>
+      <c r="D154" s="104"/>
+      <c r="E154" s="104"/>
+      <c r="F154" s="100"/>
+    </row>
+    <row r="155" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A155" s="102"/>
+      <c r="B155" s="103"/>
+      <c r="C155" s="105"/>
+      <c r="D155" s="104"/>
+      <c r="E155" s="104"/>
+      <c r="F155" s="100"/>
+    </row>
+    <row r="156" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A156" s="102"/>
+      <c r="B156" s="103"/>
+      <c r="C156" s="98"/>
+      <c r="D156" s="104"/>
+      <c r="E156" s="104"/>
+      <c r="F156" s="100"/>
+    </row>
+    <row r="157" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A157" s="102"/>
+      <c r="B157" s="103"/>
+      <c r="C157" s="98"/>
+      <c r="D157" s="104"/>
+      <c r="E157" s="104"/>
+      <c r="F157" s="100"/>
+    </row>
+    <row r="158" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A158" s="102"/>
+      <c r="B158" s="103"/>
+      <c r="C158" s="108"/>
+      <c r="D158" s="104"/>
+      <c r="E158" s="104"/>
+      <c r="F158" s="100"/>
+    </row>
+    <row r="159" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A159" s="102"/>
+      <c r="B159" s="103"/>
+      <c r="C159" s="107"/>
+      <c r="D159" s="104"/>
+      <c r="E159" s="104"/>
+      <c r="F159" s="100"/>
+    </row>
+    <row r="160" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A160" s="102"/>
+      <c r="B160" s="103"/>
+      <c r="C160" s="108"/>
+      <c r="D160" s="104"/>
+      <c r="E160" s="104"/>
+      <c r="F160" s="100"/>
+    </row>
+    <row r="161" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A161" s="102"/>
+      <c r="B161" s="103"/>
+      <c r="C161" s="108"/>
+      <c r="D161" s="104"/>
+      <c r="E161" s="104"/>
+      <c r="F161" s="100"/>
+    </row>
+    <row r="162" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A162" s="102"/>
+      <c r="B162" s="103"/>
+      <c r="C162" s="108"/>
+      <c r="D162" s="104"/>
+      <c r="E162" s="104"/>
+      <c r="F162" s="100"/>
+    </row>
+    <row r="163" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A163" s="102"/>
+      <c r="B163" s="103"/>
+      <c r="C163" s="108"/>
+      <c r="D163" s="104"/>
+      <c r="E163" s="104"/>
+      <c r="F163" s="100"/>
+    </row>
+    <row r="164" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A164" s="102"/>
+      <c r="B164" s="103"/>
+      <c r="C164" s="108"/>
+      <c r="D164" s="104"/>
+      <c r="E164" s="104"/>
+      <c r="F164" s="100"/>
+    </row>
+    <row r="165" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A165" s="102"/>
+      <c r="B165" s="103"/>
+      <c r="C165" s="108"/>
+      <c r="D165" s="104"/>
+      <c r="E165" s="104"/>
+      <c r="F165" s="100"/>
+    </row>
+    <row r="166" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A166" s="102"/>
+      <c r="B166" s="103"/>
+      <c r="C166" s="108"/>
+      <c r="D166" s="104"/>
+      <c r="E166" s="104"/>
+      <c r="F166" s="100"/>
+    </row>
+    <row r="167" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A167" s="102"/>
+      <c r="B167" s="103"/>
+      <c r="C167" s="108"/>
+      <c r="D167" s="104"/>
+      <c r="E167" s="104"/>
+      <c r="F167" s="100"/>
+    </row>
+    <row r="168" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A168" s="102"/>
+      <c r="B168" s="103"/>
+      <c r="C168" s="108"/>
+      <c r="D168" s="104"/>
+      <c r="E168" s="104"/>
+      <c r="F168" s="100"/>
+    </row>
+    <row r="169" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A169" s="102"/>
+      <c r="B169" s="103"/>
+      <c r="C169" s="108"/>
+      <c r="D169" s="104"/>
+      <c r="E169" s="104"/>
+      <c r="F169" s="100"/>
+    </row>
+    <row r="170" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A170" s="102"/>
+      <c r="B170" s="103"/>
+      <c r="C170" s="108"/>
+      <c r="D170" s="104"/>
+      <c r="E170" s="104"/>
+      <c r="F170" s="100"/>
+    </row>
+    <row r="171" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A171" s="102"/>
+      <c r="B171" s="103"/>
+      <c r="C171" s="108"/>
+      <c r="D171" s="104"/>
+      <c r="E171" s="104"/>
+      <c r="F171" s="100"/>
+    </row>
+    <row r="172" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A172" s="102"/>
+      <c r="B172" s="103"/>
+      <c r="C172" s="108"/>
+      <c r="D172" s="104"/>
+      <c r="E172" s="104"/>
+      <c r="F172" s="100"/>
+    </row>
+    <row r="173" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A173" s="102"/>
+      <c r="B173" s="103"/>
+      <c r="C173" s="108"/>
+      <c r="D173" s="104"/>
+      <c r="E173" s="104"/>
+      <c r="F173" s="100"/>
+    </row>
+    <row r="174" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A174" s="102"/>
+      <c r="B174" s="103"/>
+      <c r="C174" s="108"/>
+      <c r="D174" s="104"/>
+      <c r="E174" s="104"/>
+      <c r="F174" s="100"/>
+    </row>
+    <row r="175" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A175" s="102"/>
+      <c r="B175" s="103"/>
+      <c r="C175" s="108"/>
+      <c r="D175" s="104"/>
+      <c r="E175" s="104"/>
+      <c r="F175" s="100"/>
+    </row>
+    <row r="176" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A176" s="102"/>
+      <c r="B176" s="103"/>
+      <c r="C176" s="108"/>
+      <c r="D176" s="104"/>
+      <c r="E176" s="104"/>
+      <c r="F176" s="100"/>
+    </row>
+    <row r="177" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A177" s="102"/>
+      <c r="B177" s="103"/>
+      <c r="C177" s="108"/>
+      <c r="D177" s="104"/>
+      <c r="E177" s="104"/>
+      <c r="F177" s="100"/>
+    </row>
+    <row r="178" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A178" s="102"/>
+      <c r="B178" s="103"/>
+      <c r="C178" s="108"/>
+      <c r="D178" s="104"/>
+      <c r="E178" s="104"/>
+      <c r="F178" s="100"/>
+    </row>
+    <row r="179" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A179" s="102"/>
+      <c r="B179" s="103"/>
+      <c r="C179" s="108"/>
+      <c r="D179" s="104"/>
+      <c r="E179" s="104"/>
+      <c r="F179" s="100"/>
+    </row>
+    <row r="180" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A180" s="102"/>
+      <c r="B180" s="103"/>
+      <c r="C180" s="108"/>
+      <c r="D180" s="104"/>
+      <c r="E180" s="104"/>
+      <c r="F180" s="100"/>
+    </row>
+    <row r="181" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A181" s="102"/>
+      <c r="B181" s="103"/>
+      <c r="C181" s="108"/>
+      <c r="D181" s="104"/>
+      <c r="E181" s="104"/>
+      <c r="F181" s="100"/>
+    </row>
+    <row r="182" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A182" s="102"/>
+      <c r="B182" s="103"/>
+      <c r="C182" s="108"/>
+      <c r="D182" s="104"/>
+      <c r="E182" s="104"/>
+      <c r="F182" s="100"/>
+    </row>
+    <row r="183" spans="1:6" s="106" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A183" s="102"/>
+      <c r="B183" s="103"/>
+      <c r="C183" s="108"/>
+      <c r="D183" s="104"/>
+      <c r="E183" s="104"/>
+      <c r="F183" s="100"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D184" s="19"/>
+      <c r="E184" s="19"/>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D185" s="19"/>
+      <c r="E185" s="19"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D186" s="19"/>
+      <c r="E186" s="19"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D187" s="19"/>
+      <c r="E187" s="19"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D188" s="19"/>
+      <c r="E188" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;G</oddHeader>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8939,7 +10510,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AC22853-01AA-384A-A7A4-9366E90022A8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -10501,7 +12072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA88F251-751E-0A44-AE69-CD979CB2DC23}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -12063,7 +13634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FCE9103-D54E-4043-9BEC-BB5B051ED49E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -13625,7 +15196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E53EDB-6B4B-904B-BF10-8B5E1ECBAA4F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15187,7 +16758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E69952E-033E-D443-8839-6B5053F1DE97}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -16734,1568 +18305,6 @@
     <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D190" s="19"/>
       <c r="E190" s="19"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;G</oddHeader>
-  </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC255F8-7200-D84E-9D73-DDE699449625}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:Q191"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="60.33203125" style="95" customWidth="1"/>
-    <col min="2" max="2" width="60.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="64.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="66.1640625" style="18" customWidth="1"/>
-    <col min="5" max="5" width="86.33203125" style="18" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" style="100" customWidth="1"/>
-    <col min="7" max="7" width="5.33203125" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="33">
-        <v>46113</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6">
-        <f>COUNTA(E7:E13510)</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:17" ht="47.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="10"/>
-    </row>
-    <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="10"/>
-    </row>
-    <row r="7" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="96"/>
-      <c r="B7" s="97"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-    </row>
-    <row r="8" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="96"/>
-      <c r="B8" s="97"/>
-      <c r="C8" s="98"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-    </row>
-    <row r="9" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="96"/>
-      <c r="B9" s="97"/>
-      <c r="C9" s="98"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="101"/>
-      <c r="K9" s="101"/>
-      <c r="M9" s="101"/>
-      <c r="N9" s="101"/>
-      <c r="O9" s="101"/>
-      <c r="P9" s="101"/>
-      <c r="Q9" s="101"/>
-    </row>
-    <row r="10" spans="1:17" s="101" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="96"/>
-      <c r="B10" s="97"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="100"/>
-      <c r="M10" s="100"/>
-      <c r="N10" s="100"/>
-      <c r="O10" s="100"/>
-      <c r="P10" s="100"/>
-      <c r="Q10" s="100"/>
-    </row>
-    <row r="11" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="96"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-    </row>
-    <row r="12" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="96"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-    </row>
-    <row r="13" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="96"/>
-      <c r="B13" s="97"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-    </row>
-    <row r="14" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="96"/>
-      <c r="B14" s="97"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-    </row>
-    <row r="15" spans="1:17" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="96"/>
-      <c r="B15" s="97"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="100"/>
-    </row>
-    <row r="16" spans="1:17" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="102"/>
-      <c r="B16" s="103"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="99"/>
-      <c r="E16" s="99"/>
-      <c r="F16" s="100"/>
-    </row>
-    <row r="17" spans="1:6" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="102"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="100"/>
-    </row>
-    <row r="18" spans="1:6" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="102"/>
-      <c r="B18" s="103"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="100"/>
-    </row>
-    <row r="19" spans="1:6" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="102"/>
-      <c r="B19" s="103"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="100"/>
-    </row>
-    <row r="20" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="102"/>
-      <c r="B20" s="103"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="100"/>
-    </row>
-    <row r="21" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="102"/>
-      <c r="B21" s="103"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="100"/>
-    </row>
-    <row r="22" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="102"/>
-      <c r="B22" s="103"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="100"/>
-    </row>
-    <row r="23" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="102"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="100"/>
-    </row>
-    <row r="24" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="102"/>
-      <c r="B24" s="103"/>
-      <c r="C24" s="105"/>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="100"/>
-    </row>
-    <row r="25" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="102"/>
-      <c r="B25" s="103"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="100"/>
-    </row>
-    <row r="26" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="102"/>
-      <c r="B26" s="103"/>
-      <c r="C26" s="105"/>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="100"/>
-    </row>
-    <row r="27" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="102"/>
-      <c r="B27" s="103"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="100"/>
-    </row>
-    <row r="28" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="102"/>
-      <c r="B28" s="103"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="100"/>
-    </row>
-    <row r="29" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="102"/>
-      <c r="B29" s="103"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="104"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="100"/>
-    </row>
-    <row r="30" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="102"/>
-      <c r="B30" s="103"/>
-      <c r="C30" s="107"/>
-      <c r="D30" s="104"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="100"/>
-    </row>
-    <row r="31" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="102"/>
-      <c r="B31" s="103"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="104"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="100"/>
-    </row>
-    <row r="32" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="102"/>
-      <c r="B32" s="103"/>
-      <c r="C32" s="107"/>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="100"/>
-    </row>
-    <row r="33" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="102"/>
-      <c r="B33" s="103"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="104"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="100"/>
-    </row>
-    <row r="34" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="102"/>
-      <c r="B34" s="103"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="104"/>
-      <c r="E34" s="104"/>
-      <c r="F34" s="100"/>
-    </row>
-    <row r="35" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="102"/>
-      <c r="B35" s="103"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="104"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="100"/>
-    </row>
-    <row r="36" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="102"/>
-      <c r="B36" s="103"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="104"/>
-      <c r="E36" s="104"/>
-      <c r="F36" s="100"/>
-    </row>
-    <row r="37" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="102"/>
-      <c r="B37" s="103"/>
-      <c r="C37" s="105"/>
-      <c r="D37" s="104"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="100"/>
-    </row>
-    <row r="38" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="102"/>
-      <c r="B38" s="103"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="104"/>
-      <c r="E38" s="104"/>
-      <c r="F38" s="100"/>
-    </row>
-    <row r="39" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="102"/>
-      <c r="B39" s="103"/>
-      <c r="C39" s="98"/>
-      <c r="D39" s="104"/>
-      <c r="E39" s="104"/>
-      <c r="F39" s="100"/>
-    </row>
-    <row r="40" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="102"/>
-      <c r="B40" s="103"/>
-      <c r="C40" s="108"/>
-      <c r="D40" s="104"/>
-      <c r="E40" s="104"/>
-      <c r="F40" s="100"/>
-    </row>
-    <row r="41" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="102"/>
-      <c r="B41" s="103"/>
-      <c r="C41" s="107"/>
-      <c r="D41" s="104"/>
-      <c r="E41" s="104"/>
-      <c r="F41" s="100"/>
-    </row>
-    <row r="42" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="102"/>
-      <c r="B42" s="103"/>
-      <c r="C42" s="108"/>
-      <c r="D42" s="104"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="100"/>
-    </row>
-    <row r="43" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="102"/>
-      <c r="B43" s="103"/>
-      <c r="C43" s="108"/>
-      <c r="D43" s="104"/>
-      <c r="E43" s="104"/>
-      <c r="F43" s="100"/>
-    </row>
-    <row r="44" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="102"/>
-      <c r="B44" s="103"/>
-      <c r="C44" s="108"/>
-      <c r="D44" s="104"/>
-      <c r="E44" s="104"/>
-      <c r="F44" s="100"/>
-    </row>
-    <row r="45" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="102"/>
-      <c r="B45" s="103"/>
-      <c r="C45" s="108"/>
-      <c r="D45" s="104"/>
-      <c r="E45" s="104"/>
-      <c r="F45" s="100"/>
-    </row>
-    <row r="46" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="102"/>
-      <c r="B46" s="103"/>
-      <c r="C46" s="108"/>
-      <c r="D46" s="104"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="100"/>
-    </row>
-    <row r="47" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="102"/>
-      <c r="B47" s="103"/>
-      <c r="C47" s="108"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="100"/>
-    </row>
-    <row r="48" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="102"/>
-      <c r="B48" s="103"/>
-      <c r="C48" s="108"/>
-      <c r="D48" s="104"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="100"/>
-    </row>
-    <row r="49" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="102"/>
-      <c r="B49" s="103"/>
-      <c r="C49" s="108"/>
-      <c r="D49" s="104"/>
-      <c r="E49" s="104"/>
-      <c r="F49" s="100"/>
-    </row>
-    <row r="50" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="102"/>
-      <c r="B50" s="103"/>
-      <c r="C50" s="108"/>
-      <c r="D50" s="104"/>
-      <c r="E50" s="104"/>
-      <c r="F50" s="100"/>
-    </row>
-    <row r="51" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="102"/>
-      <c r="B51" s="103"/>
-      <c r="C51" s="108"/>
-      <c r="D51" s="104"/>
-      <c r="E51" s="104"/>
-      <c r="F51" s="100"/>
-    </row>
-    <row r="52" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="102"/>
-      <c r="B52" s="103"/>
-      <c r="C52" s="108"/>
-      <c r="D52" s="104"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="100"/>
-    </row>
-    <row r="53" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="102"/>
-      <c r="B53" s="103"/>
-      <c r="C53" s="108"/>
-      <c r="D53" s="104"/>
-      <c r="E53" s="104"/>
-      <c r="F53" s="100"/>
-    </row>
-    <row r="54" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="102"/>
-      <c r="B54" s="103"/>
-      <c r="C54" s="108"/>
-      <c r="D54" s="104"/>
-      <c r="E54" s="104"/>
-      <c r="F54" s="100"/>
-    </row>
-    <row r="55" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="102"/>
-      <c r="B55" s="103"/>
-      <c r="C55" s="108"/>
-      <c r="D55" s="104"/>
-      <c r="E55" s="104"/>
-      <c r="F55" s="100"/>
-    </row>
-    <row r="56" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="102"/>
-      <c r="B56" s="103"/>
-      <c r="C56" s="108"/>
-      <c r="D56" s="104"/>
-      <c r="E56" s="104"/>
-      <c r="F56" s="100"/>
-    </row>
-    <row r="57" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="102"/>
-      <c r="B57" s="103"/>
-      <c r="C57" s="108"/>
-      <c r="D57" s="104"/>
-      <c r="E57" s="104"/>
-      <c r="F57" s="100"/>
-    </row>
-    <row r="58" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="102"/>
-      <c r="B58" s="103"/>
-      <c r="C58" s="108"/>
-      <c r="D58" s="104"/>
-      <c r="E58" s="104"/>
-      <c r="F58" s="100"/>
-    </row>
-    <row r="59" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="102"/>
-      <c r="B59" s="103"/>
-      <c r="C59" s="108"/>
-      <c r="D59" s="104"/>
-      <c r="E59" s="104"/>
-      <c r="F59" s="100"/>
-    </row>
-    <row r="60" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="102"/>
-      <c r="B60" s="103"/>
-      <c r="C60" s="108"/>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="100"/>
-    </row>
-    <row r="61" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="102"/>
-      <c r="B61" s="103"/>
-      <c r="C61" s="108"/>
-      <c r="D61" s="104"/>
-      <c r="E61" s="104"/>
-      <c r="F61" s="100"/>
-    </row>
-    <row r="62" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="102"/>
-      <c r="B62" s="103"/>
-      <c r="C62" s="108"/>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="100"/>
-    </row>
-    <row r="63" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="102"/>
-      <c r="B63" s="103"/>
-      <c r="C63" s="108"/>
-      <c r="D63" s="104"/>
-      <c r="E63" s="104"/>
-      <c r="F63" s="100"/>
-    </row>
-    <row r="64" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="102"/>
-      <c r="B64" s="103"/>
-      <c r="C64" s="108"/>
-      <c r="D64" s="104"/>
-      <c r="E64" s="104"/>
-      <c r="F64" s="100"/>
-    </row>
-    <row r="65" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="102"/>
-      <c r="B65" s="103"/>
-      <c r="C65" s="108"/>
-      <c r="D65" s="104"/>
-      <c r="E65" s="104"/>
-      <c r="F65" s="100"/>
-    </row>
-    <row r="66" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="96"/>
-      <c r="B66" s="97"/>
-      <c r="C66" s="98"/>
-      <c r="D66" s="99"/>
-      <c r="E66" s="99"/>
-      <c r="F66" s="100"/>
-    </row>
-    <row r="67" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="96"/>
-      <c r="B67" s="97"/>
-      <c r="C67" s="98"/>
-      <c r="D67" s="99"/>
-      <c r="E67" s="99"/>
-      <c r="F67" s="100"/>
-    </row>
-    <row r="68" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="96"/>
-      <c r="B68" s="97"/>
-      <c r="C68" s="98"/>
-      <c r="D68" s="99"/>
-      <c r="E68" s="99"/>
-      <c r="F68" s="100"/>
-    </row>
-    <row r="69" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="96"/>
-      <c r="B69" s="97"/>
-      <c r="C69" s="98"/>
-      <c r="D69" s="99"/>
-      <c r="E69" s="99"/>
-      <c r="F69" s="100"/>
-    </row>
-    <row r="70" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="96"/>
-      <c r="B70" s="97"/>
-      <c r="C70" s="98"/>
-      <c r="D70" s="99"/>
-      <c r="E70" s="99"/>
-      <c r="F70" s="100"/>
-    </row>
-    <row r="71" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="96"/>
-      <c r="B71" s="97"/>
-      <c r="C71" s="98"/>
-      <c r="D71" s="99"/>
-      <c r="E71" s="99"/>
-      <c r="F71" s="100"/>
-    </row>
-    <row r="72" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="96"/>
-      <c r="B72" s="97"/>
-      <c r="C72" s="98"/>
-      <c r="D72" s="99"/>
-      <c r="E72" s="99"/>
-      <c r="F72" s="100"/>
-    </row>
-    <row r="73" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="96"/>
-      <c r="B73" s="97"/>
-      <c r="C73" s="98"/>
-      <c r="D73" s="99"/>
-      <c r="E73" s="99"/>
-      <c r="F73" s="100"/>
-    </row>
-    <row r="74" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="96"/>
-      <c r="B74" s="97"/>
-      <c r="C74" s="98"/>
-      <c r="D74" s="99"/>
-      <c r="E74" s="99"/>
-      <c r="F74" s="100"/>
-    </row>
-    <row r="75" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="102"/>
-      <c r="B75" s="103"/>
-      <c r="C75" s="98"/>
-      <c r="D75" s="99"/>
-      <c r="E75" s="99"/>
-      <c r="F75" s="100"/>
-    </row>
-    <row r="76" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="102"/>
-      <c r="B76" s="103"/>
-      <c r="C76" s="98"/>
-      <c r="D76" s="99"/>
-      <c r="E76" s="99"/>
-      <c r="F76" s="100"/>
-    </row>
-    <row r="77" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="102"/>
-      <c r="B77" s="103"/>
-      <c r="C77" s="98"/>
-      <c r="D77" s="104"/>
-      <c r="E77" s="104"/>
-      <c r="F77" s="100"/>
-    </row>
-    <row r="78" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="102"/>
-      <c r="B78" s="103"/>
-      <c r="C78" s="98"/>
-      <c r="D78" s="104"/>
-      <c r="E78" s="104"/>
-      <c r="F78" s="100"/>
-    </row>
-    <row r="79" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="102"/>
-      <c r="B79" s="103"/>
-      <c r="C79" s="98"/>
-      <c r="D79" s="104"/>
-      <c r="E79" s="104"/>
-      <c r="F79" s="100"/>
-    </row>
-    <row r="80" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="102"/>
-      <c r="B80" s="103"/>
-      <c r="C80" s="98"/>
-      <c r="D80" s="104"/>
-      <c r="E80" s="104"/>
-      <c r="F80" s="100"/>
-    </row>
-    <row r="81" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="102"/>
-      <c r="B81" s="103"/>
-      <c r="C81" s="98"/>
-      <c r="D81" s="104"/>
-      <c r="E81" s="104"/>
-      <c r="F81" s="100"/>
-    </row>
-    <row r="82" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="102"/>
-      <c r="B82" s="103"/>
-      <c r="C82" s="98"/>
-      <c r="D82" s="104"/>
-      <c r="E82" s="104"/>
-      <c r="F82" s="100"/>
-    </row>
-    <row r="83" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="102"/>
-      <c r="B83" s="103"/>
-      <c r="C83" s="105"/>
-      <c r="D83" s="104"/>
-      <c r="E83" s="104"/>
-      <c r="F83" s="100"/>
-    </row>
-    <row r="84" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="102"/>
-      <c r="B84" s="103"/>
-      <c r="C84" s="98"/>
-      <c r="D84" s="104"/>
-      <c r="E84" s="104"/>
-      <c r="F84" s="100"/>
-    </row>
-    <row r="85" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="102"/>
-      <c r="B85" s="103"/>
-      <c r="C85" s="105"/>
-      <c r="D85" s="104"/>
-      <c r="E85" s="104"/>
-      <c r="F85" s="100"/>
-    </row>
-    <row r="86" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="102"/>
-      <c r="B86" s="103"/>
-      <c r="C86" s="105"/>
-      <c r="D86" s="104"/>
-      <c r="E86" s="104"/>
-      <c r="F86" s="100"/>
-    </row>
-    <row r="87" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="102"/>
-      <c r="B87" s="103"/>
-      <c r="C87" s="98"/>
-      <c r="D87" s="104"/>
-      <c r="E87" s="104"/>
-      <c r="F87" s="100"/>
-    </row>
-    <row r="88" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="102"/>
-      <c r="B88" s="103"/>
-      <c r="C88" s="98"/>
-      <c r="D88" s="104"/>
-      <c r="E88" s="104"/>
-      <c r="F88" s="100"/>
-    </row>
-    <row r="89" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A89" s="102"/>
-      <c r="B89" s="103"/>
-      <c r="C89" s="107"/>
-      <c r="D89" s="104"/>
-      <c r="E89" s="104"/>
-      <c r="F89" s="100"/>
-    </row>
-    <row r="90" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="102"/>
-      <c r="B90" s="103"/>
-      <c r="C90" s="98"/>
-      <c r="D90" s="104"/>
-      <c r="E90" s="104"/>
-      <c r="F90" s="100"/>
-    </row>
-    <row r="91" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="102"/>
-      <c r="B91" s="103"/>
-      <c r="C91" s="107"/>
-      <c r="D91" s="104"/>
-      <c r="E91" s="104"/>
-      <c r="F91" s="100"/>
-    </row>
-    <row r="92" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="102"/>
-      <c r="B92" s="103"/>
-      <c r="C92" s="105"/>
-      <c r="D92" s="104"/>
-      <c r="E92" s="104"/>
-      <c r="F92" s="100"/>
-    </row>
-    <row r="93" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A93" s="102"/>
-      <c r="B93" s="103"/>
-      <c r="C93" s="105"/>
-      <c r="D93" s="104"/>
-      <c r="E93" s="104"/>
-      <c r="F93" s="100"/>
-    </row>
-    <row r="94" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="102"/>
-      <c r="B94" s="103"/>
-      <c r="C94" s="105"/>
-      <c r="D94" s="104"/>
-      <c r="E94" s="104"/>
-      <c r="F94" s="100"/>
-    </row>
-    <row r="95" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="102"/>
-      <c r="B95" s="103"/>
-      <c r="C95" s="105"/>
-      <c r="D95" s="104"/>
-      <c r="E95" s="104"/>
-      <c r="F95" s="100"/>
-    </row>
-    <row r="96" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="102"/>
-      <c r="B96" s="103"/>
-      <c r="C96" s="105"/>
-      <c r="D96" s="104"/>
-      <c r="E96" s="104"/>
-      <c r="F96" s="100"/>
-    </row>
-    <row r="97" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="102"/>
-      <c r="B97" s="103"/>
-      <c r="C97" s="98"/>
-      <c r="D97" s="104"/>
-      <c r="E97" s="104"/>
-      <c r="F97" s="100"/>
-    </row>
-    <row r="98" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="102"/>
-      <c r="B98" s="103"/>
-      <c r="C98" s="98"/>
-      <c r="D98" s="104"/>
-      <c r="E98" s="104"/>
-      <c r="F98" s="100"/>
-    </row>
-    <row r="99" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="102"/>
-      <c r="B99" s="103"/>
-      <c r="C99" s="108"/>
-      <c r="D99" s="104"/>
-      <c r="E99" s="104"/>
-      <c r="F99" s="100"/>
-    </row>
-    <row r="100" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="102"/>
-      <c r="B100" s="103"/>
-      <c r="C100" s="107"/>
-      <c r="D100" s="104"/>
-      <c r="E100" s="104"/>
-      <c r="F100" s="100"/>
-    </row>
-    <row r="101" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="102"/>
-      <c r="B101" s="103"/>
-      <c r="C101" s="108"/>
-      <c r="D101" s="104"/>
-      <c r="E101" s="104"/>
-      <c r="F101" s="100"/>
-    </row>
-    <row r="102" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="102"/>
-      <c r="B102" s="103"/>
-      <c r="C102" s="108"/>
-      <c r="D102" s="104"/>
-      <c r="E102" s="104"/>
-      <c r="F102" s="100"/>
-    </row>
-    <row r="103" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A103" s="102"/>
-      <c r="B103" s="103"/>
-      <c r="C103" s="108"/>
-      <c r="D103" s="104"/>
-      <c r="E103" s="104"/>
-      <c r="F103" s="100"/>
-    </row>
-    <row r="104" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A104" s="102"/>
-      <c r="B104" s="103"/>
-      <c r="C104" s="108"/>
-      <c r="D104" s="104"/>
-      <c r="E104" s="104"/>
-      <c r="F104" s="100"/>
-    </row>
-    <row r="105" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="102"/>
-      <c r="B105" s="103"/>
-      <c r="C105" s="108"/>
-      <c r="D105" s="104"/>
-      <c r="E105" s="104"/>
-      <c r="F105" s="100"/>
-    </row>
-    <row r="106" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A106" s="102"/>
-      <c r="B106" s="103"/>
-      <c r="C106" s="108"/>
-      <c r="D106" s="104"/>
-      <c r="E106" s="104"/>
-      <c r="F106" s="100"/>
-    </row>
-    <row r="107" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A107" s="102"/>
-      <c r="B107" s="103"/>
-      <c r="C107" s="108"/>
-      <c r="D107" s="104"/>
-      <c r="E107" s="104"/>
-      <c r="F107" s="100"/>
-    </row>
-    <row r="108" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A108" s="102"/>
-      <c r="B108" s="103"/>
-      <c r="C108" s="108"/>
-      <c r="D108" s="104"/>
-      <c r="E108" s="104"/>
-      <c r="F108" s="100"/>
-    </row>
-    <row r="109" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="102"/>
-      <c r="B109" s="103"/>
-      <c r="C109" s="108"/>
-      <c r="D109" s="104"/>
-      <c r="E109" s="104"/>
-      <c r="F109" s="100"/>
-    </row>
-    <row r="110" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A110" s="102"/>
-      <c r="B110" s="103"/>
-      <c r="C110" s="108"/>
-      <c r="D110" s="104"/>
-      <c r="E110" s="104"/>
-      <c r="F110" s="100"/>
-    </row>
-    <row r="111" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A111" s="102"/>
-      <c r="B111" s="103"/>
-      <c r="C111" s="108"/>
-      <c r="D111" s="104"/>
-      <c r="E111" s="104"/>
-      <c r="F111" s="100"/>
-    </row>
-    <row r="112" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="102"/>
-      <c r="B112" s="103"/>
-      <c r="C112" s="108"/>
-      <c r="D112" s="104"/>
-      <c r="E112" s="104"/>
-      <c r="F112" s="100"/>
-    </row>
-    <row r="113" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="102"/>
-      <c r="B113" s="103"/>
-      <c r="C113" s="108"/>
-      <c r="D113" s="104"/>
-      <c r="E113" s="104"/>
-      <c r="F113" s="100"/>
-    </row>
-    <row r="114" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="102"/>
-      <c r="B114" s="103"/>
-      <c r="C114" s="108"/>
-      <c r="D114" s="104"/>
-      <c r="E114" s="104"/>
-      <c r="F114" s="100"/>
-    </row>
-    <row r="115" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="102"/>
-      <c r="B115" s="103"/>
-      <c r="C115" s="108"/>
-      <c r="D115" s="104"/>
-      <c r="E115" s="104"/>
-      <c r="F115" s="100"/>
-    </row>
-    <row r="116" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A116" s="102"/>
-      <c r="B116" s="103"/>
-      <c r="C116" s="108"/>
-      <c r="D116" s="104"/>
-      <c r="E116" s="104"/>
-      <c r="F116" s="100"/>
-    </row>
-    <row r="117" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A117" s="102"/>
-      <c r="B117" s="103"/>
-      <c r="C117" s="108"/>
-      <c r="D117" s="104"/>
-      <c r="E117" s="104"/>
-      <c r="F117" s="100"/>
-    </row>
-    <row r="118" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A118" s="102"/>
-      <c r="B118" s="103"/>
-      <c r="C118" s="108"/>
-      <c r="D118" s="104"/>
-      <c r="E118" s="104"/>
-      <c r="F118" s="100"/>
-    </row>
-    <row r="119" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A119" s="102"/>
-      <c r="B119" s="103"/>
-      <c r="C119" s="108"/>
-      <c r="D119" s="104"/>
-      <c r="E119" s="104"/>
-      <c r="F119" s="100"/>
-    </row>
-    <row r="120" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A120" s="102"/>
-      <c r="B120" s="103"/>
-      <c r="C120" s="108"/>
-      <c r="D120" s="104"/>
-      <c r="E120" s="104"/>
-      <c r="F120" s="100"/>
-    </row>
-    <row r="121" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A121" s="102"/>
-      <c r="B121" s="103"/>
-      <c r="C121" s="108"/>
-      <c r="D121" s="104"/>
-      <c r="E121" s="104"/>
-      <c r="F121" s="100"/>
-    </row>
-    <row r="122" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A122" s="102"/>
-      <c r="B122" s="103"/>
-      <c r="C122" s="108"/>
-      <c r="D122" s="104"/>
-      <c r="E122" s="104"/>
-      <c r="F122" s="100"/>
-    </row>
-    <row r="123" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="102"/>
-      <c r="B123" s="103"/>
-      <c r="C123" s="108"/>
-      <c r="D123" s="104"/>
-      <c r="E123" s="104"/>
-      <c r="F123" s="100"/>
-    </row>
-    <row r="124" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A124" s="102"/>
-      <c r="B124" s="103"/>
-      <c r="C124" s="108"/>
-      <c r="D124" s="104"/>
-      <c r="E124" s="104"/>
-      <c r="F124" s="100"/>
-    </row>
-    <row r="125" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A125" s="96"/>
-      <c r="B125" s="97"/>
-      <c r="C125" s="98"/>
-      <c r="D125" s="99"/>
-      <c r="E125" s="99"/>
-      <c r="F125" s="100"/>
-    </row>
-    <row r="126" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A126" s="96"/>
-      <c r="B126" s="97"/>
-      <c r="C126" s="98"/>
-      <c r="D126" s="99"/>
-      <c r="E126" s="99"/>
-      <c r="F126" s="100"/>
-    </row>
-    <row r="127" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A127" s="96"/>
-      <c r="B127" s="97"/>
-      <c r="C127" s="98"/>
-      <c r="D127" s="99"/>
-      <c r="E127" s="99"/>
-      <c r="F127" s="100"/>
-    </row>
-    <row r="128" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="96"/>
-      <c r="B128" s="97"/>
-      <c r="C128" s="98"/>
-      <c r="D128" s="99"/>
-      <c r="E128" s="99"/>
-      <c r="F128" s="100"/>
-    </row>
-    <row r="129" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A129" s="96"/>
-      <c r="B129" s="97"/>
-      <c r="C129" s="98"/>
-      <c r="D129" s="99"/>
-      <c r="E129" s="99"/>
-      <c r="F129" s="100"/>
-    </row>
-    <row r="130" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A130" s="96"/>
-      <c r="B130" s="97"/>
-      <c r="C130" s="98"/>
-      <c r="D130" s="99"/>
-      <c r="E130" s="99"/>
-      <c r="F130" s="100"/>
-    </row>
-    <row r="131" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A131" s="96"/>
-      <c r="B131" s="97"/>
-      <c r="C131" s="98"/>
-      <c r="D131" s="99"/>
-      <c r="E131" s="99"/>
-      <c r="F131" s="100"/>
-    </row>
-    <row r="132" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A132" s="96"/>
-      <c r="B132" s="97"/>
-      <c r="C132" s="98"/>
-      <c r="D132" s="99"/>
-      <c r="E132" s="99"/>
-      <c r="F132" s="100"/>
-    </row>
-    <row r="133" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A133" s="96"/>
-      <c r="B133" s="97"/>
-      <c r="C133" s="98"/>
-      <c r="D133" s="99"/>
-      <c r="E133" s="99"/>
-      <c r="F133" s="100"/>
-    </row>
-    <row r="134" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A134" s="102"/>
-      <c r="B134" s="103"/>
-      <c r="C134" s="98"/>
-      <c r="D134" s="99"/>
-      <c r="E134" s="99"/>
-      <c r="F134" s="100"/>
-    </row>
-    <row r="135" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A135" s="102"/>
-      <c r="B135" s="103"/>
-      <c r="C135" s="98"/>
-      <c r="D135" s="99"/>
-      <c r="E135" s="99"/>
-      <c r="F135" s="100"/>
-    </row>
-    <row r="136" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A136" s="102"/>
-      <c r="B136" s="103"/>
-      <c r="C136" s="98"/>
-      <c r="D136" s="104"/>
-      <c r="E136" s="104"/>
-      <c r="F136" s="100"/>
-    </row>
-    <row r="137" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A137" s="102"/>
-      <c r="B137" s="103"/>
-      <c r="C137" s="98"/>
-      <c r="D137" s="104"/>
-      <c r="E137" s="104"/>
-      <c r="F137" s="100"/>
-    </row>
-    <row r="138" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A138" s="102"/>
-      <c r="B138" s="103"/>
-      <c r="C138" s="98"/>
-      <c r="D138" s="104"/>
-      <c r="E138" s="104"/>
-      <c r="F138" s="100"/>
-    </row>
-    <row r="139" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A139" s="102"/>
-      <c r="B139" s="103"/>
-      <c r="C139" s="98"/>
-      <c r="D139" s="104"/>
-      <c r="E139" s="104"/>
-      <c r="F139" s="100"/>
-    </row>
-    <row r="140" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A140" s="102"/>
-      <c r="B140" s="103"/>
-      <c r="C140" s="98"/>
-      <c r="D140" s="104"/>
-      <c r="E140" s="104"/>
-      <c r="F140" s="100"/>
-    </row>
-    <row r="141" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A141" s="102"/>
-      <c r="B141" s="103"/>
-      <c r="C141" s="98"/>
-      <c r="D141" s="104"/>
-      <c r="E141" s="104"/>
-      <c r="F141" s="100"/>
-    </row>
-    <row r="142" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A142" s="102"/>
-      <c r="B142" s="103"/>
-      <c r="C142" s="105"/>
-      <c r="D142" s="104"/>
-      <c r="E142" s="104"/>
-      <c r="F142" s="100"/>
-    </row>
-    <row r="143" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A143" s="102"/>
-      <c r="B143" s="103"/>
-      <c r="C143" s="98"/>
-      <c r="D143" s="104"/>
-      <c r="E143" s="104"/>
-      <c r="F143" s="100"/>
-    </row>
-    <row r="144" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A144" s="102"/>
-      <c r="B144" s="103"/>
-      <c r="C144" s="105"/>
-      <c r="D144" s="104"/>
-      <c r="E144" s="104"/>
-      <c r="F144" s="100"/>
-    </row>
-    <row r="145" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A145" s="102"/>
-      <c r="B145" s="103"/>
-      <c r="C145" s="105"/>
-      <c r="D145" s="104"/>
-      <c r="E145" s="104"/>
-      <c r="F145" s="100"/>
-    </row>
-    <row r="146" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A146" s="102"/>
-      <c r="B146" s="103"/>
-      <c r="C146" s="98"/>
-      <c r="D146" s="104"/>
-      <c r="E146" s="104"/>
-      <c r="F146" s="100"/>
-    </row>
-    <row r="147" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A147" s="102"/>
-      <c r="B147" s="103"/>
-      <c r="C147" s="98"/>
-      <c r="D147" s="104"/>
-      <c r="E147" s="104"/>
-      <c r="F147" s="100"/>
-    </row>
-    <row r="148" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A148" s="102"/>
-      <c r="B148" s="103"/>
-      <c r="C148" s="107"/>
-      <c r="D148" s="104"/>
-      <c r="E148" s="104"/>
-      <c r="F148" s="100"/>
-    </row>
-    <row r="149" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A149" s="102"/>
-      <c r="B149" s="103"/>
-      <c r="C149" s="98"/>
-      <c r="D149" s="104"/>
-      <c r="E149" s="104"/>
-      <c r="F149" s="100"/>
-    </row>
-    <row r="150" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A150" s="102"/>
-      <c r="B150" s="103"/>
-      <c r="C150" s="107"/>
-      <c r="D150" s="104"/>
-      <c r="E150" s="104"/>
-      <c r="F150" s="100"/>
-    </row>
-    <row r="151" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A151" s="102"/>
-      <c r="B151" s="103"/>
-      <c r="C151" s="105"/>
-      <c r="D151" s="104"/>
-      <c r="E151" s="104"/>
-      <c r="F151" s="100"/>
-    </row>
-    <row r="152" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A152" s="102"/>
-      <c r="B152" s="103"/>
-      <c r="C152" s="105"/>
-      <c r="D152" s="104"/>
-      <c r="E152" s="104"/>
-      <c r="F152" s="100"/>
-    </row>
-    <row r="153" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A153" s="102"/>
-      <c r="B153" s="103"/>
-      <c r="C153" s="105"/>
-      <c r="D153" s="104"/>
-      <c r="E153" s="104"/>
-      <c r="F153" s="100"/>
-    </row>
-    <row r="154" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A154" s="102"/>
-      <c r="B154" s="103"/>
-      <c r="C154" s="105"/>
-      <c r="D154" s="104"/>
-      <c r="E154" s="104"/>
-      <c r="F154" s="100"/>
-    </row>
-    <row r="155" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A155" s="102"/>
-      <c r="B155" s="103"/>
-      <c r="C155" s="105"/>
-      <c r="D155" s="104"/>
-      <c r="E155" s="104"/>
-      <c r="F155" s="100"/>
-    </row>
-    <row r="156" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A156" s="102"/>
-      <c r="B156" s="103"/>
-      <c r="C156" s="98"/>
-      <c r="D156" s="104"/>
-      <c r="E156" s="104"/>
-      <c r="F156" s="100"/>
-    </row>
-    <row r="157" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A157" s="102"/>
-      <c r="B157" s="103"/>
-      <c r="C157" s="98"/>
-      <c r="D157" s="104"/>
-      <c r="E157" s="104"/>
-      <c r="F157" s="100"/>
-    </row>
-    <row r="158" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A158" s="102"/>
-      <c r="B158" s="103"/>
-      <c r="C158" s="108"/>
-      <c r="D158" s="104"/>
-      <c r="E158" s="104"/>
-      <c r="F158" s="100"/>
-    </row>
-    <row r="159" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A159" s="102"/>
-      <c r="B159" s="103"/>
-      <c r="C159" s="107"/>
-      <c r="D159" s="104"/>
-      <c r="E159" s="104"/>
-      <c r="F159" s="100"/>
-    </row>
-    <row r="160" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A160" s="102"/>
-      <c r="B160" s="103"/>
-      <c r="C160" s="108"/>
-      <c r="D160" s="104"/>
-      <c r="E160" s="104"/>
-      <c r="F160" s="100"/>
-    </row>
-    <row r="161" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A161" s="102"/>
-      <c r="B161" s="103"/>
-      <c r="C161" s="108"/>
-      <c r="D161" s="104"/>
-      <c r="E161" s="104"/>
-      <c r="F161" s="100"/>
-    </row>
-    <row r="162" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A162" s="102"/>
-      <c r="B162" s="103"/>
-      <c r="C162" s="108"/>
-      <c r="D162" s="104"/>
-      <c r="E162" s="104"/>
-      <c r="F162" s="100"/>
-    </row>
-    <row r="163" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A163" s="102"/>
-      <c r="B163" s="103"/>
-      <c r="C163" s="108"/>
-      <c r="D163" s="104"/>
-      <c r="E163" s="104"/>
-      <c r="F163" s="100"/>
-    </row>
-    <row r="164" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A164" s="102"/>
-      <c r="B164" s="103"/>
-      <c r="C164" s="108"/>
-      <c r="D164" s="104"/>
-      <c r="E164" s="104"/>
-      <c r="F164" s="100"/>
-    </row>
-    <row r="165" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A165" s="102"/>
-      <c r="B165" s="103"/>
-      <c r="C165" s="108"/>
-      <c r="D165" s="104"/>
-      <c r="E165" s="104"/>
-      <c r="F165" s="100"/>
-    </row>
-    <row r="166" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A166" s="102"/>
-      <c r="B166" s="103"/>
-      <c r="C166" s="108"/>
-      <c r="D166" s="104"/>
-      <c r="E166" s="104"/>
-      <c r="F166" s="100"/>
-    </row>
-    <row r="167" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A167" s="102"/>
-      <c r="B167" s="103"/>
-      <c r="C167" s="108"/>
-      <c r="D167" s="104"/>
-      <c r="E167" s="104"/>
-      <c r="F167" s="100"/>
-    </row>
-    <row r="168" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A168" s="102"/>
-      <c r="B168" s="103"/>
-      <c r="C168" s="108"/>
-      <c r="D168" s="104"/>
-      <c r="E168" s="104"/>
-      <c r="F168" s="100"/>
-    </row>
-    <row r="169" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A169" s="102"/>
-      <c r="B169" s="103"/>
-      <c r="C169" s="108"/>
-      <c r="D169" s="104"/>
-      <c r="E169" s="104"/>
-      <c r="F169" s="100"/>
-    </row>
-    <row r="170" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A170" s="102"/>
-      <c r="B170" s="103"/>
-      <c r="C170" s="108"/>
-      <c r="D170" s="104"/>
-      <c r="E170" s="104"/>
-      <c r="F170" s="100"/>
-    </row>
-    <row r="171" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A171" s="102"/>
-      <c r="B171" s="103"/>
-      <c r="C171" s="108"/>
-      <c r="D171" s="104"/>
-      <c r="E171" s="104"/>
-      <c r="F171" s="100"/>
-    </row>
-    <row r="172" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A172" s="102"/>
-      <c r="B172" s="103"/>
-      <c r="C172" s="108"/>
-      <c r="D172" s="104"/>
-      <c r="E172" s="104"/>
-      <c r="F172" s="100"/>
-    </row>
-    <row r="173" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A173" s="102"/>
-      <c r="B173" s="103"/>
-      <c r="C173" s="108"/>
-      <c r="D173" s="104"/>
-      <c r="E173" s="104"/>
-      <c r="F173" s="100"/>
-    </row>
-    <row r="174" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A174" s="102"/>
-      <c r="B174" s="103"/>
-      <c r="C174" s="108"/>
-      <c r="D174" s="104"/>
-      <c r="E174" s="104"/>
-      <c r="F174" s="100"/>
-    </row>
-    <row r="175" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A175" s="102"/>
-      <c r="B175" s="103"/>
-      <c r="C175" s="108"/>
-      <c r="D175" s="104"/>
-      <c r="E175" s="104"/>
-      <c r="F175" s="100"/>
-    </row>
-    <row r="176" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A176" s="102"/>
-      <c r="B176" s="103"/>
-      <c r="C176" s="108"/>
-      <c r="D176" s="104"/>
-      <c r="E176" s="104"/>
-      <c r="F176" s="100"/>
-    </row>
-    <row r="177" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A177" s="102"/>
-      <c r="B177" s="103"/>
-      <c r="C177" s="108"/>
-      <c r="D177" s="104"/>
-      <c r="E177" s="104"/>
-      <c r="F177" s="100"/>
-    </row>
-    <row r="178" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A178" s="102"/>
-      <c r="B178" s="103"/>
-      <c r="C178" s="108"/>
-      <c r="D178" s="104"/>
-      <c r="E178" s="104"/>
-      <c r="F178" s="100"/>
-    </row>
-    <row r="179" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A179" s="102"/>
-      <c r="B179" s="103"/>
-      <c r="C179" s="108"/>
-      <c r="D179" s="104"/>
-      <c r="E179" s="104"/>
-      <c r="F179" s="100"/>
-    </row>
-    <row r="180" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A180" s="102"/>
-      <c r="B180" s="103"/>
-      <c r="C180" s="108"/>
-      <c r="D180" s="104"/>
-      <c r="E180" s="104"/>
-      <c r="F180" s="100"/>
-    </row>
-    <row r="181" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A181" s="102"/>
-      <c r="B181" s="103"/>
-      <c r="C181" s="108"/>
-      <c r="D181" s="104"/>
-      <c r="E181" s="104"/>
-      <c r="F181" s="100"/>
-    </row>
-    <row r="182" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A182" s="102"/>
-      <c r="B182" s="103"/>
-      <c r="C182" s="108"/>
-      <c r="D182" s="104"/>
-      <c r="E182" s="104"/>
-      <c r="F182" s="100"/>
-    </row>
-    <row r="183" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A183" s="102"/>
-      <c r="B183" s="103"/>
-      <c r="C183" s="108"/>
-      <c r="D183" s="104"/>
-      <c r="E183" s="104"/>
-      <c r="F183" s="100"/>
-    </row>
-    <row r="184" spans="1:6" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D184" s="19"/>
-      <c r="E184" s="19"/>
-    </row>
-    <row r="185" spans="1:6" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D185" s="19"/>
-      <c r="E185" s="19"/>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D186" s="19"/>
-      <c r="E186" s="19"/>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D187" s="19"/>
-      <c r="E187" s="19"/>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D188" s="19"/>
-      <c r="E188" s="19"/>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D189" s="19"/>
-      <c r="E189" s="19"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D190" s="19"/>
-      <c r="E190" s="19"/>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D191" s="19"/>
-      <c r="E191" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -23763,6 +23772,1568 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC255F8-7200-D84E-9D73-DDE699449625}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q191"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="60.33203125" style="95" customWidth="1"/>
+    <col min="2" max="2" width="60.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="64.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="66.1640625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="86.33203125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="100" customWidth="1"/>
+    <col min="7" max="7" width="5.33203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="33">
+        <v>46113</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <f>COUNTA(E7:E13510)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:17" ht="47.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="96"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+    </row>
+    <row r="8" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="96"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+    </row>
+    <row r="9" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="96"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="101"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="101"/>
+      <c r="M9" s="101"/>
+      <c r="N9" s="101"/>
+      <c r="O9" s="101"/>
+      <c r="P9" s="101"/>
+      <c r="Q9" s="101"/>
+    </row>
+    <row r="10" spans="1:17" s="101" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="96"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100"/>
+      <c r="H10" s="100"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
+      <c r="M10" s="100"/>
+      <c r="N10" s="100"/>
+      <c r="O10" s="100"/>
+      <c r="P10" s="100"/>
+      <c r="Q10" s="100"/>
+    </row>
+    <row r="11" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="96"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+    </row>
+    <row r="12" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="96"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+    </row>
+    <row r="13" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="96"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+    </row>
+    <row r="14" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="96"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+    </row>
+    <row r="15" spans="1:17" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="96"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="100"/>
+    </row>
+    <row r="16" spans="1:17" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="102"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="100"/>
+    </row>
+    <row r="17" spans="1:6" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="102"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="100"/>
+    </row>
+    <row r="18" spans="1:6" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="102"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="100"/>
+    </row>
+    <row r="19" spans="1:6" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="102"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="100"/>
+    </row>
+    <row r="20" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="102"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="100"/>
+    </row>
+    <row r="21" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="102"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="100"/>
+    </row>
+    <row r="22" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="102"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="100"/>
+    </row>
+    <row r="23" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="102"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="100"/>
+    </row>
+    <row r="24" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="102"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="100"/>
+    </row>
+    <row r="25" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="102"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="100"/>
+    </row>
+    <row r="26" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="102"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="100"/>
+    </row>
+    <row r="27" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="102"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="100"/>
+    </row>
+    <row r="28" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="102"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="100"/>
+    </row>
+    <row r="29" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="102"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="100"/>
+    </row>
+    <row r="30" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="102"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="100"/>
+    </row>
+    <row r="31" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="102"/>
+      <c r="B31" s="103"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="100"/>
+    </row>
+    <row r="32" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="102"/>
+      <c r="B32" s="103"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="100"/>
+    </row>
+    <row r="33" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="102"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="100"/>
+    </row>
+    <row r="34" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="102"/>
+      <c r="B34" s="103"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="100"/>
+    </row>
+    <row r="35" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="102"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="100"/>
+    </row>
+    <row r="36" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="102"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="104"/>
+      <c r="E36" s="104"/>
+      <c r="F36" s="100"/>
+    </row>
+    <row r="37" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="102"/>
+      <c r="B37" s="103"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="100"/>
+    </row>
+    <row r="38" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="102"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="100"/>
+    </row>
+    <row r="39" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="102"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="100"/>
+    </row>
+    <row r="40" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="102"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="108"/>
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="100"/>
+    </row>
+    <row r="41" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="102"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="107"/>
+      <c r="D41" s="104"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="100"/>
+    </row>
+    <row r="42" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="102"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="108"/>
+      <c r="D42" s="104"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="100"/>
+    </row>
+    <row r="43" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="102"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="100"/>
+    </row>
+    <row r="44" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="102"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="108"/>
+      <c r="D44" s="104"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="100"/>
+    </row>
+    <row r="45" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="102"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="108"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="100"/>
+    </row>
+    <row r="46" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="102"/>
+      <c r="B46" s="103"/>
+      <c r="C46" s="108"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="100"/>
+    </row>
+    <row r="47" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="102"/>
+      <c r="B47" s="103"/>
+      <c r="C47" s="108"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="100"/>
+    </row>
+    <row r="48" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="102"/>
+      <c r="B48" s="103"/>
+      <c r="C48" s="108"/>
+      <c r="D48" s="104"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="100"/>
+    </row>
+    <row r="49" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="102"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="108"/>
+      <c r="D49" s="104"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="100"/>
+    </row>
+    <row r="50" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="102"/>
+      <c r="B50" s="103"/>
+      <c r="C50" s="108"/>
+      <c r="D50" s="104"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="100"/>
+    </row>
+    <row r="51" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="102"/>
+      <c r="B51" s="103"/>
+      <c r="C51" s="108"/>
+      <c r="D51" s="104"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="100"/>
+    </row>
+    <row r="52" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="102"/>
+      <c r="B52" s="103"/>
+      <c r="C52" s="108"/>
+      <c r="D52" s="104"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="100"/>
+    </row>
+    <row r="53" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="102"/>
+      <c r="B53" s="103"/>
+      <c r="C53" s="108"/>
+      <c r="D53" s="104"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="100"/>
+    </row>
+    <row r="54" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="102"/>
+      <c r="B54" s="103"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="104"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="100"/>
+    </row>
+    <row r="55" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="102"/>
+      <c r="B55" s="103"/>
+      <c r="C55" s="108"/>
+      <c r="D55" s="104"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="100"/>
+    </row>
+    <row r="56" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="102"/>
+      <c r="B56" s="103"/>
+      <c r="C56" s="108"/>
+      <c r="D56" s="104"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="100"/>
+    </row>
+    <row r="57" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="102"/>
+      <c r="B57" s="103"/>
+      <c r="C57" s="108"/>
+      <c r="D57" s="104"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="100"/>
+    </row>
+    <row r="58" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="102"/>
+      <c r="B58" s="103"/>
+      <c r="C58" s="108"/>
+      <c r="D58" s="104"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="100"/>
+    </row>
+    <row r="59" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="102"/>
+      <c r="B59" s="103"/>
+      <c r="C59" s="108"/>
+      <c r="D59" s="104"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="100"/>
+    </row>
+    <row r="60" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="102"/>
+      <c r="B60" s="103"/>
+      <c r="C60" s="108"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="100"/>
+    </row>
+    <row r="61" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="102"/>
+      <c r="B61" s="103"/>
+      <c r="C61" s="108"/>
+      <c r="D61" s="104"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="100"/>
+    </row>
+    <row r="62" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="102"/>
+      <c r="B62" s="103"/>
+      <c r="C62" s="108"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="100"/>
+    </row>
+    <row r="63" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="102"/>
+      <c r="B63" s="103"/>
+      <c r="C63" s="108"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="100"/>
+    </row>
+    <row r="64" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="102"/>
+      <c r="B64" s="103"/>
+      <c r="C64" s="108"/>
+      <c r="D64" s="104"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="100"/>
+    </row>
+    <row r="65" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="102"/>
+      <c r="B65" s="103"/>
+      <c r="C65" s="108"/>
+      <c r="D65" s="104"/>
+      <c r="E65" s="104"/>
+      <c r="F65" s="100"/>
+    </row>
+    <row r="66" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="96"/>
+      <c r="B66" s="97"/>
+      <c r="C66" s="98"/>
+      <c r="D66" s="99"/>
+      <c r="E66" s="99"/>
+      <c r="F66" s="100"/>
+    </row>
+    <row r="67" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="96"/>
+      <c r="B67" s="97"/>
+      <c r="C67" s="98"/>
+      <c r="D67" s="99"/>
+      <c r="E67" s="99"/>
+      <c r="F67" s="100"/>
+    </row>
+    <row r="68" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="96"/>
+      <c r="B68" s="97"/>
+      <c r="C68" s="98"/>
+      <c r="D68" s="99"/>
+      <c r="E68" s="99"/>
+      <c r="F68" s="100"/>
+    </row>
+    <row r="69" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="96"/>
+      <c r="B69" s="97"/>
+      <c r="C69" s="98"/>
+      <c r="D69" s="99"/>
+      <c r="E69" s="99"/>
+      <c r="F69" s="100"/>
+    </row>
+    <row r="70" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="96"/>
+      <c r="B70" s="97"/>
+      <c r="C70" s="98"/>
+      <c r="D70" s="99"/>
+      <c r="E70" s="99"/>
+      <c r="F70" s="100"/>
+    </row>
+    <row r="71" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="96"/>
+      <c r="B71" s="97"/>
+      <c r="C71" s="98"/>
+      <c r="D71" s="99"/>
+      <c r="E71" s="99"/>
+      <c r="F71" s="100"/>
+    </row>
+    <row r="72" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="96"/>
+      <c r="B72" s="97"/>
+      <c r="C72" s="98"/>
+      <c r="D72" s="99"/>
+      <c r="E72" s="99"/>
+      <c r="F72" s="100"/>
+    </row>
+    <row r="73" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="96"/>
+      <c r="B73" s="97"/>
+      <c r="C73" s="98"/>
+      <c r="D73" s="99"/>
+      <c r="E73" s="99"/>
+      <c r="F73" s="100"/>
+    </row>
+    <row r="74" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="96"/>
+      <c r="B74" s="97"/>
+      <c r="C74" s="98"/>
+      <c r="D74" s="99"/>
+      <c r="E74" s="99"/>
+      <c r="F74" s="100"/>
+    </row>
+    <row r="75" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="102"/>
+      <c r="B75" s="103"/>
+      <c r="C75" s="98"/>
+      <c r="D75" s="99"/>
+      <c r="E75" s="99"/>
+      <c r="F75" s="100"/>
+    </row>
+    <row r="76" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="102"/>
+      <c r="B76" s="103"/>
+      <c r="C76" s="98"/>
+      <c r="D76" s="99"/>
+      <c r="E76" s="99"/>
+      <c r="F76" s="100"/>
+    </row>
+    <row r="77" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="102"/>
+      <c r="B77" s="103"/>
+      <c r="C77" s="98"/>
+      <c r="D77" s="104"/>
+      <c r="E77" s="104"/>
+      <c r="F77" s="100"/>
+    </row>
+    <row r="78" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="102"/>
+      <c r="B78" s="103"/>
+      <c r="C78" s="98"/>
+      <c r="D78" s="104"/>
+      <c r="E78" s="104"/>
+      <c r="F78" s="100"/>
+    </row>
+    <row r="79" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="102"/>
+      <c r="B79" s="103"/>
+      <c r="C79" s="98"/>
+      <c r="D79" s="104"/>
+      <c r="E79" s="104"/>
+      <c r="F79" s="100"/>
+    </row>
+    <row r="80" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="102"/>
+      <c r="B80" s="103"/>
+      <c r="C80" s="98"/>
+      <c r="D80" s="104"/>
+      <c r="E80" s="104"/>
+      <c r="F80" s="100"/>
+    </row>
+    <row r="81" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="102"/>
+      <c r="B81" s="103"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="104"/>
+      <c r="E81" s="104"/>
+      <c r="F81" s="100"/>
+    </row>
+    <row r="82" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="102"/>
+      <c r="B82" s="103"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="104"/>
+      <c r="E82" s="104"/>
+      <c r="F82" s="100"/>
+    </row>
+    <row r="83" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="102"/>
+      <c r="B83" s="103"/>
+      <c r="C83" s="105"/>
+      <c r="D83" s="104"/>
+      <c r="E83" s="104"/>
+      <c r="F83" s="100"/>
+    </row>
+    <row r="84" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="102"/>
+      <c r="B84" s="103"/>
+      <c r="C84" s="98"/>
+      <c r="D84" s="104"/>
+      <c r="E84" s="104"/>
+      <c r="F84" s="100"/>
+    </row>
+    <row r="85" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="102"/>
+      <c r="B85" s="103"/>
+      <c r="C85" s="105"/>
+      <c r="D85" s="104"/>
+      <c r="E85" s="104"/>
+      <c r="F85" s="100"/>
+    </row>
+    <row r="86" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="102"/>
+      <c r="B86" s="103"/>
+      <c r="C86" s="105"/>
+      <c r="D86" s="104"/>
+      <c r="E86" s="104"/>
+      <c r="F86" s="100"/>
+    </row>
+    <row r="87" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="102"/>
+      <c r="B87" s="103"/>
+      <c r="C87" s="98"/>
+      <c r="D87" s="104"/>
+      <c r="E87" s="104"/>
+      <c r="F87" s="100"/>
+    </row>
+    <row r="88" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="102"/>
+      <c r="B88" s="103"/>
+      <c r="C88" s="98"/>
+      <c r="D88" s="104"/>
+      <c r="E88" s="104"/>
+      <c r="F88" s="100"/>
+    </row>
+    <row r="89" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="102"/>
+      <c r="B89" s="103"/>
+      <c r="C89" s="107"/>
+      <c r="D89" s="104"/>
+      <c r="E89" s="104"/>
+      <c r="F89" s="100"/>
+    </row>
+    <row r="90" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="102"/>
+      <c r="B90" s="103"/>
+      <c r="C90" s="98"/>
+      <c r="D90" s="104"/>
+      <c r="E90" s="104"/>
+      <c r="F90" s="100"/>
+    </row>
+    <row r="91" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="102"/>
+      <c r="B91" s="103"/>
+      <c r="C91" s="107"/>
+      <c r="D91" s="104"/>
+      <c r="E91" s="104"/>
+      <c r="F91" s="100"/>
+    </row>
+    <row r="92" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="102"/>
+      <c r="B92" s="103"/>
+      <c r="C92" s="105"/>
+      <c r="D92" s="104"/>
+      <c r="E92" s="104"/>
+      <c r="F92" s="100"/>
+    </row>
+    <row r="93" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="102"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="105"/>
+      <c r="D93" s="104"/>
+      <c r="E93" s="104"/>
+      <c r="F93" s="100"/>
+    </row>
+    <row r="94" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="102"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="105"/>
+      <c r="D94" s="104"/>
+      <c r="E94" s="104"/>
+      <c r="F94" s="100"/>
+    </row>
+    <row r="95" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="102"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="105"/>
+      <c r="D95" s="104"/>
+      <c r="E95" s="104"/>
+      <c r="F95" s="100"/>
+    </row>
+    <row r="96" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="102"/>
+      <c r="B96" s="103"/>
+      <c r="C96" s="105"/>
+      <c r="D96" s="104"/>
+      <c r="E96" s="104"/>
+      <c r="F96" s="100"/>
+    </row>
+    <row r="97" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="102"/>
+      <c r="B97" s="103"/>
+      <c r="C97" s="98"/>
+      <c r="D97" s="104"/>
+      <c r="E97" s="104"/>
+      <c r="F97" s="100"/>
+    </row>
+    <row r="98" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="102"/>
+      <c r="B98" s="103"/>
+      <c r="C98" s="98"/>
+      <c r="D98" s="104"/>
+      <c r="E98" s="104"/>
+      <c r="F98" s="100"/>
+    </row>
+    <row r="99" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="102"/>
+      <c r="B99" s="103"/>
+      <c r="C99" s="108"/>
+      <c r="D99" s="104"/>
+      <c r="E99" s="104"/>
+      <c r="F99" s="100"/>
+    </row>
+    <row r="100" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="102"/>
+      <c r="B100" s="103"/>
+      <c r="C100" s="107"/>
+      <c r="D100" s="104"/>
+      <c r="E100" s="104"/>
+      <c r="F100" s="100"/>
+    </row>
+    <row r="101" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="102"/>
+      <c r="B101" s="103"/>
+      <c r="C101" s="108"/>
+      <c r="D101" s="104"/>
+      <c r="E101" s="104"/>
+      <c r="F101" s="100"/>
+    </row>
+    <row r="102" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="102"/>
+      <c r="B102" s="103"/>
+      <c r="C102" s="108"/>
+      <c r="D102" s="104"/>
+      <c r="E102" s="104"/>
+      <c r="F102" s="100"/>
+    </row>
+    <row r="103" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="102"/>
+      <c r="B103" s="103"/>
+      <c r="C103" s="108"/>
+      <c r="D103" s="104"/>
+      <c r="E103" s="104"/>
+      <c r="F103" s="100"/>
+    </row>
+    <row r="104" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="102"/>
+      <c r="B104" s="103"/>
+      <c r="C104" s="108"/>
+      <c r="D104" s="104"/>
+      <c r="E104" s="104"/>
+      <c r="F104" s="100"/>
+    </row>
+    <row r="105" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="102"/>
+      <c r="B105" s="103"/>
+      <c r="C105" s="108"/>
+      <c r="D105" s="104"/>
+      <c r="E105" s="104"/>
+      <c r="F105" s="100"/>
+    </row>
+    <row r="106" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A106" s="102"/>
+      <c r="B106" s="103"/>
+      <c r="C106" s="108"/>
+      <c r="D106" s="104"/>
+      <c r="E106" s="104"/>
+      <c r="F106" s="100"/>
+    </row>
+    <row r="107" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="102"/>
+      <c r="B107" s="103"/>
+      <c r="C107" s="108"/>
+      <c r="D107" s="104"/>
+      <c r="E107" s="104"/>
+      <c r="F107" s="100"/>
+    </row>
+    <row r="108" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A108" s="102"/>
+      <c r="B108" s="103"/>
+      <c r="C108" s="108"/>
+      <c r="D108" s="104"/>
+      <c r="E108" s="104"/>
+      <c r="F108" s="100"/>
+    </row>
+    <row r="109" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A109" s="102"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="108"/>
+      <c r="D109" s="104"/>
+      <c r="E109" s="104"/>
+      <c r="F109" s="100"/>
+    </row>
+    <row r="110" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A110" s="102"/>
+      <c r="B110" s="103"/>
+      <c r="C110" s="108"/>
+      <c r="D110" s="104"/>
+      <c r="E110" s="104"/>
+      <c r="F110" s="100"/>
+    </row>
+    <row r="111" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A111" s="102"/>
+      <c r="B111" s="103"/>
+      <c r="C111" s="108"/>
+      <c r="D111" s="104"/>
+      <c r="E111" s="104"/>
+      <c r="F111" s="100"/>
+    </row>
+    <row r="112" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A112" s="102"/>
+      <c r="B112" s="103"/>
+      <c r="C112" s="108"/>
+      <c r="D112" s="104"/>
+      <c r="E112" s="104"/>
+      <c r="F112" s="100"/>
+    </row>
+    <row r="113" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A113" s="102"/>
+      <c r="B113" s="103"/>
+      <c r="C113" s="108"/>
+      <c r="D113" s="104"/>
+      <c r="E113" s="104"/>
+      <c r="F113" s="100"/>
+    </row>
+    <row r="114" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="102"/>
+      <c r="B114" s="103"/>
+      <c r="C114" s="108"/>
+      <c r="D114" s="104"/>
+      <c r="E114" s="104"/>
+      <c r="F114" s="100"/>
+    </row>
+    <row r="115" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A115" s="102"/>
+      <c r="B115" s="103"/>
+      <c r="C115" s="108"/>
+      <c r="D115" s="104"/>
+      <c r="E115" s="104"/>
+      <c r="F115" s="100"/>
+    </row>
+    <row r="116" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A116" s="102"/>
+      <c r="B116" s="103"/>
+      <c r="C116" s="108"/>
+      <c r="D116" s="104"/>
+      <c r="E116" s="104"/>
+      <c r="F116" s="100"/>
+    </row>
+    <row r="117" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A117" s="102"/>
+      <c r="B117" s="103"/>
+      <c r="C117" s="108"/>
+      <c r="D117" s="104"/>
+      <c r="E117" s="104"/>
+      <c r="F117" s="100"/>
+    </row>
+    <row r="118" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A118" s="102"/>
+      <c r="B118" s="103"/>
+      <c r="C118" s="108"/>
+      <c r="D118" s="104"/>
+      <c r="E118" s="104"/>
+      <c r="F118" s="100"/>
+    </row>
+    <row r="119" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A119" s="102"/>
+      <c r="B119" s="103"/>
+      <c r="C119" s="108"/>
+      <c r="D119" s="104"/>
+      <c r="E119" s="104"/>
+      <c r="F119" s="100"/>
+    </row>
+    <row r="120" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A120" s="102"/>
+      <c r="B120" s="103"/>
+      <c r="C120" s="108"/>
+      <c r="D120" s="104"/>
+      <c r="E120" s="104"/>
+      <c r="F120" s="100"/>
+    </row>
+    <row r="121" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A121" s="102"/>
+      <c r="B121" s="103"/>
+      <c r="C121" s="108"/>
+      <c r="D121" s="104"/>
+      <c r="E121" s="104"/>
+      <c r="F121" s="100"/>
+    </row>
+    <row r="122" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A122" s="102"/>
+      <c r="B122" s="103"/>
+      <c r="C122" s="108"/>
+      <c r="D122" s="104"/>
+      <c r="E122" s="104"/>
+      <c r="F122" s="100"/>
+    </row>
+    <row r="123" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A123" s="102"/>
+      <c r="B123" s="103"/>
+      <c r="C123" s="108"/>
+      <c r="D123" s="104"/>
+      <c r="E123" s="104"/>
+      <c r="F123" s="100"/>
+    </row>
+    <row r="124" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A124" s="102"/>
+      <c r="B124" s="103"/>
+      <c r="C124" s="108"/>
+      <c r="D124" s="104"/>
+      <c r="E124" s="104"/>
+      <c r="F124" s="100"/>
+    </row>
+    <row r="125" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A125" s="96"/>
+      <c r="B125" s="97"/>
+      <c r="C125" s="98"/>
+      <c r="D125" s="99"/>
+      <c r="E125" s="99"/>
+      <c r="F125" s="100"/>
+    </row>
+    <row r="126" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A126" s="96"/>
+      <c r="B126" s="97"/>
+      <c r="C126" s="98"/>
+      <c r="D126" s="99"/>
+      <c r="E126" s="99"/>
+      <c r="F126" s="100"/>
+    </row>
+    <row r="127" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A127" s="96"/>
+      <c r="B127" s="97"/>
+      <c r="C127" s="98"/>
+      <c r="D127" s="99"/>
+      <c r="E127" s="99"/>
+      <c r="F127" s="100"/>
+    </row>
+    <row r="128" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A128" s="96"/>
+      <c r="B128" s="97"/>
+      <c r="C128" s="98"/>
+      <c r="D128" s="99"/>
+      <c r="E128" s="99"/>
+      <c r="F128" s="100"/>
+    </row>
+    <row r="129" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A129" s="96"/>
+      <c r="B129" s="97"/>
+      <c r="C129" s="98"/>
+      <c r="D129" s="99"/>
+      <c r="E129" s="99"/>
+      <c r="F129" s="100"/>
+    </row>
+    <row r="130" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="96"/>
+      <c r="B130" s="97"/>
+      <c r="C130" s="98"/>
+      <c r="D130" s="99"/>
+      <c r="E130" s="99"/>
+      <c r="F130" s="100"/>
+    </row>
+    <row r="131" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A131" s="96"/>
+      <c r="B131" s="97"/>
+      <c r="C131" s="98"/>
+      <c r="D131" s="99"/>
+      <c r="E131" s="99"/>
+      <c r="F131" s="100"/>
+    </row>
+    <row r="132" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A132" s="96"/>
+      <c r="B132" s="97"/>
+      <c r="C132" s="98"/>
+      <c r="D132" s="99"/>
+      <c r="E132" s="99"/>
+      <c r="F132" s="100"/>
+    </row>
+    <row r="133" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A133" s="96"/>
+      <c r="B133" s="97"/>
+      <c r="C133" s="98"/>
+      <c r="D133" s="99"/>
+      <c r="E133" s="99"/>
+      <c r="F133" s="100"/>
+    </row>
+    <row r="134" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A134" s="102"/>
+      <c r="B134" s="103"/>
+      <c r="C134" s="98"/>
+      <c r="D134" s="99"/>
+      <c r="E134" s="99"/>
+      <c r="F134" s="100"/>
+    </row>
+    <row r="135" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A135" s="102"/>
+      <c r="B135" s="103"/>
+      <c r="C135" s="98"/>
+      <c r="D135" s="99"/>
+      <c r="E135" s="99"/>
+      <c r="F135" s="100"/>
+    </row>
+    <row r="136" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A136" s="102"/>
+      <c r="B136" s="103"/>
+      <c r="C136" s="98"/>
+      <c r="D136" s="104"/>
+      <c r="E136" s="104"/>
+      <c r="F136" s="100"/>
+    </row>
+    <row r="137" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A137" s="102"/>
+      <c r="B137" s="103"/>
+      <c r="C137" s="98"/>
+      <c r="D137" s="104"/>
+      <c r="E137" s="104"/>
+      <c r="F137" s="100"/>
+    </row>
+    <row r="138" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A138" s="102"/>
+      <c r="B138" s="103"/>
+      <c r="C138" s="98"/>
+      <c r="D138" s="104"/>
+      <c r="E138" s="104"/>
+      <c r="F138" s="100"/>
+    </row>
+    <row r="139" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A139" s="102"/>
+      <c r="B139" s="103"/>
+      <c r="C139" s="98"/>
+      <c r="D139" s="104"/>
+      <c r="E139" s="104"/>
+      <c r="F139" s="100"/>
+    </row>
+    <row r="140" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A140" s="102"/>
+      <c r="B140" s="103"/>
+      <c r="C140" s="98"/>
+      <c r="D140" s="104"/>
+      <c r="E140" s="104"/>
+      <c r="F140" s="100"/>
+    </row>
+    <row r="141" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A141" s="102"/>
+      <c r="B141" s="103"/>
+      <c r="C141" s="98"/>
+      <c r="D141" s="104"/>
+      <c r="E141" s="104"/>
+      <c r="F141" s="100"/>
+    </row>
+    <row r="142" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A142" s="102"/>
+      <c r="B142" s="103"/>
+      <c r="C142" s="105"/>
+      <c r="D142" s="104"/>
+      <c r="E142" s="104"/>
+      <c r="F142" s="100"/>
+    </row>
+    <row r="143" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A143" s="102"/>
+      <c r="B143" s="103"/>
+      <c r="C143" s="98"/>
+      <c r="D143" s="104"/>
+      <c r="E143" s="104"/>
+      <c r="F143" s="100"/>
+    </row>
+    <row r="144" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A144" s="102"/>
+      <c r="B144" s="103"/>
+      <c r="C144" s="105"/>
+      <c r="D144" s="104"/>
+      <c r="E144" s="104"/>
+      <c r="F144" s="100"/>
+    </row>
+    <row r="145" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A145" s="102"/>
+      <c r="B145" s="103"/>
+      <c r="C145" s="105"/>
+      <c r="D145" s="104"/>
+      <c r="E145" s="104"/>
+      <c r="F145" s="100"/>
+    </row>
+    <row r="146" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A146" s="102"/>
+      <c r="B146" s="103"/>
+      <c r="C146" s="98"/>
+      <c r="D146" s="104"/>
+      <c r="E146" s="104"/>
+      <c r="F146" s="100"/>
+    </row>
+    <row r="147" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A147" s="102"/>
+      <c r="B147" s="103"/>
+      <c r="C147" s="98"/>
+      <c r="D147" s="104"/>
+      <c r="E147" s="104"/>
+      <c r="F147" s="100"/>
+    </row>
+    <row r="148" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A148" s="102"/>
+      <c r="B148" s="103"/>
+      <c r="C148" s="107"/>
+      <c r="D148" s="104"/>
+      <c r="E148" s="104"/>
+      <c r="F148" s="100"/>
+    </row>
+    <row r="149" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A149" s="102"/>
+      <c r="B149" s="103"/>
+      <c r="C149" s="98"/>
+      <c r="D149" s="104"/>
+      <c r="E149" s="104"/>
+      <c r="F149" s="100"/>
+    </row>
+    <row r="150" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A150" s="102"/>
+      <c r="B150" s="103"/>
+      <c r="C150" s="107"/>
+      <c r="D150" s="104"/>
+      <c r="E150" s="104"/>
+      <c r="F150" s="100"/>
+    </row>
+    <row r="151" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A151" s="102"/>
+      <c r="B151" s="103"/>
+      <c r="C151" s="105"/>
+      <c r="D151" s="104"/>
+      <c r="E151" s="104"/>
+      <c r="F151" s="100"/>
+    </row>
+    <row r="152" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A152" s="102"/>
+      <c r="B152" s="103"/>
+      <c r="C152" s="105"/>
+      <c r="D152" s="104"/>
+      <c r="E152" s="104"/>
+      <c r="F152" s="100"/>
+    </row>
+    <row r="153" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A153" s="102"/>
+      <c r="B153" s="103"/>
+      <c r="C153" s="105"/>
+      <c r="D153" s="104"/>
+      <c r="E153" s="104"/>
+      <c r="F153" s="100"/>
+    </row>
+    <row r="154" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A154" s="102"/>
+      <c r="B154" s="103"/>
+      <c r="C154" s="105"/>
+      <c r="D154" s="104"/>
+      <c r="E154" s="104"/>
+      <c r="F154" s="100"/>
+    </row>
+    <row r="155" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A155" s="102"/>
+      <c r="B155" s="103"/>
+      <c r="C155" s="105"/>
+      <c r="D155" s="104"/>
+      <c r="E155" s="104"/>
+      <c r="F155" s="100"/>
+    </row>
+    <row r="156" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A156" s="102"/>
+      <c r="B156" s="103"/>
+      <c r="C156" s="98"/>
+      <c r="D156" s="104"/>
+      <c r="E156" s="104"/>
+      <c r="F156" s="100"/>
+    </row>
+    <row r="157" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A157" s="102"/>
+      <c r="B157" s="103"/>
+      <c r="C157" s="98"/>
+      <c r="D157" s="104"/>
+      <c r="E157" s="104"/>
+      <c r="F157" s="100"/>
+    </row>
+    <row r="158" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A158" s="102"/>
+      <c r="B158" s="103"/>
+      <c r="C158" s="108"/>
+      <c r="D158" s="104"/>
+      <c r="E158" s="104"/>
+      <c r="F158" s="100"/>
+    </row>
+    <row r="159" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A159" s="102"/>
+      <c r="B159" s="103"/>
+      <c r="C159" s="107"/>
+      <c r="D159" s="104"/>
+      <c r="E159" s="104"/>
+      <c r="F159" s="100"/>
+    </row>
+    <row r="160" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A160" s="102"/>
+      <c r="B160" s="103"/>
+      <c r="C160" s="108"/>
+      <c r="D160" s="104"/>
+      <c r="E160" s="104"/>
+      <c r="F160" s="100"/>
+    </row>
+    <row r="161" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A161" s="102"/>
+      <c r="B161" s="103"/>
+      <c r="C161" s="108"/>
+      <c r="D161" s="104"/>
+      <c r="E161" s="104"/>
+      <c r="F161" s="100"/>
+    </row>
+    <row r="162" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A162" s="102"/>
+      <c r="B162" s="103"/>
+      <c r="C162" s="108"/>
+      <c r="D162" s="104"/>
+      <c r="E162" s="104"/>
+      <c r="F162" s="100"/>
+    </row>
+    <row r="163" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A163" s="102"/>
+      <c r="B163" s="103"/>
+      <c r="C163" s="108"/>
+      <c r="D163" s="104"/>
+      <c r="E163" s="104"/>
+      <c r="F163" s="100"/>
+    </row>
+    <row r="164" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A164" s="102"/>
+      <c r="B164" s="103"/>
+      <c r="C164" s="108"/>
+      <c r="D164" s="104"/>
+      <c r="E164" s="104"/>
+      <c r="F164" s="100"/>
+    </row>
+    <row r="165" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A165" s="102"/>
+      <c r="B165" s="103"/>
+      <c r="C165" s="108"/>
+      <c r="D165" s="104"/>
+      <c r="E165" s="104"/>
+      <c r="F165" s="100"/>
+    </row>
+    <row r="166" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A166" s="102"/>
+      <c r="B166" s="103"/>
+      <c r="C166" s="108"/>
+      <c r="D166" s="104"/>
+      <c r="E166" s="104"/>
+      <c r="F166" s="100"/>
+    </row>
+    <row r="167" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A167" s="102"/>
+      <c r="B167" s="103"/>
+      <c r="C167" s="108"/>
+      <c r="D167" s="104"/>
+      <c r="E167" s="104"/>
+      <c r="F167" s="100"/>
+    </row>
+    <row r="168" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A168" s="102"/>
+      <c r="B168" s="103"/>
+      <c r="C168" s="108"/>
+      <c r="D168" s="104"/>
+      <c r="E168" s="104"/>
+      <c r="F168" s="100"/>
+    </row>
+    <row r="169" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A169" s="102"/>
+      <c r="B169" s="103"/>
+      <c r="C169" s="108"/>
+      <c r="D169" s="104"/>
+      <c r="E169" s="104"/>
+      <c r="F169" s="100"/>
+    </row>
+    <row r="170" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A170" s="102"/>
+      <c r="B170" s="103"/>
+      <c r="C170" s="108"/>
+      <c r="D170" s="104"/>
+      <c r="E170" s="104"/>
+      <c r="F170" s="100"/>
+    </row>
+    <row r="171" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A171" s="102"/>
+      <c r="B171" s="103"/>
+      <c r="C171" s="108"/>
+      <c r="D171" s="104"/>
+      <c r="E171" s="104"/>
+      <c r="F171" s="100"/>
+    </row>
+    <row r="172" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A172" s="102"/>
+      <c r="B172" s="103"/>
+      <c r="C172" s="108"/>
+      <c r="D172" s="104"/>
+      <c r="E172" s="104"/>
+      <c r="F172" s="100"/>
+    </row>
+    <row r="173" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A173" s="102"/>
+      <c r="B173" s="103"/>
+      <c r="C173" s="108"/>
+      <c r="D173" s="104"/>
+      <c r="E173" s="104"/>
+      <c r="F173" s="100"/>
+    </row>
+    <row r="174" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A174" s="102"/>
+      <c r="B174" s="103"/>
+      <c r="C174" s="108"/>
+      <c r="D174" s="104"/>
+      <c r="E174" s="104"/>
+      <c r="F174" s="100"/>
+    </row>
+    <row r="175" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A175" s="102"/>
+      <c r="B175" s="103"/>
+      <c r="C175" s="108"/>
+      <c r="D175" s="104"/>
+      <c r="E175" s="104"/>
+      <c r="F175" s="100"/>
+    </row>
+    <row r="176" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A176" s="102"/>
+      <c r="B176" s="103"/>
+      <c r="C176" s="108"/>
+      <c r="D176" s="104"/>
+      <c r="E176" s="104"/>
+      <c r="F176" s="100"/>
+    </row>
+    <row r="177" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A177" s="102"/>
+      <c r="B177" s="103"/>
+      <c r="C177" s="108"/>
+      <c r="D177" s="104"/>
+      <c r="E177" s="104"/>
+      <c r="F177" s="100"/>
+    </row>
+    <row r="178" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A178" s="102"/>
+      <c r="B178" s="103"/>
+      <c r="C178" s="108"/>
+      <c r="D178" s="104"/>
+      <c r="E178" s="104"/>
+      <c r="F178" s="100"/>
+    </row>
+    <row r="179" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A179" s="102"/>
+      <c r="B179" s="103"/>
+      <c r="C179" s="108"/>
+      <c r="D179" s="104"/>
+      <c r="E179" s="104"/>
+      <c r="F179" s="100"/>
+    </row>
+    <row r="180" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A180" s="102"/>
+      <c r="B180" s="103"/>
+      <c r="C180" s="108"/>
+      <c r="D180" s="104"/>
+      <c r="E180" s="104"/>
+      <c r="F180" s="100"/>
+    </row>
+    <row r="181" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A181" s="102"/>
+      <c r="B181" s="103"/>
+      <c r="C181" s="108"/>
+      <c r="D181" s="104"/>
+      <c r="E181" s="104"/>
+      <c r="F181" s="100"/>
+    </row>
+    <row r="182" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A182" s="102"/>
+      <c r="B182" s="103"/>
+      <c r="C182" s="108"/>
+      <c r="D182" s="104"/>
+      <c r="E182" s="104"/>
+      <c r="F182" s="100"/>
+    </row>
+    <row r="183" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A183" s="102"/>
+      <c r="B183" s="103"/>
+      <c r="C183" s="108"/>
+      <c r="D183" s="104"/>
+      <c r="E183" s="104"/>
+      <c r="F183" s="100"/>
+    </row>
+    <row r="184" spans="1:6" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D184" s="19"/>
+      <c r="E184" s="19"/>
+    </row>
+    <row r="185" spans="1:6" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D185" s="19"/>
+      <c r="E185" s="19"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D186" s="19"/>
+      <c r="E186" s="19"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D187" s="19"/>
+      <c r="E187" s="19"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D188" s="19"/>
+      <c r="E188" s="19"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D189" s="19"/>
+      <c r="E189" s="19"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D190" s="19"/>
+      <c r="E190" s="19"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D191" s="19"/>
+      <c r="E191" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;G</oddHeader>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F00C344-2D59-6945-A5F8-608B01C1260C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>

--- a/Month YEAR - Body Motions.xlsx
+++ b/Month YEAR - Body Motions.xlsx
@@ -1,51 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyayas/VALD Automator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1603B5A5-D37C-A841-8713-9E5D7D4854C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6271E9-60DA-0745-9369-F76B2458B77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="REPORT 2" sheetId="10" r:id="rId1"/>
-    <sheet name="REPORT" sheetId="22" r:id="rId2"/>
-    <sheet name="RUH - Al Malaz" sheetId="8" r:id="rId3"/>
-    <sheet name="RUH - Al Sahafa" sheetId="7" r:id="rId4"/>
+    <sheet name="REPORT 2" sheetId="1" r:id="rId1"/>
+    <sheet name="REPORT" sheetId="2" r:id="rId2"/>
+    <sheet name="RUH - Al Malaz" sheetId="3" r:id="rId3"/>
+    <sheet name="RUH - Al Sahafa" sheetId="4" r:id="rId4"/>
     <sheet name="RUH - Al Aarid" sheetId="5" r:id="rId5"/>
     <sheet name="RUH - Al Fayha" sheetId="6" r:id="rId6"/>
-    <sheet name="RUH - Al Uraija" sheetId="13" r:id="rId7"/>
-    <sheet name="RUH - Badr" sheetId="14" r:id="rId8"/>
-    <sheet name="RUH - Al Badia" sheetId="15" r:id="rId9"/>
-    <sheet name="JED - Al Basateen" sheetId="3" r:id="rId10"/>
-    <sheet name="JED - Al Faisaliyah" sheetId="1" r:id="rId11"/>
-    <sheet name="JED - Al Naeem" sheetId="4" r:id="rId12"/>
-    <sheet name="JED - Obhor" sheetId="24" r:id="rId13"/>
-    <sheet name="DMM - Al Faisaliyah" sheetId="2" r:id="rId14"/>
-    <sheet name="DMM - Al Jalawiah" sheetId="18" r:id="rId15"/>
-    <sheet name="DMM - Al Nada" sheetId="23" r:id="rId16"/>
-    <sheet name="ALQ - Buraidah" sheetId="16" r:id="rId17"/>
-    <sheet name="ALQ - Unaizah" sheetId="17" r:id="rId18"/>
-    <sheet name="Al Ahsaa" sheetId="19" r:id="rId19"/>
-    <sheet name="AlUla" sheetId="21" r:id="rId20"/>
-    <sheet name="Tabuk" sheetId="20" r:id="rId21"/>
+    <sheet name="RUH - Al Uraija" sheetId="7" r:id="rId7"/>
+    <sheet name="RUH - Badr" sheetId="8" r:id="rId8"/>
+    <sheet name="RUH - Al Badia" sheetId="9" r:id="rId9"/>
+    <sheet name="JED - Al Basateen" sheetId="10" r:id="rId10"/>
+    <sheet name="JED - Al Faisaliyah" sheetId="11" r:id="rId11"/>
+    <sheet name="JED - Al Naeem" sheetId="12" r:id="rId12"/>
+    <sheet name="JED - Obhor" sheetId="13" r:id="rId13"/>
+    <sheet name="DMM - Al Faisaliyah" sheetId="14" r:id="rId14"/>
+    <sheet name="DMM - Al Jalawiah" sheetId="15" r:id="rId15"/>
+    <sheet name="DMM - Al Nada" sheetId="16" r:id="rId16"/>
+    <sheet name="ALQ - Al Rayyan" sheetId="23" r:id="rId17"/>
+    <sheet name="ALQ - Buraidah" sheetId="18" r:id="rId18"/>
+    <sheet name="ALQ - Unaizah" sheetId="19" r:id="rId19"/>
+    <sheet name="Al Ahsaa" sheetId="20" r:id="rId20"/>
+    <sheet name="AlUla" sheetId="21" r:id="rId21"/>
+    <sheet name="Tabuk" sheetId="22" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">REPORT!$B$1:$B$363</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">REPORT!$A$1:$D$217</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'REPORT 2'!$A$1:$G$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'REPORT 2'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -61,192 +58,60 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="212">
   <si>
     <t>REPORT DATE:</t>
   </si>
   <si>
-    <t>NUMBER OF PROGRAMS:</t>
+    <t>MONTHLY TOTAL:</t>
   </si>
   <si>
-    <t xml:space="preserve">CLIENT NAME
+    <t xml:space="preserve">CLUB NAME
 </t>
   </si>
   <si>
-    <t>TRAINER NAME</t>
+    <t>LAST 7 DAYS</t>
   </si>
   <si>
-    <t>DATE OF TEST</t>
+    <t>MONTH TO DATE</t>
   </si>
   <si>
-    <t>DATE OF PROGRAM DISPATCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسم العميل
-</t>
-  </si>
-  <si>
-    <t>اسم المدرّب</t>
-  </si>
-  <si>
-    <t>تاريخ الفحص</t>
-  </si>
-  <si>
-    <t>تاريخ ارسال الجدول</t>
-  </si>
-  <si>
-    <t>Moroj Samir Abdel Hamid</t>
-  </si>
-  <si>
-    <t>Shurooq Amer</t>
-  </si>
-  <si>
-    <t>Kholod Khaled</t>
-  </si>
-  <si>
-    <t>Iman Kouisseh</t>
-  </si>
-  <si>
-    <t>Nadine Ghaleb</t>
-  </si>
-  <si>
-    <t>Asmaa Ahmed</t>
-  </si>
-  <si>
-    <t>Asmaa Adel</t>
-  </si>
-  <si>
-    <t>Ines Rezgui</t>
-  </si>
-  <si>
-    <t>Maha Fayez Al Ahmari</t>
-  </si>
-  <si>
-    <t>Ikram Gueddes</t>
-  </si>
-  <si>
-    <t>Shefa Ghazi</t>
-  </si>
-  <si>
-    <t>Sirine Mohamed Hamdi</t>
-  </si>
-  <si>
-    <t>Hadir Nasr Mohamed</t>
-  </si>
-  <si>
-    <t>Wiem Dridi</t>
-  </si>
-  <si>
-    <t>Shourooq Al Jundi</t>
-  </si>
-  <si>
-    <t>Kholoud Khaled</t>
-  </si>
-  <si>
-    <t>Rania Manita</t>
-  </si>
-  <si>
-    <t>Sirine Jawadi</t>
-  </si>
-  <si>
-    <t>Soulaima Hassan</t>
-  </si>
-  <si>
-    <t>Cyrine Ali</t>
-  </si>
-  <si>
-    <t>Asmaa Shehata</t>
-  </si>
-  <si>
-    <t>Manel Manasria</t>
-  </si>
-  <si>
-    <t>Sabrine Al Amine</t>
-  </si>
-  <si>
-    <t>Mouna Farhat</t>
-  </si>
-  <si>
-    <t>Salwa Mlaiki</t>
-  </si>
-  <si>
-    <t>Hind Al Ahmad</t>
-  </si>
-  <si>
-    <t>Safa Al Saggadi</t>
-  </si>
-  <si>
-    <t>Walaa Kamel</t>
-  </si>
-  <si>
-    <t>Al Bandari Al Harbi</t>
-  </si>
-  <si>
-    <t>Hala Saied</t>
-  </si>
-  <si>
-    <t>Nahla Al Hajri</t>
-  </si>
-  <si>
-    <t>Hidaya Moubarak</t>
-  </si>
-  <si>
-    <t>Taghrid Khaled</t>
-  </si>
-  <si>
-    <t>Warda Al Hajji</t>
-  </si>
-  <si>
-    <t>RUH - Al Fayha</t>
+    <t>YEAR TO DATE</t>
   </si>
   <si>
     <t xml:space="preserve">اسم النادي
 </t>
   </si>
   <si>
-    <t xml:space="preserve">CLUB NAME
-</t>
+    <t>آخر 7 أيام</t>
+  </si>
+  <si>
+    <t>منذ بداية الشهر حتى اليوم</t>
   </si>
   <si>
     <t>منذ بداية السنة حتى اليوم</t>
   </si>
   <si>
-    <t>منذ بداية الشهر حتى اليوم</t>
+    <t>RUH - Al Malaz</t>
   </si>
   <si>
-    <t>آخر 7 أيام</t>
+    <t>RUH - Al Sahafa</t>
   </si>
   <si>
-    <t>YEAR TO DATE</t>
+    <t>RUH - Al Aarid</t>
   </si>
   <si>
-    <t>MONTH TO DATE</t>
+    <t>RUH - Al Fayha</t>
   </si>
   <si>
-    <t>LAST 7 DAYS</t>
+    <t>RUH - Al Uraija</t>
+  </si>
+  <si>
+    <t>RUH - Badr</t>
+  </si>
+  <si>
+    <t>RUH - Al Badia</t>
   </si>
   <si>
     <t>JED - Al Basateen</t>
@@ -258,61 +123,169 @@
     <t>JED - Al Naeem</t>
   </si>
   <si>
-    <t>RUH - Al Aarid</t>
+    <t>JED - Obhor</t>
   </si>
   <si>
     <t>DMM - Al Faisaliyah</t>
   </si>
   <si>
+    <t>DMM - Al Jalawiah</t>
+  </si>
+  <si>
+    <t>DMM - Al Nada</t>
+  </si>
+  <si>
+    <t>ALQ - Buraidah</t>
+  </si>
+  <si>
+    <t>ALQ - Unaizah</t>
+  </si>
+  <si>
+    <t>Al Ahsaa</t>
+  </si>
+  <si>
+    <t>AlUla</t>
+  </si>
+  <si>
+    <t>Tabuk</t>
+  </si>
+  <si>
+    <t>TRAINER NAME</t>
+  </si>
+  <si>
+    <t>اسم المدرّب</t>
+  </si>
+  <si>
+    <t>Abir Salloum</t>
+  </si>
+  <si>
+    <t>Faemeh Al Seraji</t>
+  </si>
+  <si>
+    <t>Ikram Gueddes</t>
+  </si>
+  <si>
+    <t>Latoya Fantisi</t>
+  </si>
+  <si>
+    <t>Mariam Jahin</t>
+  </si>
+  <si>
+    <t>Moroj Samir Abdel Hamid</t>
+  </si>
+  <si>
+    <t>Nadine Ghaleb</t>
+  </si>
+  <si>
+    <t>Sarah Shaabane</t>
+  </si>
+  <si>
+    <t>Loel Du Bruyn</t>
+  </si>
+  <si>
+    <t>Taghrid Khaled</t>
+  </si>
+  <si>
+    <t>Shayma Hanashi</t>
+  </si>
+  <si>
+    <t>Nwabisa Liwane</t>
+  </si>
+  <si>
+    <t>Areej Hajj Abdallah</t>
+  </si>
+  <si>
+    <t>Hadir Nasr Mohamed</t>
+  </si>
+  <si>
+    <t>Taif Saad Alahmari</t>
+  </si>
+  <si>
+    <t>Zouhaira Al-Omrani</t>
+  </si>
+  <si>
+    <t>Shefa Ghazi</t>
+  </si>
+  <si>
+    <t>Manel Manasria</t>
+  </si>
+  <si>
+    <t>Abeer Al Saloum</t>
+  </si>
+  <si>
+    <t>Rania Manita</t>
+  </si>
+  <si>
+    <t>Kholoud Khaled</t>
+  </si>
+  <si>
     <t>Guesmi Kholoud</t>
+  </si>
+  <si>
+    <t>Nashwa Attia Elbendary</t>
+  </si>
+  <si>
+    <t>Sirine Mohamed Hamdi</t>
+  </si>
+  <si>
+    <t>Maram Tlili</t>
+  </si>
+  <si>
+    <t>Sara Said</t>
+  </si>
+  <si>
+    <t>Malek Belguith</t>
+  </si>
+  <si>
+    <t>Safaa Karim</t>
+  </si>
+  <si>
+    <t>Amal Al Chiboub</t>
+  </si>
+  <si>
+    <t>Hidaya Moubarak</t>
+  </si>
+  <si>
+    <t>Safa Al Saggadi</t>
+  </si>
+  <si>
+    <t>Warda Al Hajji</t>
+  </si>
+  <si>
+    <t>Maryam Al-Qawsari</t>
+  </si>
+  <si>
+    <t>Fawz Jibran Al-Qahtani</t>
+  </si>
+  <si>
+    <t>Malak Al Zahabi</t>
+  </si>
+  <si>
+    <t>Nada Mohamed Khalifa</t>
+  </si>
+  <si>
+    <t>Chaza Ben Miled</t>
   </si>
   <si>
     <t>Shaden Omar</t>
   </si>
   <si>
-    <t>Taif Saad Alahmari</t>
+    <t>Walaa Kamel</t>
   </si>
   <si>
-    <t>Areej Hajj Abdallah</t>
+    <t>Hind Al Ahmad</t>
   </si>
   <si>
-    <t>Sarah Shaabane</t>
+    <t>Asmaa Adel</t>
   </si>
   <si>
-    <t>Rania Bahloul</t>
+    <t>Maram Al Sousou</t>
   </si>
   <si>
-    <t>Sara Said</t>
+    <t>Asmaa Ahmed</t>
   </si>
   <si>
-    <t>Maram Tlili</t>
-  </si>
-  <si>
-    <t>Raghad Al Bir Qaddar</t>
-  </si>
-  <si>
-    <t>Asayel Sultan</t>
-  </si>
-  <si>
-    <t>Maysem Mohamed</t>
-  </si>
-  <si>
-    <t>Lamia Al Amer</t>
-  </si>
-  <si>
-    <t>Shayma Abbes</t>
-  </si>
-  <si>
-    <t>Sara Mahdi</t>
-  </si>
-  <si>
-    <t>Diaa Sobhi</t>
-  </si>
-  <si>
-    <t>Chourouk Sherif</t>
-  </si>
-  <si>
-    <t>Maryam Al-Qawsari</t>
+    <t>Ebtihal Al Kathiri</t>
   </si>
   <si>
     <t>Feryel Ben Nacer</t>
@@ -321,79 +294,217 @@
     <t>Al Anoud Saleh Al-Qablan</t>
   </si>
   <si>
-    <t>Ebtihal Al Kathiri</t>
+    <t>Khawla Saif</t>
+  </si>
+  <si>
+    <t>Basnat Abdel Qawi</t>
+  </si>
+  <si>
+    <t>Sanae Hassel</t>
+  </si>
+  <si>
+    <t>Khouloud Wanna</t>
+  </si>
+  <si>
+    <t>Hadiya Al-Mohammad</t>
+  </si>
+  <si>
+    <t>Aya Al-Jallouli</t>
+  </si>
+  <si>
+    <t>Rania Bahloul</t>
+  </si>
+  <si>
+    <t>Shorouq Osama Metwaly Ibrahim</t>
+  </si>
+  <si>
+    <t>Arwa Ahmed Baflah</t>
+  </si>
+  <si>
+    <t>Hadeer Ibrahim Gamal</t>
+  </si>
+  <si>
+    <t>Rihem Hossam</t>
+  </si>
+  <si>
+    <t>Sarah Ghoneim</t>
+  </si>
+  <si>
+    <t>Al-Hanouf Al-Khurayan</t>
+  </si>
+  <si>
+    <t>Amal Al-Bjeoui</t>
+  </si>
+  <si>
+    <t>Seham Hussein</t>
+  </si>
+  <si>
+    <t>Maysaa Mowafaq Al-Aqram</t>
+  </si>
+  <si>
+    <t>Takwa Abdelly</t>
+  </si>
+  <si>
+    <t>Hasna AlKayyal</t>
+  </si>
+  <si>
+    <t>Souha Al-Bajawi</t>
+  </si>
+  <si>
+    <t>Hanin Barrani</t>
+  </si>
+  <si>
+    <t>Safa Radif</t>
+  </si>
+  <si>
+    <t>Maram Farhawi</t>
+  </si>
+  <si>
+    <t>Rajae Al-Jabouji</t>
+  </si>
+  <si>
+    <t>Ghofran Bint Kamal Aouni</t>
+  </si>
+  <si>
+    <t>Nermin Hadi Debaya</t>
+  </si>
+  <si>
+    <t>Nawres Khordeni</t>
+  </si>
+  <si>
+    <t>Raghad Al Bir Qaddar</t>
+  </si>
+  <si>
+    <t>Iman Kouisseh</t>
+  </si>
+  <si>
+    <t>Salwa Mlaiki</t>
+  </si>
+  <si>
+    <t>Sabrine Al Amine</t>
+  </si>
+  <si>
+    <t>Mouna Farhat</t>
+  </si>
+  <si>
+    <t>Moutidis Ofantisi</t>
+  </si>
+  <si>
+    <t>Shurooq Amer</t>
+  </si>
+  <si>
+    <t>Reyouf Saad</t>
+  </si>
+  <si>
+    <t>Ranim Brahmi</t>
+  </si>
+  <si>
+    <t>Maha Fayez Al Ahmari</t>
+  </si>
+  <si>
+    <t>Salma Jadli</t>
+  </si>
+  <si>
+    <t>Hala Saied</t>
+  </si>
+  <si>
+    <t>Kholod Khaled</t>
+  </si>
+  <si>
+    <t>Wiem Dridi</t>
+  </si>
+  <si>
+    <t>Shourooq Al Jundi</t>
+  </si>
+  <si>
+    <t>Ines Rezgui</t>
+  </si>
+  <si>
+    <t>Hajer Jamal Al-Deen Khalifa Ali</t>
+  </si>
+  <si>
+    <t>Mariam Baomar</t>
+  </si>
+  <si>
+    <t>Chourouk Sherif</t>
+  </si>
+  <si>
+    <t>Sara Mahdi</t>
+  </si>
+  <si>
+    <t>Siwar Al Habib</t>
+  </si>
+  <si>
+    <t>Shayma Abbes</t>
+  </si>
+  <si>
+    <t>Nahla Al Hajri</t>
+  </si>
+  <si>
+    <t>Afraa Almasri</t>
+  </si>
+  <si>
+    <t>Lamia Al Amer</t>
+  </si>
+  <si>
+    <t>Diaa Sobhi</t>
+  </si>
+  <si>
+    <t>Maysem Mohamed</t>
+  </si>
+  <si>
+    <t>Asayel Sultan</t>
+  </si>
+  <si>
+    <t>Nadine Shawky</t>
+  </si>
+  <si>
+    <t>Mayssa Bin Mohamad Nasser Mejri</t>
+  </si>
+  <si>
+    <t>Rasha Hamid</t>
+  </si>
+  <si>
+    <t>Amira Omar</t>
+  </si>
+  <si>
+    <t>Soulaima Hassan</t>
+  </si>
+  <si>
+    <t>Cyrine Ali</t>
+  </si>
+  <si>
+    <t>Sirine Jawadi</t>
   </si>
   <si>
     <t>Moulouk Al Lawi</t>
   </si>
   <si>
-    <t>Rasha Hamid</t>
-  </si>
-  <si>
     <t>Nourhan Hosny</t>
   </si>
   <si>
-    <t>Malak Al Zahabi</t>
-  </si>
-  <si>
-    <t>Reyouf Saad</t>
+    <t>Al Bandari Al Harbi</t>
   </si>
   <si>
     <t>Mirna Mostafa</t>
   </si>
   <si>
-    <t>Nada Mohamed Khalifa</t>
+    <t>Mariem Laamiri</t>
   </si>
   <si>
-    <t>RUH - Al Sahafa</t>
-  </si>
-  <si>
-    <t>RUH - Al Malaz</t>
-  </si>
-  <si>
-    <t>Al Ahsaa</t>
-  </si>
-  <si>
-    <t>DMM - Al Jalawiah</t>
-  </si>
-  <si>
-    <t>ALQ - Unaizah</t>
-  </si>
-  <si>
-    <t>ALQ - Buraidah</t>
-  </si>
-  <si>
-    <t>RUH - Al Badia</t>
-  </si>
-  <si>
-    <t>RUH - Badr</t>
-  </si>
-  <si>
-    <t>RUH - Al Uraija</t>
-  </si>
-  <si>
-    <t>Iman Aboushosha</t>
-  </si>
-  <si>
-    <t>Amina Mohammad Mosbeh</t>
-  </si>
-  <si>
-    <t>Marwa Almudyni</t>
-  </si>
-  <si>
-    <t>Afnan Khalid</t>
-  </si>
-  <si>
-    <t>Mona Maatouq</t>
-  </si>
-  <si>
-    <t>Samar Mohammed</t>
+    <t>Rahma Qays</t>
   </si>
   <si>
     <t>Asmaa Mahmoud</t>
   </si>
   <si>
-    <t>Chaima Boutita</t>
+    <t>Basma Baza</t>
+  </si>
+  <si>
+    <t>Mennatllah Saad</t>
+  </si>
+  <si>
+    <t>Wyssal Ben Dhieb</t>
   </si>
   <si>
     <t>Asmaa Ashraf</t>
@@ -402,7 +513,70 @@
     <t>Chaima Gharsalli</t>
   </si>
   <si>
+    <t>Fatima Abdallah</t>
+  </si>
+  <si>
     <t>Emna Ben Chalbia</t>
+  </si>
+  <si>
+    <t>Hebatallah Ali</t>
+  </si>
+  <si>
+    <t>Aya Maayoufi</t>
+  </si>
+  <si>
+    <t>Amal Al-Fahat Ghazi Al-Ruwaili</t>
+  </si>
+  <si>
+    <t>Chaima Boutita</t>
+  </si>
+  <si>
+    <t>Asmaa Shehata</t>
+  </si>
+  <si>
+    <t>Sarah Rasheeq</t>
+  </si>
+  <si>
+    <t>Nawal Akermi</t>
+  </si>
+  <si>
+    <t>Rawiya Alarousi Mabrouk</t>
+  </si>
+  <si>
+    <t>Anfal Nasser Alhusseini</t>
+  </si>
+  <si>
+    <t>Nourhan Ehab Amarah</t>
+  </si>
+  <si>
+    <t>Nouran Emad Jad</t>
+  </si>
+  <si>
+    <t>Lulu Alzaaj</t>
+  </si>
+  <si>
+    <t>Malath Suleiman Alshamasi</t>
+  </si>
+  <si>
+    <t>Chayma Hannachi</t>
+  </si>
+  <si>
+    <t>Mai Mosleh</t>
+  </si>
+  <si>
+    <t>Ines Souissi</t>
+  </si>
+  <si>
+    <t>Anwar Ben Rhayem</t>
+  </si>
+  <si>
+    <t>Raja Reeba</t>
+  </si>
+  <si>
+    <t>Aya Mahmoud Abed Al-Wanis</t>
+  </si>
+  <si>
+    <t>Eilaf Mohamed Al-Fayizi</t>
   </si>
   <si>
     <t>Rana Mohammad Hassan Aaref</t>
@@ -423,282 +597,25 @@
     <t>Samar Lajnef</t>
   </si>
   <si>
-    <t>Rawiya Alarousi Mabrouk</t>
-  </si>
-  <si>
-    <t>Anfal Nasser Alhusseini</t>
-  </si>
-  <si>
-    <t>Nourhan Ehab Amarah</t>
-  </si>
-  <si>
-    <t>Nouran Emad Jad</t>
-  </si>
-  <si>
-    <t>Ines Souissi</t>
-  </si>
-  <si>
-    <t>Lulu Alzaaj</t>
-  </si>
-  <si>
-    <t>Malath Suleiman Alshamasi</t>
-  </si>
-  <si>
-    <t>Chayma Hannachi</t>
-  </si>
-  <si>
-    <t>Mai Mosleh</t>
-  </si>
-  <si>
-    <t>Takwa Abdelly</t>
-  </si>
-  <si>
-    <t>Hasna AlKayyal</t>
-  </si>
-  <si>
-    <t>Hanin Barrani</t>
-  </si>
-  <si>
-    <t>Safa Radif</t>
-  </si>
-  <si>
-    <t>Maram Farhawi</t>
-  </si>
-  <si>
-    <t>Rajae Al-Jabouji</t>
-  </si>
-  <si>
-    <t>Shorouq Osama Metwaly Ibrahim</t>
-  </si>
-  <si>
-    <t>Arwa Ahmed Baflah</t>
-  </si>
-  <si>
-    <t>Hadeer Ibrahim Gamal</t>
-  </si>
-  <si>
-    <t>Rihem Hossam</t>
-  </si>
-  <si>
-    <t>Amal Al-Bjeoui</t>
-  </si>
-  <si>
-    <t>Nawal Akermi</t>
-  </si>
-  <si>
-    <t>Seham Hussein</t>
-  </si>
-  <si>
-    <t>Basnat Abdel Qawi</t>
-  </si>
-  <si>
-    <t>Sanae Hassel</t>
-  </si>
-  <si>
-    <t>Sarah Rasheeq</t>
-  </si>
-  <si>
-    <t>Khouloud Wanna</t>
-  </si>
-  <si>
-    <t>Hadiya Al-Mohammad</t>
-  </si>
-  <si>
-    <t>Aya Al-Jallouli</t>
-  </si>
-  <si>
-    <t>AlUla</t>
-  </si>
-  <si>
-    <t>Tabuk</t>
-  </si>
-  <si>
-    <t>Amal Saad</t>
-  </si>
-  <si>
-    <t>Bassant Majed Eid</t>
-  </si>
-  <si>
-    <t>Marwa Jendoubi</t>
-  </si>
-  <si>
-    <t>Sahar Mrad Berguiga</t>
-  </si>
-  <si>
-    <t>Ishraf Mohamed Al-Zaghdoudi</t>
-  </si>
-  <si>
-    <t>Nada Ahmed Mohamed</t>
-  </si>
-  <si>
-    <t>Rasha Abu Hassan</t>
-  </si>
-  <si>
-    <t>Walaa Ahmed</t>
-  </si>
-  <si>
-    <t>Amal Saleh</t>
-  </si>
-  <si>
-    <t>Bayan Al-Anzi</t>
-  </si>
-  <si>
-    <t>Rehab Naji Al-Nasri</t>
-  </si>
-  <si>
-    <t>Khouloud Suibgui</t>
-  </si>
-  <si>
-    <t>Anwar Ben Rhayem</t>
-  </si>
-  <si>
-    <t>MONTHLY TOTAL:</t>
-  </si>
-  <si>
-    <t>Malek Belguith</t>
-  </si>
-  <si>
-    <t>Ranim Brahmi</t>
-  </si>
-  <si>
-    <t>Nermin Hadi Debaya</t>
-  </si>
-  <si>
-    <t>Chaza Ben Miled</t>
-  </si>
-  <si>
-    <t>Aya Maayoufi</t>
-  </si>
-  <si>
-    <t>Raja Reeba</t>
-  </si>
-  <si>
-    <t>Hajer Jamal Al-Deen Khalifa Ali</t>
-  </si>
-  <si>
     <t>Rim Chabi</t>
   </si>
   <si>
-    <t>Mariam Baomar</t>
+    <t>Iman Aboushosha</t>
   </si>
   <si>
-    <t>Rahma Qays</t>
+    <t>Marwa Almudyni</t>
   </si>
   <si>
-    <t>Khawla Saif</t>
+    <t>Afnan Khalid</t>
   </si>
   <si>
-    <t>Zouhaira Al-Omrani</t>
-  </si>
-  <si>
-    <t>Aya Mahmoud Abed Al-Wanis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIENT ID
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رقم العميل
-</t>
-  </si>
-  <si>
-    <t>Safaa Karim</t>
-  </si>
-  <si>
-    <t>Abir Salloum</t>
-  </si>
-  <si>
-    <t>Faemeh Al Seraji</t>
-  </si>
-  <si>
-    <t>Latoya Fantisi</t>
-  </si>
-  <si>
-    <t>Mariam Jahin</t>
-  </si>
-  <si>
-    <t>Loel Du Bruyn</t>
-  </si>
-  <si>
-    <t>Shayma Hanashi</t>
-  </si>
-  <si>
-    <t>Nwabisa Liwane</t>
-  </si>
-  <si>
-    <t>Abeer Al Saloum</t>
-  </si>
-  <si>
-    <t>Nashwa Attia Elbendary</t>
-  </si>
-  <si>
-    <t>Amal Al Chiboub</t>
-  </si>
-  <si>
-    <t>Fawz Jibran Al-Qahtani</t>
-  </si>
-  <si>
-    <t>Maram Al Sousou</t>
-  </si>
-  <si>
-    <t>Sarah Ghoneim</t>
-  </si>
-  <si>
-    <t>Al-Hanouf Al-Khurayan</t>
-  </si>
-  <si>
-    <t>Maysaa Mowafaq Al-Aqram</t>
-  </si>
-  <si>
-    <t>Souha Al-Bajawi</t>
-  </si>
-  <si>
-    <t>Ghofran Bint Kamal Aouni</t>
-  </si>
-  <si>
-    <t>Nawres Khordeni</t>
-  </si>
-  <si>
-    <t>Moutidis Ofantisi</t>
-  </si>
-  <si>
-    <t>Salma Jadli</t>
-  </si>
-  <si>
-    <t>Siwar Al Habib</t>
-  </si>
-  <si>
-    <t>Afraa Almasri</t>
-  </si>
-  <si>
-    <t>Nadine Shawky</t>
-  </si>
-  <si>
-    <t>Mayssa Bin Mohamad Nasser Mejri</t>
-  </si>
-  <si>
-    <t>Amira Omar</t>
-  </si>
-  <si>
-    <t>Mariem Laamiri</t>
-  </si>
-  <si>
-    <t>Basma Baza</t>
-  </si>
-  <si>
-    <t>Mennatllah Saad</t>
-  </si>
-  <si>
-    <t>Fatima Abdallah</t>
-  </si>
-  <si>
-    <t>Hebatallah Ali</t>
-  </si>
-  <si>
-    <t>Eilaf Mohamed Al-Fayizi</t>
+    <t>Mona Maatouq</t>
   </si>
   <si>
     <t>Sohaila Refaat</t>
+  </si>
+  <si>
+    <t>Samar Mohammed</t>
   </si>
   <si>
     <t>Esraa Idris</t>
@@ -710,22 +627,80 @@
     <t>Habiba Alghareeb</t>
   </si>
   <si>
+    <t>Amina Mohammad Mosbeh</t>
+  </si>
+  <si>
     <t>Nour Toumi</t>
+  </si>
+  <si>
+    <t>Khouloud Suibgui</t>
+  </si>
+  <si>
+    <t>Rehab Naji Al-Nasri</t>
+  </si>
+  <si>
+    <t>Bayan Al-Anzi</t>
+  </si>
+  <si>
+    <t>Amal Saleh</t>
+  </si>
+  <si>
+    <t>Walaa Ahmed</t>
+  </si>
+  <si>
+    <t>Rasha Abu Hassan</t>
+  </si>
+  <si>
+    <t>Nada Ahmed Mohamed</t>
+  </si>
+  <si>
+    <t>Ishraf Mohamed Al-Zaghdoudi</t>
+  </si>
+  <si>
+    <t>Sahar Mrad Berguiga</t>
+  </si>
+  <si>
+    <t>Marwa Jendoubi</t>
+  </si>
+  <si>
+    <t>Bassant Majed Eid</t>
+  </si>
+  <si>
+    <t>Amal Saad</t>
   </si>
   <si>
     <t>Hanane Bankroum</t>
   </si>
   <si>
-    <t>DMM - Al Nada</t>
+    <t>NUMBER OF PROGRAMS:</t>
   </si>
   <si>
-    <t>Amal Al-Fahat Ghazi Al-Ruwaili</t>
+    <t xml:space="preserve">CLIENT ID
+</t>
   </si>
   <si>
-    <t>Wyssal Ben Dhieb</t>
+    <t xml:space="preserve">CLIENT NAME
+</t>
   </si>
   <si>
-    <t>JED - Obhor</t>
+    <t>DATE OF TEST</t>
+  </si>
+  <si>
+    <t>DATE OF PROGRAM DISPATCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رقم العميل
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسم العميل
+</t>
+  </si>
+  <si>
+    <t>تاريخ الفحص</t>
+  </si>
+  <si>
+    <t>تاريخ ارسال الجدول</t>
   </si>
 </sst>
 </file>
@@ -1475,22 +1450,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFF2F2F2"/>
-      <color rgb="FF4B858F"/>
-      <color rgb="FFF2BB46"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1776,7 +1742,8 @@
     <col min="6" max="6" width="5.5" customWidth="1"/>
     <col min="7" max="7" width="40.6640625" style="1" customWidth="1"/>
     <col min="8" max="11" width="5.5" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="1"/>
+    <col min="12" max="12" width="8.6640625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -1797,7 +1764,7 @@
         <v>46119</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="D3" s="89">
         <f ca="1">SUM(C7:C25)</f>
@@ -1811,43 +1778,43 @@
     </row>
     <row r="5" spans="1:16" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="53" t="s">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="D5" s="55" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:16" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="F6" s="10"/>
     </row>
     <row r="7" spans="1:16" s="15" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="57" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="B7" s="37">
         <f t="shared" ref="B7:B25" ca="1" si="0">IFERROR(COUNTIFS(INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&gt;=" &amp; $B$3-7, INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&lt;=" &amp; $B$3),0)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="36" cm="1">
+      <c r="C7" s="36">
         <f t="array" aca="1" ref="C7" ca="1">INDIRECT("'" &amp; A7 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -1870,13 +1837,13 @@
     </row>
     <row r="8" spans="1:16" s="14" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="57" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="B8" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="36" cm="1">
+      <c r="C8" s="36">
         <f t="array" aca="1" ref="C8" ca="1">INDIRECT("'" &amp; A8 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -1899,13 +1866,13 @@
     </row>
     <row r="9" spans="1:16" s="14" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="57" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="B9" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9" s="36" cm="1">
+      <c r="C9" s="36">
         <f t="array" aca="1" ref="C9" ca="1">INDIRECT("'" &amp; A9 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -1917,13 +1884,13 @@
     </row>
     <row r="10" spans="1:16" s="14" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="31" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B10" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C10" s="36" cm="1">
+      <c r="C10" s="36">
         <f t="array" aca="1" ref="C10" ca="1">INDIRECT("'" &amp; A10 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -1935,13 +1902,13 @@
     </row>
     <row r="11" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="57" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="B11" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="36" cm="1">
+      <c r="C11" s="36">
         <f t="array" aca="1" ref="C11" ca="1">INDIRECT("'" &amp; A11 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -1954,13 +1921,13 @@
     </row>
     <row r="12" spans="1:16" s="14" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="57" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="B12" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="36" cm="1">
+      <c r="C12" s="36">
         <f t="array" aca="1" ref="C12" ca="1">INDIRECT("'" &amp; A12 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -1972,13 +1939,13 @@
     </row>
     <row r="13" spans="1:16" s="14" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="57" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="B13" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="36" cm="1">
+      <c r="C13" s="36">
         <f t="array" aca="1" ref="C13" ca="1">INDIRECT("'" &amp; A13 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -1990,13 +1957,13 @@
     </row>
     <row r="14" spans="1:16" s="15" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="57" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B14" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="36" cm="1">
+      <c r="C14" s="36">
         <f t="array" aca="1" ref="C14" ca="1">INDIRECT("'" &amp; A14 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2017,15 +1984,15 @@
       <c r="O14" s="16"/>
       <c r="P14" s="16"/>
     </row>
-    <row r="15" spans="1:16" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="58" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="B15" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C15" s="36" cm="1">
+      <c r="C15" s="36">
         <f t="array" aca="1" ref="C15" ca="1">INDIRECT("'" &amp; A15 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2035,15 +2002,15 @@
       </c>
       <c r="E15" s="17"/>
     </row>
-    <row r="16" spans="1:16" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="57" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="B16" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C16" s="36" cm="1">
+      <c r="C16" s="36">
         <f t="array" aca="1" ref="C16" ca="1">INDIRECT("'" &amp; A16 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2053,15 +2020,15 @@
       </c>
       <c r="E16" s="17"/>
     </row>
-    <row r="17" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="57" t="s">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="B17" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C17" s="36" cm="1">
+      <c r="C17" s="36">
         <f t="array" aca="1" ref="C17" ca="1">INDIRECT("'" &amp; A17 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2071,15 +2038,15 @@
       </c>
       <c r="E17" s="17"/>
     </row>
-    <row r="18" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="31" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="B18" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C18" s="36" cm="1">
+      <c r="C18" s="36">
         <f t="array" aca="1" ref="C18" ca="1">INDIRECT("'" &amp; A18 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2089,15 +2056,15 @@
       </c>
       <c r="E18" s="17"/>
     </row>
-    <row r="19" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="57" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="B19" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C19" s="36" cm="1">
+      <c r="C19" s="36">
         <f t="array" aca="1" ref="C19" ca="1">INDIRECT("'" &amp; A19 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2107,15 +2074,15 @@
       </c>
       <c r="E19" s="17"/>
     </row>
-    <row r="20" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="57" t="s">
-        <v>208</v>
+        <v>23</v>
       </c>
       <c r="B20" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C20" s="36" cm="1">
+      <c r="C20" s="36">
         <f t="array" aca="1" ref="C20" ca="1">INDIRECT("'" &amp; A20 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2125,15 +2092,15 @@
       </c>
       <c r="E20" s="17"/>
     </row>
-    <row r="21" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="58" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="B21" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C21" s="36" cm="1">
+      <c r="C21" s="36">
         <f t="array" aca="1" ref="C21" ca="1">INDIRECT("'" &amp; A21 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2143,15 +2110,15 @@
       </c>
       <c r="E21" s="17"/>
     </row>
-    <row r="22" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="31" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="B22" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C22" s="36" cm="1">
+      <c r="C22" s="36">
         <f t="array" aca="1" ref="C22" ca="1">INDIRECT("'" &amp; A22 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2161,15 +2128,15 @@
       </c>
       <c r="E22" s="17"/>
     </row>
-    <row r="23" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="57" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="B23" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C23" s="36" cm="1">
+      <c r="C23" s="36">
         <f t="array" aca="1" ref="C23" ca="1">INDIRECT("'" &amp; A23 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2179,15 +2146,15 @@
       </c>
       <c r="E23" s="17"/>
     </row>
-    <row r="24" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="31" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="B24" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C24" s="36" cm="1">
+      <c r="C24" s="36">
         <f t="array" aca="1" ref="C24" ca="1">INDIRECT("'" &amp; A24 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2197,15 +2164,15 @@
       </c>
       <c r="E24" s="17"/>
     </row>
-    <row r="25" spans="1:5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="57" t="s">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="B25" s="37">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="C25" s="36" cm="1">
+      <c r="C25" s="36">
         <f t="array" aca="1" ref="C25" ca="1">INDIRECT("'" &amp; A25 &amp; "'!D3")</f>
         <v>0</v>
       </c>
@@ -2215,354 +2182,354 @@
       </c>
       <c r="E25" s="17"/>
     </row>
-    <row r="26" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="35"/>
       <c r="D26" s="35"/>
       <c r="E26" s="17"/>
     </row>
-    <row r="27" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="35"/>
       <c r="D27" s="35"/>
       <c r="E27" s="17"/>
     </row>
-    <row r="28" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="35"/>
       <c r="D28" s="35"/>
       <c r="E28" s="17"/>
     </row>
-    <row r="29" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="35"/>
       <c r="D29" s="35"/>
       <c r="E29" s="17"/>
     </row>
-    <row r="30" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="35"/>
       <c r="D30" s="35"/>
       <c r="E30" s="17"/>
     </row>
-    <row r="31" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="35"/>
       <c r="D31" s="35"/>
       <c r="E31" s="17"/>
     </row>
-    <row r="32" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="35"/>
       <c r="D32" s="35"/>
       <c r="E32" s="17"/>
     </row>
-    <row r="33" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="35"/>
       <c r="D33" s="35"/>
       <c r="E33" s="17"/>
     </row>
-    <row r="34" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
       <c r="E34" s="17"/>
     </row>
-    <row r="35" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="35"/>
       <c r="D35" s="35"/>
       <c r="E35" s="17"/>
     </row>
-    <row r="36" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="35"/>
       <c r="D36" s="35"/>
       <c r="E36" s="17"/>
     </row>
-    <row r="37" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="35"/>
       <c r="D37" s="35"/>
       <c r="E37" s="17"/>
     </row>
-    <row r="38" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
       <c r="E38" s="17"/>
     </row>
-    <row r="39" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="35"/>
       <c r="D39" s="35"/>
       <c r="E39" s="17"/>
     </row>
-    <row r="40" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="35"/>
       <c r="D40" s="35"/>
       <c r="E40" s="17"/>
     </row>
-    <row r="41" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="35"/>
       <c r="D41" s="35"/>
       <c r="E41" s="17"/>
     </row>
-    <row r="42" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="35"/>
       <c r="D42" s="35"/>
       <c r="E42" s="17"/>
     </row>
-    <row r="43" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
       <c r="E43" s="17"/>
     </row>
-    <row r="44" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="35"/>
       <c r="D44" s="35"/>
       <c r="E44" s="17"/>
     </row>
-    <row r="45" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="35"/>
       <c r="D45" s="35"/>
       <c r="E45" s="17"/>
     </row>
-    <row r="46" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="35"/>
       <c r="D46" s="35"/>
       <c r="E46" s="17"/>
     </row>
-    <row r="47" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="35"/>
       <c r="D47" s="35"/>
       <c r="E47" s="17"/>
     </row>
-    <row r="48" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="35"/>
       <c r="D48" s="35"/>
       <c r="E48" s="17"/>
     </row>
-    <row r="49" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="35"/>
       <c r="D49" s="35"/>
       <c r="E49" s="17"/>
     </row>
-    <row r="50" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
       <c r="C50" s="35"/>
       <c r="D50" s="35"/>
       <c r="E50" s="17"/>
     </row>
-    <row r="51" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="35"/>
       <c r="D51" s="35"/>
       <c r="E51" s="17"/>
     </row>
-    <row r="52" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
       <c r="C52" s="35"/>
       <c r="D52" s="35"/>
       <c r="E52" s="17"/>
     </row>
-    <row r="53" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
       <c r="C53" s="35"/>
       <c r="D53" s="35"/>
       <c r="E53" s="17"/>
     </row>
-    <row r="54" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
       <c r="C54" s="35"/>
       <c r="D54" s="35"/>
       <c r="E54" s="17"/>
     </row>
-    <row r="55" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="35"/>
       <c r="D55" s="35"/>
       <c r="E55" s="17"/>
     </row>
-    <row r="56" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="35"/>
       <c r="D56" s="35"/>
       <c r="E56" s="17"/>
     </row>
-    <row r="57" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="35"/>
       <c r="D57" s="35"/>
       <c r="E57" s="17"/>
     </row>
-    <row r="58" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="35"/>
       <c r="D58" s="35"/>
       <c r="E58" s="17"/>
     </row>
-    <row r="59" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="35"/>
       <c r="D59" s="35"/>
       <c r="E59" s="17"/>
     </row>
-    <row r="60" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="35"/>
       <c r="D60" s="35"/>
       <c r="E60" s="17"/>
     </row>
-    <row r="61" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
       <c r="C61" s="35"/>
       <c r="D61" s="35"/>
       <c r="E61" s="17"/>
     </row>
-    <row r="62" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
       <c r="C62" s="35"/>
       <c r="D62" s="35"/>
       <c r="E62" s="17"/>
     </row>
-    <row r="63" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
       <c r="C63" s="35"/>
       <c r="D63" s="35"/>
       <c r="E63" s="17"/>
     </row>
-    <row r="64" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="17"/>
       <c r="B64" s="17"/>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
       <c r="E64" s="17"/>
     </row>
-    <row r="65" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="35"/>
       <c r="D65" s="35"/>
       <c r="E65" s="17"/>
     </row>
-    <row r="66" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="17"/>
       <c r="B66" s="17"/>
       <c r="C66" s="35"/>
       <c r="D66" s="35"/>
       <c r="E66" s="17"/>
     </row>
-    <row r="67" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="17"/>
       <c r="B67" s="17"/>
       <c r="C67" s="35"/>
       <c r="D67" s="35"/>
       <c r="E67" s="17"/>
     </row>
-    <row r="68" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="17"/>
       <c r="B68" s="17"/>
       <c r="C68" s="35"/>
       <c r="D68" s="35"/>
       <c r="E68" s="17"/>
     </row>
-    <row r="69" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="17"/>
       <c r="B69" s="17"/>
       <c r="C69" s="35"/>
       <c r="D69" s="35"/>
       <c r="E69" s="17"/>
     </row>
-    <row r="70" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="17"/>
       <c r="B70" s="17"/>
       <c r="C70" s="35"/>
       <c r="D70" s="35"/>
       <c r="E70" s="17"/>
     </row>
-    <row r="71" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="17"/>
       <c r="B71" s="17"/>
       <c r="C71" s="35"/>
       <c r="D71" s="35"/>
       <c r="E71" s="17"/>
     </row>
-    <row r="72" spans="1:5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="35"/>
       <c r="D72" s="35"/>
       <c r="E72" s="17"/>
     </row>
-    <row r="73" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="17"/>
       <c r="B73" s="17"/>
       <c r="C73" s="35"/>
       <c r="D73" s="35"/>
     </row>
-    <row r="74" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="17"/>
       <c r="B74" s="17"/>
       <c r="C74" s="35"/>
       <c r="D74" s="35"/>
     </row>
-    <row r="75" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="17"/>
       <c r="B75" s="17"/>
       <c r="C75" s="35"/>
       <c r="D75" s="35"/>
     </row>
-    <row r="76" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="17"/>
       <c r="B76" s="17"/>
       <c r="C76" s="35"/>
@@ -2570,16 +2537,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="41" fitToHeight="2" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="41" fitToHeight="2" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2595,7 +2561,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -2618,7 +2585,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -2632,39 +2599,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:7" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -4213,16 +4180,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4238,7 +4204,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -4261,7 +4228,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13508)</f>
@@ -4275,39 +4242,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -5791,16 +5758,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="20" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="20" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5816,7 +5782,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -5839,7 +5806,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13508)</f>
@@ -5853,39 +5820,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -7340,16 +7307,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{682DEFF1-D972-214F-8BEA-A9100E335D9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7365,7 +7331,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -7388,7 +7355,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13508)</f>
@@ -7402,39 +7369,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -8889,16 +8856,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8914,7 +8880,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -8937,7 +8904,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -8951,39 +8918,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -10502,16 +10469,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AC22853-01AA-384A-A7A4-9366E90022A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10527,7 +10493,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -10550,7 +10517,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -10564,39 +10531,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -12064,16 +12031,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA88F251-751E-0A44-AE69-CD979CB2DC23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -12089,7 +12055,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -12112,7 +12079,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -12126,39 +12093,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -13626,16 +13593,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FCE9103-D54E-4043-9BEC-BB5B051ED49E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CAB358-55A1-0F42-9948-65AA425EDB6A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -13651,7 +13617,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -13674,7 +13641,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -13688,39 +13655,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -15188,16 +15155,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E53EDB-6B4B-904B-BF10-8B5E1ECBAA4F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -15213,7 +15179,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -15236,7 +15203,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -15250,39 +15217,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -16750,20 +16717,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E69952E-033E-D443-8839-6B5053F1DE97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q190"/>
+  <dimension ref="A1:Q191"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="60.33203125" style="95" customWidth="1"/>
@@ -16775,7 +16741,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -16798,7 +16765,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -16812,39 +16779,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -18282,7 +18249,7 @@
       <c r="D184" s="19"/>
       <c r="E184" s="19"/>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" ht="62" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D185" s="19"/>
       <c r="E185" s="19"/>
     </row>
@@ -18306,31 +18273,34 @@
       <c r="D190" s="19"/>
       <c r="E190" s="19"/>
     </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D191" s="19"/>
+      <c r="E191" s="19"/>
+    </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7051E0-986F-8244-A07B-F9D8BD0E96B4}">
-  <dimension ref="A1:W363"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:N363"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="50.83203125" defaultRowHeight="50" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="67.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="56.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="56.1640625" customWidth="1"/>
-    <col min="5" max="19" width="50.83203125" style="1"/>
-    <col min="20" max="20" width="50.83203125" style="1" customWidth="1"/>
+    <col min="5" max="20" width="50.83203125" style="1" customWidth="1"/>
     <col min="21" max="21" width="0.1640625" style="1" customWidth="1"/>
     <col min="22" max="22" width="0.83203125" style="1" customWidth="1"/>
     <col min="23" max="23" width="0.1640625" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="50.83203125" style="1"/>
+    <col min="24" max="24" width="50.83203125" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="50.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="67" customHeight="1" x14ac:dyDescent="0.2">
@@ -18353,20 +18323,19 @@
       <c r="A4" s="93"/>
       <c r="B4" s="94"/>
       <c r="C4" s="1"/>
-      <c r="D4"/>
     </row>
     <row r="5" spans="1:14" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="49" t="s">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="B5" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="50" t="s">
         <v>3</v>
-      </c>
-      <c r="C5" s="50" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="50" t="s">
-        <v>52</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
@@ -18381,16 +18350,16 @@
     </row>
     <row r="6" spans="1:14" s="15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B6" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="56" t="s">
         <v>7</v>
-      </c>
-      <c r="C6" s="56" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>49</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
@@ -18405,10 +18374,10 @@
     </row>
     <row r="7" spans="1:14" s="15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="68" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>171</v>
+        <v>31</v>
       </c>
       <c r="C7" s="67">
         <f ca="1">IFERROR(
@@ -18417,7 +18386,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D7" s="73" cm="1">
+      <c r="D7" s="73">
         <f t="array" aca="1" ref="D7" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A7&lt;&gt;""),$A$7:A7) &amp; "'!C:C"), $B7,
@@ -18441,7 +18410,7 @@
     <row r="8" spans="1:14" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="28"/>
       <c r="B8" s="29" t="s">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="C8" s="67">
         <f ca="1">IFERROR(
@@ -18450,7 +18419,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D8" s="73" cm="1">
+      <c r="D8" s="73">
         <f t="array" aca="1" ref="D8" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A8&lt;&gt;""),$A$7:A8) &amp; "'!C:C"), $B8,
@@ -18464,7 +18433,7 @@
     <row r="9" spans="1:14" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="28"/>
       <c r="B9" s="29" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C9" s="67">
         <f ca="1">IFERROR(
@@ -18473,7 +18442,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D9" s="73" cm="1">
+      <c r="D9" s="73">
         <f t="array" aca="1" ref="D9" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A9&lt;&gt;""),$A$7:A9) &amp; "'!C:C"), $B9,
@@ -18487,7 +18456,7 @@
     <row r="10" spans="1:14" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="28"/>
       <c r="B10" s="29" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="C10" s="67">
         <f ca="1">IFERROR(
@@ -18496,7 +18465,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D10" s="73" cm="1">
+      <c r="D10" s="73">
         <f t="array" aca="1" ref="D10" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A10&lt;&gt;""),$A$7:A10) &amp; "'!C:C"), $B10,
@@ -18510,7 +18479,7 @@
     <row r="11" spans="1:14" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="28"/>
       <c r="B11" s="29" t="s">
-        <v>174</v>
+        <v>35</v>
       </c>
       <c r="C11" s="67">
         <f ca="1">IFERROR(
@@ -18519,7 +18488,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D11" s="73" cm="1">
+      <c r="D11" s="73">
         <f t="array" aca="1" ref="D11" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A11&lt;&gt;""),$A$7:A11) &amp; "'!C:C"), $B11,
@@ -18533,7 +18502,7 @@
     <row r="12" spans="1:14" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="28"/>
       <c r="B12" s="29" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C12" s="67">
         <f ca="1">IFERROR(
@@ -18542,7 +18511,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D12" s="73" cm="1">
+      <c r="D12" s="73">
         <f t="array" aca="1" ref="D12" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A12&lt;&gt;""),$A$7:A12) &amp; "'!C:C"), $B12,
@@ -18556,7 +18525,7 @@
     <row r="13" spans="1:14" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="28"/>
       <c r="B13" s="29" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C13" s="67">
         <f ca="1">IFERROR(
@@ -18565,7 +18534,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D13" s="73" cm="1">
+      <c r="D13" s="73">
         <f t="array" aca="1" ref="D13" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A13&lt;&gt;""),$A$7:A13) &amp; "'!C:C"), $B13,
@@ -18579,7 +18548,7 @@
     <row r="14" spans="1:14" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="28"/>
       <c r="B14" s="29" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C14" s="67">
         <f ca="1">IFERROR(
@@ -18588,7 +18557,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D14" s="73" cm="1">
+      <c r="D14" s="73">
         <f t="array" aca="1" ref="D14" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A14&lt;&gt;""),$A$7:A14) &amp; "'!C:C"), $B14,
@@ -18602,7 +18571,7 @@
     <row r="15" spans="1:14" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="28"/>
       <c r="B15" s="29" t="s">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="C15" s="67">
         <f ca="1">IFERROR(
@@ -18611,7 +18580,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D15" s="73" cm="1">
+      <c r="D15" s="73">
         <f t="array" aca="1" ref="D15" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A15&lt;&gt;""),$A$7:A15) &amp; "'!C:C"), $B15,
@@ -18625,7 +18594,7 @@
     <row r="16" spans="1:14" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="28"/>
       <c r="B16" s="29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C16" s="67">
         <f ca="1">IFERROR(
@@ -18634,7 +18603,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D16" s="73" cm="1">
+      <c r="D16" s="73">
         <f t="array" aca="1" ref="D16" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A16&lt;&gt;""),$A$7:A16) &amp; "'!C:C"), $B16,
@@ -18648,7 +18617,7 @@
     <row r="17" spans="1:4" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="28"/>
       <c r="B17" s="29" t="s">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c r="C17" s="67">
         <f ca="1">IFERROR(
@@ -18657,7 +18626,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D17" s="73" cm="1">
+      <c r="D17" s="73">
         <f t="array" aca="1" ref="D17" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A17&lt;&gt;""),$A$7:A17) &amp; "'!C:C"), $B17,
@@ -18671,7 +18640,7 @@
     <row r="18" spans="1:4" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="28"/>
       <c r="B18" s="29" t="s">
-        <v>177</v>
+        <v>42</v>
       </c>
       <c r="C18" s="67">
         <f ca="1">IFERROR(
@@ -18680,7 +18649,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D18" s="73" cm="1">
+      <c r="D18" s="73">
         <f t="array" aca="1" ref="D18" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A18&lt;&gt;""),$A$7:A18) &amp; "'!C:C"), $B18,
@@ -18694,7 +18663,7 @@
     <row r="19" spans="1:4" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="28"/>
       <c r="B19" s="29" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C19" s="67">
         <f ca="1">IFERROR(
@@ -18703,7 +18672,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D19" s="73" cm="1">
+      <c r="D19" s="73">
         <f t="array" aca="1" ref="D19" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A19&lt;&gt;""),$A$7:A19) &amp; "'!C:C"), $B19,
@@ -18717,7 +18686,7 @@
     <row r="20" spans="1:4" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="28"/>
       <c r="B20" s="29" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C20" s="67">
         <f ca="1">IFERROR(
@@ -18726,7 +18695,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D20" s="73" cm="1">
+      <c r="D20" s="73">
         <f t="array" aca="1" ref="D20" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A20&lt;&gt;""),$A$7:A20) &amp; "'!C:C"), $B20,
@@ -18740,7 +18709,7 @@
     <row r="21" spans="1:4" s="32" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="28"/>
       <c r="B21" s="29" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C21" s="67">
         <f ca="1">IFERROR(
@@ -18749,7 +18718,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D21" s="73" cm="1">
+      <c r="D21" s="73">
         <f t="array" aca="1" ref="D21" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A21&lt;&gt;""),$A$7:A21) &amp; "'!C:C"), $B21,
@@ -18763,7 +18732,7 @@
     <row r="22" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="26"/>
       <c r="B22" s="27" t="s">
-        <v>166</v>
+        <v>46</v>
       </c>
       <c r="C22" s="26">
         <f ca="1">IFERROR(
@@ -18772,7 +18741,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D22" s="87" cm="1">
+      <c r="D22" s="87">
         <f t="array" aca="1" ref="D22" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A22&lt;&gt;""),$A$7:A22) &amp; "'!C:C"), $B22,
@@ -18785,10 +18754,10 @@
     </row>
     <row r="23" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="57" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C23" s="24">
         <f ca="1">IFERROR(
@@ -18797,7 +18766,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D23" s="88" cm="1">
+      <c r="D23" s="88">
         <f t="array" aca="1" ref="D23" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A23&lt;&gt;""),$A$7:A23) &amp; "'!C:C"), $B23,
@@ -18811,7 +18780,7 @@
     <row r="24" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="57"/>
       <c r="B24" s="29" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C24" s="24">
         <f ca="1">IFERROR(
@@ -18820,7 +18789,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D24" s="73" cm="1">
+      <c r="D24" s="73">
         <f t="array" aca="1" ref="D24" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A24&lt;&gt;""),$A$7:A24) &amp; "'!C:C"), $B24,
@@ -18834,7 +18803,7 @@
     <row r="25" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="31"/>
       <c r="B25" s="29" t="s">
-        <v>178</v>
+        <v>49</v>
       </c>
       <c r="C25" s="24">
         <f ca="1">IFERROR(
@@ -18843,7 +18812,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D25" s="73" cm="1">
+      <c r="D25" s="73">
         <f t="array" aca="1" ref="D25" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A25&lt;&gt;""),$A$7:A25) &amp; "'!C:C"), $B25,
@@ -18857,7 +18826,7 @@
     <row r="26" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="31"/>
       <c r="B26" s="29" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C26" s="24">
         <f ca="1">IFERROR(
@@ -18866,7 +18835,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D26" s="73" cm="1">
+      <c r="D26" s="73">
         <f t="array" aca="1" ref="D26" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A26&lt;&gt;""),$A$7:A26) &amp; "'!C:C"), $B26,
@@ -18880,7 +18849,7 @@
     <row r="27" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="31"/>
       <c r="B27" s="29" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C27" s="24">
         <f ca="1">IFERROR(
@@ -18889,7 +18858,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D27" s="73" cm="1">
+      <c r="D27" s="73">
         <f t="array" aca="1" ref="D27" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A27&lt;&gt;""),$A$7:A27) &amp; "'!C:C"), $B27,
@@ -18903,7 +18872,7 @@
     <row r="28" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="31"/>
       <c r="B28" s="29" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C28" s="24">
         <f ca="1">IFERROR(
@@ -18912,7 +18881,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D28" s="73" cm="1">
+      <c r="D28" s="73">
         <f t="array" aca="1" ref="D28" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A28&lt;&gt;""),$A$7:A28) &amp; "'!C:C"), $B28,
@@ -18926,7 +18895,7 @@
     <row r="29" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="65"/>
       <c r="B29" s="43" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="C29" s="24">
         <f ca="1">IFERROR(
@@ -18935,7 +18904,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D29" s="73" cm="1">
+      <c r="D29" s="73">
         <f t="array" aca="1" ref="D29" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A29&lt;&gt;""),$A$7:A29) &amp; "'!C:C"), $B29,
@@ -18949,7 +18918,7 @@
     <row r="30" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="65"/>
       <c r="B30" s="43" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C30" s="24">
         <f ca="1">IFERROR(
@@ -18958,7 +18927,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D30" s="73" cm="1">
+      <c r="D30" s="73">
         <f t="array" aca="1" ref="D30" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A30&lt;&gt;""),$A$7:A30) &amp; "'!C:C"), $B30,
@@ -18972,7 +18941,7 @@
     <row r="31" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="65"/>
       <c r="B31" s="43" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C31" s="24">
         <f ca="1">IFERROR(
@@ -18981,7 +18950,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D31" s="73" cm="1">
+      <c r="D31" s="73">
         <f t="array" aca="1" ref="D31" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A31&lt;&gt;""),$A$7:A31) &amp; "'!C:C"), $B31,
@@ -18995,7 +18964,7 @@
     <row r="32" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="65"/>
       <c r="B32" s="43" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C32" s="24">
         <f ca="1">IFERROR(
@@ -19004,7 +18973,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D32" s="73" cm="1">
+      <c r="D32" s="73">
         <f t="array" aca="1" ref="D32" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A32&lt;&gt;""),$A$7:A32) &amp; "'!C:C"), $B32,
@@ -19018,7 +18987,7 @@
     <row r="33" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="65"/>
       <c r="B33" s="43" t="s">
-        <v>155</v>
+        <v>57</v>
       </c>
       <c r="C33" s="24">
         <f ca="1">IFERROR(
@@ -19027,7 +18996,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D33" s="73" cm="1">
+      <c r="D33" s="73">
         <f t="array" aca="1" ref="D33" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A33&lt;&gt;""),$A$7:A33) &amp; "'!C:C"), $B33,
@@ -19038,10 +19007,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="63"/>
       <c r="B34" s="27" t="s">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="C34" s="26">
         <f ca="1">IFERROR(
@@ -19050,7 +19019,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D34" s="87" cm="1">
+      <c r="D34" s="87">
         <f t="array" aca="1" ref="D34" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A34&lt;&gt;""),$A$7:A34) &amp; "'!C:C"), $B34,
@@ -19061,12 +19030,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="57" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>180</v>
+        <v>59</v>
       </c>
       <c r="C35" s="24">
         <f ca="1">IFERROR(
@@ -19075,7 +19044,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D35" s="88" cm="1">
+      <c r="D35" s="88">
         <f t="array" aca="1" ref="D35" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A35&lt;&gt;""),$A$7:A35) &amp; "'!C:C"), $B35,
@@ -19086,10 +19055,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
       <c r="B36" s="29" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C36" s="24">
         <f ca="1">IFERROR(
@@ -19098,7 +19067,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D36" s="73" cm="1">
+      <c r="D36" s="73">
         <f t="array" aca="1" ref="D36" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A36&lt;&gt;""),$A$7:A36) &amp; "'!C:C"), $B36,
@@ -19109,10 +19078,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="28"/>
       <c r="B37" s="29" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C37" s="24">
         <f ca="1">IFERROR(
@@ -19121,7 +19090,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D37" s="73" cm="1">
+      <c r="D37" s="73">
         <f t="array" aca="1" ref="D37" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A37&lt;&gt;""),$A$7:A37) &amp; "'!C:C"), $B37,
@@ -19132,10 +19101,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="28"/>
       <c r="B38" s="29" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C38" s="24">
         <f ca="1">IFERROR(
@@ -19144,7 +19113,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D38" s="73" cm="1">
+      <c r="D38" s="73">
         <f t="array" aca="1" ref="D38" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A38&lt;&gt;""),$A$7:A38) &amp; "'!C:C"), $B38,
@@ -19155,10 +19124,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="28"/>
       <c r="B39" s="29" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C39" s="24">
         <f ca="1">IFERROR(
@@ -19167,7 +19136,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D39" s="73" cm="1">
+      <c r="D39" s="73">
         <f t="array" aca="1" ref="D39" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A39&lt;&gt;""),$A$7:A39) &amp; "'!C:C"), $B39,
@@ -19178,10 +19147,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="28"/>
       <c r="B40" s="29" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="C40" s="24">
         <f ca="1">IFERROR(
@@ -19190,7 +19159,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D40" s="73" cm="1">
+      <c r="D40" s="73">
         <f t="array" aca="1" ref="D40" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A40&lt;&gt;""),$A$7:A40) &amp; "'!C:C"), $B40,
@@ -19201,10 +19170,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="28"/>
       <c r="B41" s="29" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C41" s="24">
         <f ca="1">IFERROR(
@@ -19213,7 +19182,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D41" s="73" cm="1">
+      <c r="D41" s="73">
         <f t="array" aca="1" ref="D41" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A41&lt;&gt;""),$A$7:A41) &amp; "'!C:C"), $B41,
@@ -19224,10 +19193,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="38"/>
       <c r="B42" s="43" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C42" s="24">
         <f ca="1">IFERROR(
@@ -19236,7 +19205,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D42" s="73" cm="1">
+      <c r="D42" s="73">
         <f t="array" aca="1" ref="D42" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A42&lt;&gt;""),$A$7:A42) &amp; "'!C:C"), $B42,
@@ -19247,10 +19216,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="38"/>
       <c r="B43" s="43" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="C43" s="24">
         <f ca="1">IFERROR(
@@ -19259,7 +19228,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D43" s="73" cm="1">
+      <c r="D43" s="73">
         <f t="array" aca="1" ref="D43" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A43&lt;&gt;""),$A$7:A43) &amp; "'!C:C"), $B43,
@@ -19270,10 +19239,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="38"/>
       <c r="B44" s="43" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C44" s="26">
         <f ca="1">IFERROR(
@@ -19282,7 +19251,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D44" s="87" cm="1">
+      <c r="D44" s="87">
         <f t="array" aca="1" ref="D44" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A44&lt;&gt;""),$A$7:A44) &amp; "'!C:C"), $B44,
@@ -19293,12 +19262,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="69" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B45" s="46" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="C45" s="47">
         <f ca="1">IFERROR(
@@ -19307,7 +19276,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D45" s="88" cm="1">
+      <c r="D45" s="88">
         <f t="array" aca="1" ref="D45" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A45&lt;&gt;""),$A$7:A45) &amp; "'!C:C"), $B45,
@@ -19318,10 +19287,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="70"/>
       <c r="B46" s="25" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C46" s="28">
         <f ca="1">IFERROR(
@@ -19330,7 +19299,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D46" s="73" cm="1">
+      <c r="D46" s="73">
         <f t="array" aca="1" ref="D46" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A46&lt;&gt;""),$A$7:A46) &amp; "'!C:C"), $B46,
@@ -19341,10 +19310,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="70"/>
       <c r="B47" s="25" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="C47" s="28">
         <f ca="1">IFERROR(
@@ -19353,7 +19322,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D47" s="73" cm="1">
+      <c r="D47" s="73">
         <f t="array" aca="1" ref="D47" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A47&lt;&gt;""),$A$7:A47) &amp; "'!C:C"), $B47,
@@ -19364,10 +19333,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="70"/>
       <c r="B48" s="25" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="C48" s="28">
         <f ca="1">IFERROR(
@@ -19376,7 +19345,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D48" s="73" cm="1">
+      <c r="D48" s="73">
         <f t="array" aca="1" ref="D48" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A48&lt;&gt;""),$A$7:A48) &amp; "'!C:C"), $B48,
@@ -19387,10 +19356,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="70"/>
       <c r="B49" s="25" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="C49" s="28">
         <f ca="1">IFERROR(
@@ -19399,7 +19368,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D49" s="73" cm="1">
+      <c r="D49" s="73">
         <f t="array" aca="1" ref="D49" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A49&lt;&gt;""),$A$7:A49) &amp; "'!C:C"), $B49,
@@ -19410,10 +19379,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="28"/>
       <c r="B50" s="29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C50" s="28">
         <f ca="1">IFERROR(
@@ -19422,7 +19391,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D50" s="73" cm="1">
+      <c r="D50" s="73">
         <f t="array" aca="1" ref="D50" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A50&lt;&gt;""),$A$7:A50) &amp; "'!C:C"), $B50,
@@ -19433,7 +19402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="28"/>
       <c r="B51" s="29" t="s">
         <v>75</v>
@@ -19445,7 +19414,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D51" s="73" cm="1">
+      <c r="D51" s="73">
         <f t="array" aca="1" ref="D51" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A51&lt;&gt;""),$A$7:A51) &amp; "'!C:C"), $B51,
@@ -19456,7 +19425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="28"/>
       <c r="B52" s="29" t="s">
         <v>76</v>
@@ -19468,7 +19437,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D52" s="73" cm="1">
+      <c r="D52" s="73">
         <f t="array" aca="1" ref="D52" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A52&lt;&gt;""),$A$7:A52) &amp; "'!C:C"), $B52,
@@ -19479,10 +19448,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="80"/>
       <c r="B53" s="75" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="C53" s="26">
         <f ca="1">IFERROR(
@@ -19491,7 +19460,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D53" s="87" cm="1">
+      <c r="D53" s="87">
         <f t="array" aca="1" ref="D53" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A53&lt;&gt;""),$A$7:A53) &amp; "'!C:C"), $B53,
@@ -19502,12 +19471,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="84" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="B54" s="83" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C54" s="82">
         <f ca="1">IFERROR(
@@ -19516,7 +19485,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D54" s="88" cm="1">
+      <c r="D54" s="88">
         <f t="array" aca="1" ref="D54" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A54&lt;&gt;""),$A$7:A54) &amp; "'!C:C"), $B54,
@@ -19527,10 +19496,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="31"/>
       <c r="B55" s="29" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="C55" s="28">
         <f ca="1">IFERROR(
@@ -19539,7 +19508,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D55" s="73" cm="1">
+      <c r="D55" s="73">
         <f t="array" aca="1" ref="D55" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A55&lt;&gt;""),$A$7:A55) &amp; "'!C:C"), $B55,
@@ -19550,10 +19519,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="73"/>
       <c r="B56" s="29" t="s">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="C56" s="28">
         <f ca="1">IFERROR(
@@ -19562,7 +19531,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D56" s="73" cm="1">
+      <c r="D56" s="73">
         <f t="array" aca="1" ref="D56" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A56&lt;&gt;""),$A$7:A56) &amp; "'!C:C"), $B56,
@@ -19576,7 +19545,7 @@
     <row r="57" spans="1:4" s="14" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="28"/>
       <c r="B57" s="29" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="C57" s="28">
         <f ca="1">IFERROR(
@@ -19585,7 +19554,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D57" s="73" cm="1">
+      <c r="D57" s="73">
         <f t="array" aca="1" ref="D57" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A57&lt;&gt;""),$A$7:A57) &amp; "'!C:C"), $B57,
@@ -19596,10 +19565,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="28"/>
       <c r="B58" s="29" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="C58" s="28">
         <f ca="1">IFERROR(
@@ -19608,7 +19577,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D58" s="73" cm="1">
+      <c r="D58" s="73">
         <f t="array" aca="1" ref="D58" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A58&lt;&gt;""),$A$7:A58) &amp; "'!C:C"), $B58,
@@ -19619,10 +19588,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="80"/>
       <c r="B59" s="75" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C59" s="80">
         <f ca="1">IFERROR(
@@ -19631,7 +19600,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D59" s="110" cm="1">
+      <c r="D59" s="110">
         <f t="array" aca="1" ref="D59" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A59&lt;&gt;""),$A$7:A59) &amp; "'!C:C"), $B59,
@@ -19642,12 +19611,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="57" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="C60" s="24">
         <f ca="1">IFERROR(
@@ -19656,7 +19625,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D60" s="109" cm="1">
+      <c r="D60" s="109">
         <f t="array" aca="1" ref="D60" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A60&lt;&gt;""),$A$7:A60) &amp; "'!C:C"), $B60,
@@ -19667,10 +19636,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="57"/>
       <c r="B61" s="29" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="C61" s="28">
         <f ca="1">IFERROR(
@@ -19679,7 +19648,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D61" s="73" cm="1">
+      <c r="D61" s="73">
         <f t="array" aca="1" ref="D61" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A61&lt;&gt;""),$A$7:A61) &amp; "'!C:C"), $B61,
@@ -19690,10 +19659,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="57"/>
       <c r="B62" s="29" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="C62" s="28">
         <f ca="1">IFERROR(
@@ -19702,7 +19671,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D62" s="73" cm="1">
+      <c r="D62" s="73">
         <f t="array" aca="1" ref="D62" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A62&lt;&gt;""),$A$7:A62) &amp; "'!C:C"), $B62,
@@ -19713,10 +19682,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="57"/>
       <c r="B63" s="29" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="C63" s="28">
         <f ca="1">IFERROR(
@@ -19725,7 +19694,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D63" s="73" cm="1">
+      <c r="D63" s="73">
         <f t="array" aca="1" ref="D63" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A63&lt;&gt;""),$A$7:A63) &amp; "'!C:C"), $B63,
@@ -19736,10 +19705,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="57"/>
       <c r="B64" s="29" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="C64" s="28">
         <f ca="1">IFERROR(
@@ -19748,7 +19717,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D64" s="73" cm="1">
+      <c r="D64" s="73">
         <f t="array" aca="1" ref="D64" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A64&lt;&gt;""),$A$7:A64) &amp; "'!C:C"), $B64,
@@ -19759,10 +19728,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="31"/>
       <c r="B65" s="29" t="s">
-        <v>184</v>
+        <v>89</v>
       </c>
       <c r="C65" s="28">
         <f ca="1">IFERROR(
@@ -19771,7 +19740,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D65" s="73" cm="1">
+      <c r="D65" s="73">
         <f t="array" aca="1" ref="D65" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A65&lt;&gt;""),$A$7:A65) &amp; "'!C:C"), $B65,
@@ -19782,10 +19751,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="31"/>
       <c r="B66" s="29" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="C66" s="28">
         <f ca="1">IFERROR(
@@ -19794,7 +19763,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D66" s="73" cm="1">
+      <c r="D66" s="73">
         <f t="array" aca="1" ref="D66" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A66&lt;&gt;""),$A$7:A66) &amp; "'!C:C"), $B66,
@@ -19805,10 +19774,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="65"/>
       <c r="B67" s="43" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="C67" s="28">
         <f ca="1">IFERROR(
@@ -19817,7 +19786,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D67" s="73" cm="1">
+      <c r="D67" s="73">
         <f t="array" aca="1" ref="D67" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A67&lt;&gt;""),$A$7:A67) &amp; "'!C:C"), $B67,
@@ -19828,10 +19797,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="81"/>
       <c r="B68" s="75" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="C68" s="80">
         <f ca="1">IFERROR(
@@ -19840,7 +19809,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D68" s="87" cm="1">
+      <c r="D68" s="87">
         <f t="array" aca="1" ref="D68" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A68&lt;&gt;""),$A$7:A68) &amp; "'!C:C"), $B68,
@@ -19851,12 +19820,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="57" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="B69" s="29" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="C69" s="28">
         <f ca="1">IFERROR(
@@ -19865,7 +19834,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D69" s="88" cm="1">
+      <c r="D69" s="88">
         <f t="array" aca="1" ref="D69" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A69&lt;&gt;""),$A$7:A69) &amp; "'!C:C"), $B69,
@@ -19876,10 +19845,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="62"/>
       <c r="B70" s="29" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C70" s="28">
         <f ca="1">IFERROR(
@@ -19888,7 +19857,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D70" s="73" cm="1">
+      <c r="D70" s="73">
         <f t="array" aca="1" ref="D70" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A70&lt;&gt;""),$A$7:A70) &amp; "'!C:C"), $B70,
@@ -19899,10 +19868,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="62"/>
       <c r="B71" s="29" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="C71" s="28">
         <f ca="1">IFERROR(
@@ -19911,7 +19880,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D71" s="73" cm="1">
+      <c r="D71" s="73">
         <f t="array" aca="1" ref="D71" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A71&lt;&gt;""),$A$7:A71) &amp; "'!C:C"), $B71,
@@ -19922,10 +19891,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="62"/>
       <c r="B72" s="29" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C72" s="28">
         <f ca="1">IFERROR(
@@ -19934,7 +19903,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D72" s="73" cm="1">
+      <c r="D72" s="73">
         <f t="array" aca="1" ref="D72" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A72&lt;&gt;""),$A$7:A72) &amp; "'!C:C"), $B72,
@@ -19945,10 +19914,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="62"/>
       <c r="B73" s="29" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="C73" s="28">
         <f ca="1">IFERROR(
@@ -19957,7 +19926,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D73" s="73" cm="1">
+      <c r="D73" s="73">
         <f t="array" aca="1" ref="D73" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A73&lt;&gt;""),$A$7:A73) &amp; "'!C:C"), $B73,
@@ -19968,10 +19937,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="62"/>
       <c r="B74" s="29" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C74" s="28">
         <f ca="1">IFERROR(
@@ -19980,7 +19949,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D74" s="73" cm="1">
+      <c r="D74" s="73">
         <f t="array" aca="1" ref="D74" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A74&lt;&gt;""),$A$7:A74) &amp; "'!C:C"), $B74,
@@ -19991,10 +19960,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="62"/>
       <c r="B75" s="29" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C75" s="28">
         <f ca="1">IFERROR(
@@ -20003,7 +19972,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D75" s="73" cm="1">
+      <c r="D75" s="73">
         <f t="array" aca="1" ref="D75" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A75&lt;&gt;""),$A$7:A75) &amp; "'!C:C"), $B75,
@@ -20014,10 +19983,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="62"/>
       <c r="B76" s="29" t="s">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="C76" s="28">
         <f ca="1">IFERROR(
@@ -20026,7 +19995,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D76" s="73" cm="1">
+      <c r="D76" s="73">
         <f t="array" aca="1" ref="D76" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A76&lt;&gt;""),$A$7:A76) &amp; "'!C:C"), $B76,
@@ -20037,10 +20006,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="28"/>
       <c r="B77" s="29" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="C77" s="28">
         <f ca="1">IFERROR(
@@ -20049,7 +20018,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D77" s="73" cm="1">
+      <c r="D77" s="73">
         <f t="array" aca="1" ref="D77" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A77&lt;&gt;""),$A$7:A77) &amp; "'!C:C"), $B77,
@@ -20060,10 +20029,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="26"/>
       <c r="B78" s="27" t="s">
-        <v>188</v>
+        <v>102</v>
       </c>
       <c r="C78" s="26">
         <f ca="1">IFERROR(
@@ -20072,7 +20041,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D78" s="87" cm="1">
+      <c r="D78" s="87">
         <f t="array" aca="1" ref="D78" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A78&lt;&gt;""),$A$7:A78) &amp; "'!C:C"), $B78,
@@ -20083,12 +20052,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="71" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="C79" s="47">
         <f ca="1">IFERROR(
@@ -20097,7 +20066,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D79" s="88" cm="1">
+      <c r="D79" s="88">
         <f t="array" aca="1" ref="D79" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A79&lt;&gt;""),$A$7:A79) &amp; "'!C:C"), $B79,
@@ -20108,10 +20077,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="62"/>
       <c r="B80" s="29" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="C80" s="28">
         <f ca="1">IFERROR(
@@ -20120,7 +20089,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D80" s="73" cm="1">
+      <c r="D80" s="73">
         <f t="array" aca="1" ref="D80" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A80&lt;&gt;""),$A$7:A80) &amp; "'!C:C"), $B80,
@@ -20131,10 +20100,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="62"/>
       <c r="B81" s="29" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="C81" s="28">
         <f ca="1">IFERROR(
@@ -20143,7 +20112,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D81" s="73" cm="1">
+      <c r="D81" s="73">
         <f t="array" aca="1" ref="D81" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A81&lt;&gt;""),$A$7:A81) &amp; "'!C:C"), $B81,
@@ -20154,10 +20123,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="62"/>
       <c r="B82" s="29" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="C82" s="28">
         <f ca="1">IFERROR(
@@ -20166,7 +20135,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D82" s="73" cm="1">
+      <c r="D82" s="73">
         <f t="array" aca="1" ref="D82" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A82&lt;&gt;""),$A$7:A82) &amp; "'!C:C"), $B82,
@@ -20177,10 +20146,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="62"/>
       <c r="B83" s="29" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="C83" s="28">
         <f ca="1">IFERROR(
@@ -20189,7 +20158,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D83" s="73" cm="1">
+      <c r="D83" s="73">
         <f t="array" aca="1" ref="D83" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A83&lt;&gt;""),$A$7:A83) &amp; "'!C:C"), $B83,
@@ -20200,10 +20169,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="62"/>
       <c r="B84" s="29" t="s">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="C84" s="28">
         <f ca="1">IFERROR(
@@ -20212,7 +20181,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D84" s="73" cm="1">
+      <c r="D84" s="73">
         <f t="array" aca="1" ref="D84" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A84&lt;&gt;""),$A$7:A84) &amp; "'!C:C"), $B84,
@@ -20223,10 +20192,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="62"/>
       <c r="B85" s="29" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="C85" s="28">
         <f ca="1">IFERROR(
@@ -20235,7 +20204,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D85" s="73" cm="1">
+      <c r="D85" s="73">
         <f t="array" aca="1" ref="D85" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A85&lt;&gt;""),$A$7:A85) &amp; "'!C:C"), $B85,
@@ -20246,10 +20215,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="28"/>
       <c r="B86" s="29" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C86" s="28">
         <f ca="1">IFERROR(
@@ -20258,7 +20227,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D86" s="73" cm="1">
+      <c r="D86" s="73">
         <f t="array" aca="1" ref="D86" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A86&lt;&gt;""),$A$7:A86) &amp; "'!C:C"), $B86,
@@ -20269,10 +20238,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="38"/>
       <c r="B87" s="43" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="C87" s="28">
         <f ca="1">IFERROR(
@@ -20281,7 +20250,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D87" s="73" cm="1">
+      <c r="D87" s="73">
         <f t="array" aca="1" ref="D87" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A87&lt;&gt;""),$A$7:A87) &amp; "'!C:C"), $B87,
@@ -20292,10 +20261,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="28"/>
       <c r="B88" s="29" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="C88" s="28">
         <f ca="1">IFERROR(
@@ -20304,7 +20273,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D88" s="87" cm="1">
+      <c r="D88" s="87">
         <f t="array" aca="1" ref="D88" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A88&lt;&gt;""),$A$7:A88) &amp; "'!C:C"), $B88,
@@ -20315,10 +20284,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="90"/>
       <c r="B89" s="91" t="s">
-        <v>190</v>
+        <v>113</v>
       </c>
       <c r="C89" s="90">
         <f ca="1">IFERROR(
@@ -20327,7 +20296,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D89" s="87" cm="1">
+      <c r="D89" s="87">
         <f t="array" aca="1" ref="D89" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A89&lt;&gt;""),$A$7:A89) &amp; "'!C:C"), $B89,
@@ -20337,24 +20306,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
-      <c r="L89" s="1"/>
-      <c r="M89" s="1"/>
-      <c r="N89" s="1"/>
-      <c r="O89" s="1"/>
-    </row>
-    <row r="90" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="71" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="B90" s="46" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="C90" s="47">
         <f ca="1">IFERROR(
@@ -20363,7 +20321,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D90" s="88" cm="1">
+      <c r="D90" s="88">
         <f t="array" aca="1" ref="D90" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A90&lt;&gt;""),$A$7:A90) &amp; "'!C:C"), $B90,
@@ -20374,10 +20332,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="28"/>
       <c r="B91" s="29" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="C91" s="28">
         <f ca="1">IFERROR(
@@ -20386,7 +20344,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D91" s="73" cm="1">
+      <c r="D91" s="73">
         <f t="array" aca="1" ref="D91" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A91&lt;&gt;""),$A$7:A91) &amp; "'!C:C"), $B91,
@@ -20397,10 +20355,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="28"/>
       <c r="B92" s="29" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="C92" s="28">
         <f ca="1">IFERROR(
@@ -20409,7 +20367,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D92" s="73" cm="1">
+      <c r="D92" s="73">
         <f t="array" aca="1" ref="D92" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A92&lt;&gt;""),$A$7:A92) &amp; "'!C:C"), $B92,
@@ -20420,10 +20378,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="28"/>
       <c r="B93" s="29" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C93" s="28">
         <f ca="1">IFERROR(
@@ -20432,7 +20390,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D93" s="73" cm="1">
+      <c r="D93" s="73">
         <f t="array" aca="1" ref="D93" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A93&lt;&gt;""),$A$7:A93) &amp; "'!C:C"), $B93,
@@ -20443,10 +20401,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="28"/>
       <c r="B94" s="29" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="C94" s="28">
         <f ca="1">IFERROR(
@@ -20455,7 +20413,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D94" s="73" cm="1">
+      <c r="D94" s="73">
         <f t="array" aca="1" ref="D94" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A94&lt;&gt;""),$A$7:A94) &amp; "'!C:C"), $B94,
@@ -20466,10 +20424,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="28"/>
       <c r="B95" s="92" t="s">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="C95" s="28">
         <f ca="1">IFERROR(
@@ -20478,7 +20436,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D95" s="73" cm="1">
+      <c r="D95" s="73">
         <f t="array" aca="1" ref="D95" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A95&lt;&gt;""),$A$7:A95) &amp; "'!C:C"), $B95,
@@ -20489,10 +20447,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="28"/>
       <c r="B96" s="29" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="C96" s="28">
         <f ca="1">IFERROR(
@@ -20501,7 +20459,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D96" s="87" cm="1">
+      <c r="D96" s="87">
         <f t="array" aca="1" ref="D96" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A96&lt;&gt;""),$A$7:A96) &amp; "'!C:C"), $B96,
@@ -20512,10 +20470,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="24"/>
       <c r="B97" s="25" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="C97" s="24">
         <f ca="1">IFERROR(
@@ -20524,7 +20482,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D97" s="73" cm="1">
+      <c r="D97" s="73">
         <f t="array" aca="1" ref="D97" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A97&lt;&gt;""),$A$7:A97) &amp; "'!C:C"), $B97,
@@ -20535,12 +20493,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="72" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="B98" s="44" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="C98" s="45">
         <f ca="1">IFERROR(
@@ -20549,7 +20507,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D98" s="88" cm="1">
+      <c r="D98" s="88">
         <f t="array" aca="1" ref="D98" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A98&lt;&gt;""),$A$7:A98) &amp; "'!C:C"), $B98,
@@ -20559,22 +20517,11 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="1"/>
-      <c r="K98" s="1"/>
-      <c r="L98" s="1"/>
-      <c r="M98" s="1"/>
-      <c r="N98" s="1"/>
-      <c r="O98" s="1"/>
-    </row>
-    <row r="99" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="28"/>
       <c r="B99" s="29" t="s">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="C99" s="28">
         <f ca="1">IFERROR(
@@ -20583,7 +20530,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D99" s="73" cm="1">
+      <c r="D99" s="73">
         <f t="array" aca="1" ref="D99" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A99&lt;&gt;""),$A$7:A99) &amp; "'!C:C"), $B99,
@@ -20593,22 +20540,11 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
-      <c r="K99" s="1"/>
-      <c r="L99" s="1"/>
-      <c r="M99" s="1"/>
-      <c r="N99" s="1"/>
-      <c r="O99" s="1"/>
-    </row>
-    <row r="100" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="28"/>
       <c r="B100" s="29" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="C100" s="28">
         <f ca="1">IFERROR(
@@ -20617,7 +20553,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D100" s="73" cm="1">
+      <c r="D100" s="73">
         <f t="array" aca="1" ref="D100" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A100&lt;&gt;""),$A$7:A100) &amp; "'!C:C"), $B100,
@@ -20627,22 +20563,11 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
-      <c r="L100" s="1"/>
-      <c r="M100" s="1"/>
-      <c r="N100" s="1"/>
-      <c r="O100" s="1"/>
-    </row>
-    <row r="101" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="28"/>
       <c r="B101" s="29" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="C101" s="28">
         <f ca="1">IFERROR(
@@ -20651,7 +20576,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D101" s="73" cm="1">
+      <c r="D101" s="73">
         <f t="array" aca="1" ref="D101" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A101&lt;&gt;""),$A$7:A101) &amp; "'!C:C"), $B101,
@@ -20662,10 +20587,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="28"/>
       <c r="B102" s="29" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="C102" s="28">
         <f ca="1">IFERROR(
@@ -20674,7 +20599,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D102" s="73" cm="1">
+      <c r="D102" s="73">
         <f t="array" aca="1" ref="D102" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A102&lt;&gt;""),$A$7:A102) &amp; "'!C:C"), $B102,
@@ -20685,10 +20610,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="28"/>
       <c r="B103" s="29" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="C103" s="28">
         <f ca="1">IFERROR(
@@ -20697,7 +20622,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D103" s="73" cm="1">
+      <c r="D103" s="73">
         <f t="array" aca="1" ref="D103" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A103&lt;&gt;""),$A$7:A103) &amp; "'!C:C"), $B103,
@@ -20708,10 +20633,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="28"/>
       <c r="B104" s="29" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="C104" s="28">
         <f ca="1">IFERROR(
@@ -20720,7 +20645,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D104" s="73" cm="1">
+      <c r="D104" s="73">
         <f t="array" aca="1" ref="D104" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A104&lt;&gt;""),$A$7:A104) &amp; "'!C:C"), $B104,
@@ -20731,10 +20656,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="28"/>
       <c r="B105" s="29" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="C105" s="28">
         <f ca="1">IFERROR(
@@ -20743,7 +20668,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D105" s="73" cm="1">
+      <c r="D105" s="73">
         <f t="array" aca="1" ref="D105" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A105&lt;&gt;""),$A$7:A105) &amp; "'!C:C"), $B105,
@@ -20753,22 +20678,11 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
-      <c r="K105" s="1"/>
-      <c r="L105" s="1"/>
-      <c r="M105" s="1"/>
-      <c r="N105" s="1"/>
-      <c r="O105" s="1"/>
-    </row>
-    <row r="106" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="28"/>
       <c r="B106" s="29" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="C106" s="28">
         <f ca="1">IFERROR(
@@ -20777,7 +20691,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D106" s="73" cm="1">
+      <c r="D106" s="73">
         <f t="array" aca="1" ref="D106" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A106&lt;&gt;""),$A$7:A106) &amp; "'!C:C"), $B106,
@@ -20787,22 +20701,11 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
-      <c r="K106" s="1"/>
-      <c r="L106" s="1"/>
-      <c r="M106" s="1"/>
-      <c r="N106" s="1"/>
-      <c r="O106" s="1"/>
-    </row>
-    <row r="107" spans="1:15" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="28"/>
       <c r="B107" s="29" t="s">
-        <v>193</v>
+        <v>131</v>
       </c>
       <c r="C107" s="28">
         <f ca="1">IFERROR(
@@ -20811,7 +20714,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D107" s="73" cm="1">
+      <c r="D107" s="73">
         <f t="array" aca="1" ref="D107" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A107&lt;&gt;""),$A$7:A107) &amp; "'!C:C"), $B107,
@@ -20821,22 +20724,11 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
-      <c r="K107" s="1"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="1"/>
-      <c r="N107" s="1"/>
-      <c r="O107" s="1"/>
-    </row>
-    <row r="108" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="28"/>
       <c r="B108" s="29" t="s">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="C108" s="28">
         <f ca="1">IFERROR(
@@ -20845,7 +20737,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D108" s="73" cm="1">
+      <c r="D108" s="73">
         <f t="array" aca="1" ref="D108" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A108&lt;&gt;""),$A$7:A108) &amp; "'!C:C"), $B108,
@@ -20856,12 +20748,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="69" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="B109" s="48" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="C109" s="47">
         <f ca="1">IFERROR(
@@ -20870,7 +20762,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D109" s="88" cm="1">
+      <c r="D109" s="88">
         <f t="array" aca="1" ref="D109" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A109&lt;&gt;""),$A$7:A109) &amp; "'!C:C"), $B109,
@@ -20881,10 +20773,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="31"/>
       <c r="B110" s="30" t="s">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="C110" s="28">
         <f ca="1">IFERROR(
@@ -20893,7 +20785,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D110" s="73" cm="1">
+      <c r="D110" s="73">
         <f t="array" aca="1" ref="D110" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A110&lt;&gt;""),$A$7:A110) &amp; "'!C:C"), $B110,
@@ -20904,10 +20796,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="31"/>
       <c r="B111" s="30" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="C111" s="28">
         <f ca="1">IFERROR(
@@ -20916,7 +20808,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D111" s="73" cm="1">
+      <c r="D111" s="73">
         <f t="array" aca="1" ref="D111" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A111&lt;&gt;""),$A$7:A111) &amp; "'!C:C"), $B111,
@@ -20927,10 +20819,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="31"/>
       <c r="B112" s="30" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="C112" s="28">
         <f ca="1">IFERROR(
@@ -20939,7 +20831,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D112" s="73" cm="1">
+      <c r="D112" s="73">
         <f t="array" aca="1" ref="D112" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A112&lt;&gt;""),$A$7:A112) &amp; "'!C:C"), $B112,
@@ -20953,7 +20845,7 @@
     <row r="113" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="31"/>
       <c r="B113" s="30" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="C113" s="28">
         <f ca="1">IFERROR(
@@ -20962,7 +20854,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D113" s="73" cm="1">
+      <c r="D113" s="73">
         <f t="array" aca="1" ref="D113" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A113&lt;&gt;""),$A$7:A113) &amp; "'!C:C"), $B113,
@@ -20976,7 +20868,7 @@
     <row r="114" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="31"/>
       <c r="B114" s="30" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="C114" s="28">
         <f ca="1">IFERROR(
@@ -20985,7 +20877,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D114" s="73" cm="1">
+      <c r="D114" s="73">
         <f t="array" aca="1" ref="D114" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A114&lt;&gt;""),$A$7:A114) &amp; "'!C:C"), $B114,
@@ -20999,7 +20891,7 @@
     <row r="115" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="31"/>
       <c r="B115" s="30" t="s">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="C115" s="28">
         <f ca="1">IFERROR(
@@ -21008,7 +20900,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D115" s="73" cm="1">
+      <c r="D115" s="73">
         <f t="array" aca="1" ref="D115" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A115&lt;&gt;""),$A$7:A115) &amp; "'!C:C"), $B115,
@@ -21022,7 +20914,7 @@
     <row r="116" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="31"/>
       <c r="B116" s="30" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="C116" s="28">
         <f ca="1">IFERROR(
@@ -21031,7 +20923,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D116" s="73" cm="1">
+      <c r="D116" s="73">
         <f t="array" aca="1" ref="D116" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A116&lt;&gt;""),$A$7:A116) &amp; "'!C:C"), $B116,
@@ -21045,7 +20937,7 @@
     <row r="117" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="31"/>
       <c r="B117" s="30" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="C117" s="28">
         <f ca="1">IFERROR(
@@ -21054,7 +20946,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D117" s="73" cm="1">
+      <c r="D117" s="73">
         <f t="array" aca="1" ref="D117" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A117&lt;&gt;""),$A$7:A117) &amp; "'!C:C"), $B117,
@@ -21068,7 +20960,7 @@
     <row r="118" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="65"/>
       <c r="B118" s="66" t="s">
-        <v>196</v>
+        <v>142</v>
       </c>
       <c r="C118" s="28">
         <f ca="1">IFERROR(
@@ -21077,7 +20969,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D118" s="73" cm="1">
+      <c r="D118" s="73">
         <f t="array" aca="1" ref="D118" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A118&lt;&gt;""),$A$7:A118) &amp; "'!C:C"), $B118,
@@ -21091,7 +20983,7 @@
     <row r="119" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="81"/>
       <c r="B119" s="85" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="C119" s="80">
         <f ca="1">IFERROR(
@@ -21100,7 +20992,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D119" s="87" cm="1">
+      <c r="D119" s="87">
         <f t="array" aca="1" ref="D119" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A119&lt;&gt;""),$A$7:A119) &amp; "'!C:C"), $B119,
@@ -21113,10 +21005,10 @@
     </row>
     <row r="120" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="24" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="B120" s="29" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C120" s="24">
         <f ca="1">IFERROR(
@@ -21125,7 +21017,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D120" s="88" cm="1">
+      <c r="D120" s="88">
         <f t="array" aca="1" ref="D120" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A120&lt;&gt;""),$A$7:A120) &amp; "'!C:C"), $B120,
@@ -21139,7 +21031,7 @@
     <row r="121" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="24"/>
       <c r="B121" s="29" t="s">
-        <v>197</v>
+        <v>145</v>
       </c>
       <c r="C121" s="28">
         <f ca="1">IFERROR(
@@ -21148,7 +21040,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D121" s="73" cm="1">
+      <c r="D121" s="73">
         <f t="array" aca="1" ref="D121" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A121&lt;&gt;""),$A$7:A121) &amp; "'!C:C"), $B121,
@@ -21162,7 +21054,7 @@
     <row r="122" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="24"/>
       <c r="B122" s="29" t="s">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="C122" s="28">
         <f ca="1">IFERROR(
@@ -21171,7 +21063,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D122" s="73" cm="1">
+      <c r="D122" s="73">
         <f t="array" aca="1" ref="D122" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A122&lt;&gt;""),$A$7:A122) &amp; "'!C:C"), $B122,
@@ -21185,7 +21077,7 @@
     <row r="123" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="24"/>
       <c r="B123" s="29" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="C123" s="28">
         <f ca="1">IFERROR(
@@ -21194,7 +21086,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D123" s="73" cm="1">
+      <c r="D123" s="73">
         <f t="array" aca="1" ref="D123" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A123&lt;&gt;""),$A$7:A123) &amp; "'!C:C"), $B123,
@@ -21208,7 +21100,7 @@
     <row r="124" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="24"/>
       <c r="B124" s="29" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="C124" s="28">
         <f ca="1">IFERROR(
@@ -21217,7 +21109,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D124" s="73" cm="1">
+      <c r="D124" s="73">
         <f t="array" aca="1" ref="D124" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A124&lt;&gt;""),$A$7:A124) &amp; "'!C:C"), $B124,
@@ -21231,7 +21123,7 @@
     <row r="125" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="73"/>
       <c r="B125" s="29" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="C125" s="28">
         <f ca="1">IFERROR(
@@ -21240,7 +21132,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D125" s="73" cm="1">
+      <c r="D125" s="73">
         <f t="array" aca="1" ref="D125" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A125&lt;&gt;""),$A$7:A125) &amp; "'!C:C"), $B125,
@@ -21254,7 +21146,7 @@
     <row r="126" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="28"/>
       <c r="B126" s="29" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C126" s="28">
         <f ca="1">IFERROR(
@@ -21263,7 +21155,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D126" s="73" cm="1">
+      <c r="D126" s="73">
         <f t="array" aca="1" ref="D126" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A126&lt;&gt;""),$A$7:A126) &amp; "'!C:C"), $B126,
@@ -21277,7 +21169,7 @@
     <row r="127" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="28"/>
       <c r="B127" s="29" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="C127" s="28">
         <f ca="1">IFERROR(
@@ -21286,7 +21178,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D127" s="73" cm="1">
+      <c r="D127" s="73">
         <f t="array" aca="1" ref="D127" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A127&lt;&gt;""),$A$7:A127) &amp; "'!C:C"), $B127,
@@ -21300,7 +21192,7 @@
     <row r="128" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="28"/>
       <c r="B128" s="29" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="C128" s="28">
         <f ca="1">IFERROR(
@@ -21309,7 +21201,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D128" s="73" cm="1">
+      <c r="D128" s="73">
         <f t="array" aca="1" ref="D128" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A128&lt;&gt;""),$A$7:A128) &amp; "'!C:C"), $B128,
@@ -21323,7 +21215,7 @@
     <row r="129" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="80"/>
       <c r="B129" s="75" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C129" s="80">
         <f ca="1">IFERROR(
@@ -21332,7 +21224,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D129" s="87" cm="1">
+      <c r="D129" s="87">
         <f t="array" aca="1" ref="D129" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A129&lt;&gt;""),$A$7:A129) &amp; "'!C:C"), $B129,
@@ -21345,10 +21237,10 @@
     </row>
     <row r="130" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="69" t="s">
-        <v>208</v>
+        <v>23</v>
       </c>
       <c r="B130" s="48" t="s">
-        <v>209</v>
+        <v>154</v>
       </c>
       <c r="C130" s="47">
         <f ca="1">IFERROR(
@@ -21357,7 +21249,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D130" s="88" cm="1">
+      <c r="D130" s="88">
         <f t="array" aca="1" ref="D130" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A130&lt;&gt;""),$A$7:A130) &amp; "'!C:C"), $B130,
@@ -21371,7 +21263,7 @@
     <row r="131" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="31"/>
       <c r="B131" s="30" t="s">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="C131" s="28">
         <f ca="1">IFERROR(
@@ -21380,7 +21272,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D131" s="73" cm="1">
+      <c r="D131" s="73">
         <f t="array" aca="1" ref="D131" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A131&lt;&gt;""),$A$7:A131) &amp; "'!C:C"), $B131,
@@ -21394,7 +21286,7 @@
     <row r="132" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="31"/>
       <c r="B132" s="30" t="s">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="C132" s="28">
         <f ca="1">IFERROR(
@@ -21403,7 +21295,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D132" s="73" cm="1">
+      <c r="D132" s="73">
         <f t="array" aca="1" ref="D132" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A132&lt;&gt;""),$A$7:A132) &amp; "'!C:C"), $B132,
@@ -21417,7 +21309,7 @@
     <row r="133" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="65"/>
       <c r="B133" s="66" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C133" s="38">
         <f ca="1">IFERROR(
@@ -21426,7 +21318,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D133" s="73" cm="1">
+      <c r="D133" s="73">
         <f t="array" aca="1" ref="D133" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A133&lt;&gt;""),$A$7:A133) &amp; "'!C:C"), $B133,
@@ -21440,7 +21332,7 @@
     <row r="134" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="81"/>
       <c r="B134" s="85" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="C134" s="80">
         <f ca="1">IFERROR(
@@ -21449,7 +21341,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D134" s="110" cm="1">
+      <c r="D134" s="110">
         <f t="array" aca="1" ref="D134" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A134&lt;&gt;""),$A$7:A134) &amp; "'!C:C"), $B134,
@@ -21462,10 +21354,10 @@
     </row>
     <row r="135" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="24" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="B135" s="25" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="C135" s="24">
         <f ca="1">IFERROR(
@@ -21474,7 +21366,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D135" s="109" cm="1">
+      <c r="D135" s="109">
         <f t="array" aca="1" ref="D135" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A135&lt;&gt;""),$A$7:A135) &amp; "'!C:C"), $B135,
@@ -21488,7 +21380,7 @@
     <row r="136" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="28"/>
       <c r="B136" s="29" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="C136" s="28">
         <f ca="1">IFERROR(
@@ -21497,7 +21389,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D136" s="73" cm="1">
+      <c r="D136" s="73">
         <f t="array" aca="1" ref="D136" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A136&lt;&gt;""),$A$7:A136) &amp; "'!C:C"), $B136,
@@ -21511,7 +21403,7 @@
     <row r="137" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="28"/>
       <c r="B137" s="29" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="C137" s="28">
         <f ca="1">IFERROR(
@@ -21520,7 +21412,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D137" s="73" cm="1">
+      <c r="D137" s="73">
         <f t="array" aca="1" ref="D137" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A137&lt;&gt;""),$A$7:A137) &amp; "'!C:C"), $B137,
@@ -21534,7 +21426,7 @@
     <row r="138" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="28"/>
       <c r="B138" s="29" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="C138" s="28">
         <f ca="1">IFERROR(
@@ -21543,7 +21435,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D138" s="73" cm="1">
+      <c r="D138" s="73">
         <f t="array" aca="1" ref="D138" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A138&lt;&gt;""),$A$7:A138) &amp; "'!C:C"), $B138,
@@ -21557,7 +21449,7 @@
     <row r="139" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="28"/>
       <c r="B139" s="29" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="C139" s="28">
         <f ca="1">IFERROR(
@@ -21566,7 +21458,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D139" s="73" cm="1">
+      <c r="D139" s="73">
         <f t="array" aca="1" ref="D139" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A139&lt;&gt;""),$A$7:A139) &amp; "'!C:C"), $B139,
@@ -21580,7 +21472,7 @@
     <row r="140" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="28"/>
       <c r="B140" s="29" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="C140" s="28">
         <f ca="1">IFERROR(
@@ -21589,7 +21481,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D140" s="73" cm="1">
+      <c r="D140" s="73">
         <f t="array" aca="1" ref="D140" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A140&lt;&gt;""),$A$7:A140) &amp; "'!C:C"), $B140,
@@ -21603,7 +21495,7 @@
     <row r="141" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="28"/>
       <c r="B141" s="29" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="C141" s="28">
         <f ca="1">IFERROR(
@@ -21612,7 +21504,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D141" s="73" cm="1">
+      <c r="D141" s="73">
         <f t="array" aca="1" ref="D141" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A141&lt;&gt;""),$A$7:A141) &amp; "'!C:C"), $B141,
@@ -21626,7 +21518,7 @@
     <row r="142" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="28"/>
       <c r="B142" s="29" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="C142" s="28">
         <f ca="1">IFERROR(
@@ -21635,7 +21527,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D142" s="73" cm="1">
+      <c r="D142" s="73">
         <f t="array" aca="1" ref="D142" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A142&lt;&gt;""),$A$7:A142) &amp; "'!C:C"), $B142,
@@ -21649,7 +21541,7 @@
     <row r="143" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="28"/>
       <c r="B143" s="29" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="C143" s="28">
         <f ca="1">IFERROR(
@@ -21658,7 +21550,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D143" s="73" cm="1">
+      <c r="D143" s="73">
         <f t="array" aca="1" ref="D143" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A143&lt;&gt;""),$A$7:A143) &amp; "'!C:C"), $B143,
@@ -21672,7 +21564,7 @@
     <row r="144" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="28"/>
       <c r="B144" s="29" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C144" s="28">
         <f ca="1">IFERROR(
@@ -21681,7 +21573,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D144" s="73" cm="1">
+      <c r="D144" s="73">
         <f t="array" aca="1" ref="D144" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A144&lt;&gt;""),$A$7:A144) &amp; "'!C:C"), $B144,
@@ -21695,7 +21587,7 @@
     <row r="145" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="31"/>
       <c r="B145" s="30" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C145" s="28">
         <f ca="1">IFERROR(
@@ -21704,7 +21596,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D145" s="73" cm="1">
+      <c r="D145" s="73">
         <f t="array" aca="1" ref="D145" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A145&lt;&gt;""),$A$7:A145) &amp; "'!C:C"), $B145,
@@ -21718,7 +21610,7 @@
     <row r="146" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="31"/>
       <c r="B146" s="30" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C146" s="28">
         <f ca="1">IFERROR(
@@ -21727,7 +21619,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D146" s="73" cm="1">
+      <c r="D146" s="73">
         <f t="array" aca="1" ref="D146" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A146&lt;&gt;""),$A$7:A146) &amp; "'!C:C"), $B146,
@@ -21741,7 +21633,7 @@
     <row r="147" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="79"/>
       <c r="B147" s="78" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="C147" s="77">
         <f ca="1">IFERROR(
@@ -21750,7 +21642,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D147" s="87" cm="1">
+      <c r="D147" s="87">
         <f t="array" aca="1" ref="D147" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A147&lt;&gt;""),$A$7:A147) &amp; "'!C:C"), $B147,
@@ -21763,10 +21655,10 @@
     </row>
     <row r="148" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="24" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="B148" s="25" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C148" s="24">
         <f ca="1">IFERROR(
@@ -21775,7 +21667,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D148" s="88" cm="1">
+      <c r="D148" s="88">
         <f t="array" aca="1" ref="D148" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A148&lt;&gt;""),$A$7:A148) &amp; "'!C:C"), $B148,
@@ -21789,7 +21681,7 @@
     <row r="149" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="28"/>
       <c r="B149" s="29" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="C149" s="28">
         <f ca="1">IFERROR(
@@ -21798,7 +21690,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D149" s="73" cm="1">
+      <c r="D149" s="73">
         <f t="array" aca="1" ref="D149" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A149&lt;&gt;""),$A$7:A149) &amp; "'!C:C"), $B149,
@@ -21812,7 +21704,7 @@
     <row r="150" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="28"/>
       <c r="B150" s="29" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="C150" s="28">
         <f ca="1">IFERROR(
@@ -21821,7 +21713,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D150" s="73" cm="1">
+      <c r="D150" s="73">
         <f t="array" aca="1" ref="D150" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A150&lt;&gt;""),$A$7:A150) &amp; "'!C:C"), $B150,
@@ -21835,7 +21727,7 @@
     <row r="151" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="28"/>
       <c r="B151" s="29" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="C151" s="28">
         <f ca="1">IFERROR(
@@ -21844,7 +21736,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D151" s="73" cm="1">
+      <c r="D151" s="73">
         <f t="array" aca="1" ref="D151" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A151&lt;&gt;""),$A$7:A151) &amp; "'!C:C"), $B151,
@@ -21858,7 +21750,7 @@
     <row r="152" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="28"/>
       <c r="B152" s="29" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="C152" s="28">
         <f ca="1">IFERROR(
@@ -21867,7 +21759,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D152" s="73" cm="1">
+      <c r="D152" s="73">
         <f t="array" aca="1" ref="D152" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A152&lt;&gt;""),$A$7:A152) &amp; "'!C:C"), $B152,
@@ -21881,7 +21773,7 @@
     <row r="153" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="28"/>
       <c r="B153" s="29" t="s">
-        <v>110</v>
+        <v>177</v>
       </c>
       <c r="C153" s="28">
         <f ca="1">IFERROR(
@@ -21890,7 +21782,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D153" s="73" cm="1">
+      <c r="D153" s="73">
         <f t="array" aca="1" ref="D153" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A153&lt;&gt;""),$A$7:A153) &amp; "'!C:C"), $B153,
@@ -21904,7 +21796,7 @@
     <row r="154" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="76"/>
       <c r="B154" s="75" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="C154" s="74">
         <f ca="1">IFERROR(
@@ -21913,7 +21805,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D154" s="87" cm="1">
+      <c r="D154" s="87">
         <f t="array" aca="1" ref="D154" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A154&lt;&gt;""),$A$7:A154) &amp; "'!C:C"), $B154,
@@ -21926,10 +21818,10 @@
     </row>
     <row r="155" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="69" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="B155" s="66" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
       <c r="C155" s="47">
         <f ca="1">IFERROR(
@@ -21938,7 +21830,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D155" s="88" cm="1">
+      <c r="D155" s="88">
         <f t="array" aca="1" ref="D155" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A155&lt;&gt;""),$A$7:A155) &amp; "'!C:C"), $B155,
@@ -21952,7 +21844,7 @@
     <row r="156" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="73"/>
       <c r="B156" s="29" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="C156" s="28">
         <f ca="1">IFERROR(
@@ -21961,7 +21853,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D156" s="73" cm="1">
+      <c r="D156" s="73">
         <f t="array" aca="1" ref="D156" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A156&lt;&gt;""),$A$7:A156) &amp; "'!C:C"), $B156,
@@ -21975,7 +21867,7 @@
     <row r="157" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="73"/>
       <c r="B157" s="29" t="s">
-        <v>97</v>
+        <v>181</v>
       </c>
       <c r="C157" s="28">
         <f ca="1">IFERROR(
@@ -21984,7 +21876,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D157" s="73" cm="1">
+      <c r="D157" s="73">
         <f t="array" aca="1" ref="D157" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A157&lt;&gt;""),$A$7:A157) &amp; "'!C:C"), $B157,
@@ -21998,7 +21890,7 @@
     <row r="158" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="73"/>
       <c r="B158" s="29" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="C158" s="28">
         <f ca="1">IFERROR(
@@ -22007,7 +21899,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D158" s="73" cm="1">
+      <c r="D158" s="73">
         <f t="array" aca="1" ref="D158" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A158&lt;&gt;""),$A$7:A158) &amp; "'!C:C"), $B158,
@@ -22021,7 +21913,7 @@
     <row r="159" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="73"/>
       <c r="B159" s="29" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="C159" s="28">
         <f ca="1">IFERROR(
@@ -22030,7 +21922,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D159" s="73" cm="1">
+      <c r="D159" s="73">
         <f t="array" aca="1" ref="D159" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A159&lt;&gt;""),$A$7:A159) &amp; "'!C:C"), $B159,
@@ -22044,7 +21936,7 @@
     <row r="160" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="28"/>
       <c r="B160" s="29" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="C160" s="28">
         <f ca="1">IFERROR(
@@ -22053,7 +21945,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D160" s="73" cm="1">
+      <c r="D160" s="73">
         <f t="array" aca="1" ref="D160" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A160&lt;&gt;""),$A$7:A160) &amp; "'!C:C"), $B160,
@@ -22067,7 +21959,7 @@
     <row r="161" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="24"/>
       <c r="B161" s="25" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="C161" s="28">
         <f ca="1">IFERROR(
@@ -22076,7 +21968,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D161" s="73" cm="1">
+      <c r="D161" s="73">
         <f t="array" aca="1" ref="D161" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A161&lt;&gt;""),$A$7:A161) &amp; "'!C:C"), $B161,
@@ -22090,7 +21982,7 @@
     <row r="162" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="24"/>
       <c r="B162" s="25" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="C162" s="28">
         <f ca="1">IFERROR(
@@ -22099,7 +21991,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D162" s="73" cm="1">
+      <c r="D162" s="73">
         <f t="array" aca="1" ref="D162" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A162&lt;&gt;""),$A$7:A162) &amp; "'!C:C"), $B162,
@@ -22113,7 +22005,7 @@
     <row r="163" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="24"/>
       <c r="B163" s="25" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="C163" s="24">
         <f ca="1">IFERROR(
@@ -22122,7 +22014,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D163" s="73" cm="1">
+      <c r="D163" s="73">
         <f t="array" aca="1" ref="D163" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A163&lt;&gt;""),$A$7:A163) &amp; "'!C:C"), $B163,
@@ -22136,7 +22028,7 @@
     <row r="164" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="38"/>
       <c r="B164" s="43" t="s">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="C164" s="28">
         <f ca="1">IFERROR(
@@ -22145,7 +22037,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D164" s="73" cm="1">
+      <c r="D164" s="73">
         <f t="array" aca="1" ref="D164" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A164&lt;&gt;""),$A$7:A164) &amp; "'!C:C"), $B164,
@@ -22159,7 +22051,7 @@
     <row r="165" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="28"/>
       <c r="B165" s="29" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="C165" s="28">
         <f ca="1">IFERROR(
@@ -22168,7 +22060,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D165" s="87" cm="1">
+      <c r="D165" s="87">
         <f t="array" aca="1" ref="D165" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A165&lt;&gt;""),$A$7:A165) &amp; "'!C:C"), $B165,
@@ -22181,10 +22073,10 @@
     </row>
     <row r="166" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="69" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="B166" s="48" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="C166" s="47">
         <f ca="1">IFERROR(
@@ -22193,7 +22085,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D166" s="88" cm="1">
+      <c r="D166" s="88">
         <f t="array" aca="1" ref="D166" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A166&lt;&gt;""),$A$7:A166) &amp; "'!C:C"), $B166,
@@ -22207,7 +22099,7 @@
     <row r="167" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="31"/>
       <c r="B167" s="30" t="s">
-        <v>151</v>
+        <v>191</v>
       </c>
       <c r="C167" s="28">
         <f ca="1">IFERROR(
@@ -22216,7 +22108,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D167" s="73" cm="1">
+      <c r="D167" s="73">
         <f t="array" aca="1" ref="D167" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A167&lt;&gt;""),$A$7:A167) &amp; "'!C:C"), $B167,
@@ -22230,7 +22122,7 @@
     <row r="168" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="31"/>
       <c r="B168" s="30" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C168" s="28">
         <f ca="1">IFERROR(
@@ -22239,7 +22131,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D168" s="73" cm="1">
+      <c r="D168" s="73">
         <f t="array" aca="1" ref="D168" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A168&lt;&gt;""),$A$7:A168) &amp; "'!C:C"), $B168,
@@ -22253,7 +22145,7 @@
     <row r="169" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="65"/>
       <c r="B169" s="66" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="C169" s="38">
         <f ca="1">IFERROR(
@@ -22262,7 +22154,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D169" s="73" cm="1">
+      <c r="D169" s="73">
         <f t="array" aca="1" ref="D169" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A169&lt;&gt;""),$A$7:A169) &amp; "'!C:C"), $B169,
@@ -22276,7 +22168,7 @@
     <row r="170" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="31"/>
       <c r="B170" s="30" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="C170" s="28">
         <f ca="1">IFERROR(
@@ -22285,7 +22177,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D170" s="73" cm="1">
+      <c r="D170" s="73">
         <f t="array" aca="1" ref="D170" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A170&lt;&gt;""),$A$7:A170) &amp; "'!C:C"), $B170,
@@ -22299,7 +22191,7 @@
     <row r="171" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="73"/>
       <c r="B171" s="29" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="C171" s="28">
         <f ca="1">IFERROR(
@@ -22308,7 +22200,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D171" s="87" cm="1">
+      <c r="D171" s="87">
         <f t="array" aca="1" ref="D171" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A171&lt;&gt;""),$A$7:A171) &amp; "'!C:C"), $B171,
@@ -22321,10 +22213,10 @@
     </row>
     <row r="172" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="69" t="s">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="B172" s="48" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="C172" s="47">
         <f ca="1">IFERROR(
@@ -22333,7 +22225,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D172" s="88" cm="1">
+      <c r="D172" s="88">
         <f t="array" aca="1" ref="D172" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A172&lt;&gt;""),$A$7:A172) &amp; "'!C:C"), $B172,
@@ -22347,7 +22239,7 @@
     <row r="173" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="31"/>
       <c r="B173" s="30" t="s">
-        <v>146</v>
+        <v>196</v>
       </c>
       <c r="C173" s="28">
         <f ca="1">IFERROR(
@@ -22356,7 +22248,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D173" s="73" cm="1">
+      <c r="D173" s="73">
         <f t="array" aca="1" ref="D173" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A173&lt;&gt;""),$A$7:A173) &amp; "'!C:C"), $B173,
@@ -22370,7 +22262,7 @@
     <row r="174" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="31"/>
       <c r="B174" s="30" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="C174" s="28">
         <f ca="1">IFERROR(
@@ -22379,7 +22271,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D174" s="73" cm="1">
+      <c r="D174" s="73">
         <f t="array" aca="1" ref="D174" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A174&lt;&gt;""),$A$7:A174) &amp; "'!C:C"), $B174,
@@ -22393,7 +22285,7 @@
     <row r="175" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="65"/>
       <c r="B175" s="66" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="C175" s="28">
         <f ca="1">IFERROR(
@@ -22402,7 +22294,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D175" s="73" cm="1">
+      <c r="D175" s="73">
         <f t="array" aca="1" ref="D175" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A175&lt;&gt;""),$A$7:A175) &amp; "'!C:C"), $B175,
@@ -22416,7 +22308,7 @@
     <row r="176" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="65"/>
       <c r="B176" s="66" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="C176" s="38">
         <f ca="1">IFERROR(
@@ -22425,7 +22317,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D176" s="73" cm="1">
+      <c r="D176" s="73">
         <f t="array" aca="1" ref="D176" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A176&lt;&gt;""),$A$7:A176) &amp; "'!C:C"), $B176,
@@ -22439,7 +22331,7 @@
     <row r="177" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="31"/>
       <c r="B177" s="30" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="C177" s="28">
         <f ca="1">IFERROR(
@@ -22448,7 +22340,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D177" s="73" cm="1">
+      <c r="D177" s="73">
         <f t="array" aca="1" ref="D177" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A177&lt;&gt;""),$A$7:A177) &amp; "'!C:C"), $B177,
@@ -22462,7 +22354,7 @@
     <row r="178" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="73"/>
       <c r="B178" s="29" t="s">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="C178" s="28">
         <f ca="1">IFERROR(
@@ -22471,7 +22363,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D178" s="73" cm="1">
+      <c r="D178" s="73">
         <f t="array" aca="1" ref="D178" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A178&lt;&gt;""),$A$7:A178) &amp; "'!C:C"), $B178,
@@ -22485,7 +22377,7 @@
     <row r="179" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="28"/>
       <c r="B179" s="29" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C179" s="28">
         <f ca="1">IFERROR(
@@ -22494,7 +22386,7 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D179" s="73" cm="1">
+      <c r="D179" s="73">
         <f t="array" aca="1" ref="D179" ca="1">IFERROR(
   COUNTIFS(
     INDIRECT("'" &amp; LOOKUP(2,1/($A$7:A179&lt;&gt;""),$A$7:A179) &amp; "'!C:C"), $B179,
@@ -23063,461 +22955,157 @@
       <c r="C272" s="21"/>
       <c r="D272" s="22"/>
     </row>
-    <row r="273" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="23"/>
       <c r="B273" s="21"/>
       <c r="C273" s="21"/>
       <c r="D273" s="22"/>
     </row>
-    <row r="274" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="23"/>
       <c r="B274" s="21"/>
       <c r="C274" s="21"/>
       <c r="D274" s="22"/>
     </row>
-    <row r="275" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="23"/>
       <c r="B275" s="21"/>
       <c r="C275" s="21"/>
     </row>
-    <row r="276" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="23"/>
       <c r="B276" s="21"/>
       <c r="C276" s="21"/>
     </row>
-    <row r="277" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="23"/>
       <c r="B277" s="21"/>
       <c r="C277" s="21"/>
     </row>
-    <row r="278" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="23"/>
       <c r="B278" s="21"/>
       <c r="C278" s="21"/>
     </row>
-    <row r="279" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="21"/>
       <c r="B279" s="21"/>
       <c r="C279" s="21"/>
     </row>
-    <row r="280" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="21"/>
       <c r="B280" s="21"/>
       <c r="C280" s="21"/>
     </row>
-    <row r="281" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="21"/>
       <c r="B281" s="21"/>
       <c r="C281" s="21"/>
-      <c r="E281" s="1"/>
-      <c r="F281" s="1"/>
-      <c r="G281" s="1"/>
-      <c r="H281" s="1"/>
-      <c r="I281" s="1"/>
-      <c r="J281" s="1"/>
-      <c r="K281" s="1"/>
-      <c r="L281" s="1"/>
-      <c r="M281" s="1"/>
-      <c r="N281" s="1"/>
-      <c r="O281" s="1"/>
-      <c r="P281" s="1"/>
-      <c r="Q281" s="1"/>
-      <c r="R281" s="1"/>
-      <c r="S281" s="1"/>
-      <c r="T281" s="1"/>
-      <c r="U281" s="1"/>
-      <c r="V281" s="1"/>
-      <c r="W281" s="1"/>
-    </row>
-    <row r="282" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="282" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="21"/>
       <c r="B282" s="21"/>
       <c r="C282" s="21"/>
-      <c r="E282" s="1"/>
-      <c r="F282" s="1"/>
-      <c r="G282" s="1"/>
-      <c r="H282" s="1"/>
-      <c r="I282" s="1"/>
-      <c r="J282" s="1"/>
-      <c r="K282" s="1"/>
-      <c r="L282" s="1"/>
-      <c r="M282" s="1"/>
-      <c r="N282" s="1"/>
-      <c r="O282" s="1"/>
-      <c r="P282" s="1"/>
-      <c r="Q282" s="1"/>
-      <c r="R282" s="1"/>
-      <c r="S282" s="1"/>
-      <c r="T282" s="1"/>
-      <c r="U282" s="1"/>
-      <c r="V282" s="1"/>
-      <c r="W282" s="1"/>
-    </row>
-    <row r="283" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="283" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="21"/>
       <c r="B283" s="21"/>
       <c r="C283" s="21"/>
-      <c r="E283" s="1"/>
-      <c r="F283" s="1"/>
-      <c r="G283" s="1"/>
-      <c r="H283" s="1"/>
-      <c r="I283" s="1"/>
-      <c r="J283" s="1"/>
-      <c r="K283" s="1"/>
-      <c r="L283" s="1"/>
-      <c r="M283" s="1"/>
-      <c r="N283" s="1"/>
-      <c r="O283" s="1"/>
-      <c r="P283" s="1"/>
-      <c r="Q283" s="1"/>
-      <c r="R283" s="1"/>
-      <c r="S283" s="1"/>
-      <c r="T283" s="1"/>
-      <c r="U283" s="1"/>
-      <c r="V283" s="1"/>
-      <c r="W283" s="1"/>
-    </row>
-    <row r="284" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="284" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="21"/>
       <c r="B284" s="21"/>
       <c r="C284" s="21"/>
-      <c r="E284" s="1"/>
-      <c r="F284" s="1"/>
-      <c r="G284" s="1"/>
-      <c r="H284" s="1"/>
-      <c r="I284" s="1"/>
-      <c r="J284" s="1"/>
-      <c r="K284" s="1"/>
-      <c r="L284" s="1"/>
-      <c r="M284" s="1"/>
-      <c r="N284" s="1"/>
-      <c r="O284" s="1"/>
-      <c r="P284" s="1"/>
-      <c r="Q284" s="1"/>
-      <c r="R284" s="1"/>
-      <c r="S284" s="1"/>
-      <c r="T284" s="1"/>
-      <c r="U284" s="1"/>
-      <c r="V284" s="1"/>
-      <c r="W284" s="1"/>
-    </row>
-    <row r="285" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="285" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="21"/>
       <c r="B285" s="21"/>
       <c r="C285" s="21"/>
-      <c r="E285" s="1"/>
-      <c r="F285" s="1"/>
-      <c r="G285" s="1"/>
-      <c r="H285" s="1"/>
-      <c r="I285" s="1"/>
-      <c r="J285" s="1"/>
-      <c r="K285" s="1"/>
-      <c r="L285" s="1"/>
-      <c r="M285" s="1"/>
-      <c r="N285" s="1"/>
-      <c r="O285" s="1"/>
-      <c r="P285" s="1"/>
-      <c r="Q285" s="1"/>
-      <c r="R285" s="1"/>
-      <c r="S285" s="1"/>
-      <c r="T285" s="1"/>
-      <c r="U285" s="1"/>
-      <c r="V285" s="1"/>
-      <c r="W285" s="1"/>
-    </row>
-    <row r="286" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="286" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="21"/>
       <c r="B286" s="21"/>
       <c r="C286" s="21"/>
-      <c r="E286" s="1"/>
-      <c r="F286" s="1"/>
-      <c r="G286" s="1"/>
-      <c r="H286" s="1"/>
-      <c r="I286" s="1"/>
-      <c r="J286" s="1"/>
-      <c r="K286" s="1"/>
-      <c r="L286" s="1"/>
-      <c r="M286" s="1"/>
-      <c r="N286" s="1"/>
-      <c r="O286" s="1"/>
-      <c r="P286" s="1"/>
-      <c r="Q286" s="1"/>
-      <c r="R286" s="1"/>
-      <c r="S286" s="1"/>
-      <c r="T286" s="1"/>
-      <c r="U286" s="1"/>
-      <c r="V286" s="1"/>
-      <c r="W286" s="1"/>
-    </row>
-    <row r="287" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="287" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="21"/>
       <c r="B287" s="21"/>
       <c r="C287" s="21"/>
-      <c r="E287" s="1"/>
-      <c r="F287" s="1"/>
-      <c r="G287" s="1"/>
-      <c r="H287" s="1"/>
-      <c r="I287" s="1"/>
-      <c r="J287" s="1"/>
-      <c r="K287" s="1"/>
-      <c r="L287" s="1"/>
-      <c r="M287" s="1"/>
-      <c r="N287" s="1"/>
-      <c r="O287" s="1"/>
-      <c r="P287" s="1"/>
-      <c r="Q287" s="1"/>
-      <c r="R287" s="1"/>
-      <c r="S287" s="1"/>
-      <c r="T287" s="1"/>
-      <c r="U287" s="1"/>
-      <c r="V287" s="1"/>
-      <c r="W287" s="1"/>
-    </row>
-    <row r="288" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="288" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="21"/>
       <c r="B288" s="21"/>
       <c r="C288" s="21"/>
-      <c r="E288" s="1"/>
-      <c r="F288" s="1"/>
-      <c r="G288" s="1"/>
-      <c r="H288" s="1"/>
-      <c r="I288" s="1"/>
-      <c r="J288" s="1"/>
-      <c r="K288" s="1"/>
-      <c r="L288" s="1"/>
-      <c r="M288" s="1"/>
-      <c r="N288" s="1"/>
-      <c r="O288" s="1"/>
-      <c r="P288" s="1"/>
-      <c r="Q288" s="1"/>
-      <c r="R288" s="1"/>
-      <c r="S288" s="1"/>
-      <c r="T288" s="1"/>
-      <c r="U288" s="1"/>
-      <c r="V288" s="1"/>
-      <c r="W288" s="1"/>
-    </row>
-    <row r="289" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="289" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="21"/>
       <c r="B289" s="21"/>
       <c r="C289" s="21"/>
-      <c r="E289" s="1"/>
-      <c r="F289" s="1"/>
-      <c r="G289" s="1"/>
-      <c r="H289" s="1"/>
-      <c r="I289" s="1"/>
-      <c r="J289" s="1"/>
-      <c r="K289" s="1"/>
-      <c r="L289" s="1"/>
-      <c r="M289" s="1"/>
-      <c r="N289" s="1"/>
-      <c r="O289" s="1"/>
-      <c r="P289" s="1"/>
-      <c r="Q289" s="1"/>
-      <c r="R289" s="1"/>
-      <c r="S289" s="1"/>
-      <c r="T289" s="1"/>
-      <c r="U289" s="1"/>
-      <c r="V289" s="1"/>
-      <c r="W289" s="1"/>
-    </row>
-    <row r="290" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="290" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="21"/>
       <c r="B290" s="21"/>
       <c r="C290" s="21"/>
-      <c r="E290" s="1"/>
-      <c r="F290" s="1"/>
-      <c r="G290" s="1"/>
-      <c r="H290" s="1"/>
-      <c r="I290" s="1"/>
-      <c r="J290" s="1"/>
-      <c r="K290" s="1"/>
-      <c r="L290" s="1"/>
-      <c r="M290" s="1"/>
-      <c r="N290" s="1"/>
-      <c r="O290" s="1"/>
-      <c r="P290" s="1"/>
-      <c r="Q290" s="1"/>
-      <c r="R290" s="1"/>
-      <c r="S290" s="1"/>
-      <c r="T290" s="1"/>
-      <c r="U290" s="1"/>
-      <c r="V290" s="1"/>
-      <c r="W290" s="1"/>
-    </row>
-    <row r="291" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="291" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="21"/>
       <c r="B291" s="21"/>
       <c r="C291" s="21"/>
-      <c r="E291" s="1"/>
-      <c r="F291" s="1"/>
-      <c r="G291" s="1"/>
-      <c r="H291" s="1"/>
-      <c r="I291" s="1"/>
-      <c r="J291" s="1"/>
-      <c r="K291" s="1"/>
-      <c r="L291" s="1"/>
-      <c r="M291" s="1"/>
-      <c r="N291" s="1"/>
-      <c r="O291" s="1"/>
-      <c r="P291" s="1"/>
-      <c r="Q291" s="1"/>
-      <c r="R291" s="1"/>
-      <c r="S291" s="1"/>
-      <c r="T291" s="1"/>
-      <c r="U291" s="1"/>
-      <c r="V291" s="1"/>
-      <c r="W291" s="1"/>
-    </row>
-    <row r="292" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="292" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="21"/>
       <c r="B292" s="21"/>
       <c r="C292" s="21"/>
-      <c r="E292" s="1"/>
-      <c r="F292" s="1"/>
-      <c r="G292" s="1"/>
-      <c r="H292" s="1"/>
-      <c r="I292" s="1"/>
-      <c r="J292" s="1"/>
-      <c r="K292" s="1"/>
-      <c r="L292" s="1"/>
-      <c r="M292" s="1"/>
-      <c r="N292" s="1"/>
-      <c r="O292" s="1"/>
-      <c r="P292" s="1"/>
-      <c r="Q292" s="1"/>
-      <c r="R292" s="1"/>
-      <c r="S292" s="1"/>
-      <c r="T292" s="1"/>
-      <c r="U292" s="1"/>
-      <c r="V292" s="1"/>
-      <c r="W292" s="1"/>
-    </row>
-    <row r="293" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="293" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="21"/>
       <c r="B293" s="21"/>
       <c r="C293" s="21"/>
-      <c r="E293" s="1"/>
-      <c r="F293" s="1"/>
-      <c r="G293" s="1"/>
-      <c r="H293" s="1"/>
-      <c r="I293" s="1"/>
-      <c r="J293" s="1"/>
-      <c r="K293" s="1"/>
-      <c r="L293" s="1"/>
-      <c r="M293" s="1"/>
-      <c r="N293" s="1"/>
-      <c r="O293" s="1"/>
-      <c r="P293" s="1"/>
-      <c r="Q293" s="1"/>
-      <c r="R293" s="1"/>
-      <c r="S293" s="1"/>
-      <c r="T293" s="1"/>
-      <c r="U293" s="1"/>
-      <c r="V293" s="1"/>
-      <c r="W293" s="1"/>
-    </row>
-    <row r="294" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="294" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="21"/>
       <c r="B294" s="21"/>
       <c r="C294" s="21"/>
-      <c r="E294" s="1"/>
-      <c r="F294" s="1"/>
-      <c r="G294" s="1"/>
-      <c r="H294" s="1"/>
-      <c r="I294" s="1"/>
-      <c r="J294" s="1"/>
-      <c r="K294" s="1"/>
-      <c r="L294" s="1"/>
-      <c r="M294" s="1"/>
-      <c r="N294" s="1"/>
-      <c r="O294" s="1"/>
-      <c r="P294" s="1"/>
-      <c r="Q294" s="1"/>
-      <c r="R294" s="1"/>
-      <c r="S294" s="1"/>
-      <c r="T294" s="1"/>
-      <c r="U294" s="1"/>
-      <c r="V294" s="1"/>
-      <c r="W294" s="1"/>
-    </row>
-    <row r="295" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="295" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="21"/>
       <c r="B295" s="21"/>
       <c r="C295" s="21"/>
-      <c r="E295" s="1"/>
-      <c r="F295" s="1"/>
-      <c r="G295" s="1"/>
-      <c r="H295" s="1"/>
-      <c r="I295" s="1"/>
-      <c r="J295" s="1"/>
-      <c r="K295" s="1"/>
-      <c r="L295" s="1"/>
-      <c r="M295" s="1"/>
-      <c r="N295" s="1"/>
-      <c r="O295" s="1"/>
-      <c r="P295" s="1"/>
-      <c r="Q295" s="1"/>
-      <c r="R295" s="1"/>
-      <c r="S295" s="1"/>
-      <c r="T295" s="1"/>
-      <c r="U295" s="1"/>
-      <c r="V295" s="1"/>
-      <c r="W295" s="1"/>
-    </row>
-    <row r="296" spans="1:23" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="296" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="21"/>
       <c r="B296" s="21"/>
       <c r="C296" s="21"/>
-      <c r="E296" s="1"/>
-      <c r="F296" s="1"/>
-      <c r="G296" s="1"/>
-      <c r="H296" s="1"/>
-      <c r="I296" s="1"/>
-      <c r="J296" s="1"/>
-      <c r="K296" s="1"/>
-      <c r="L296" s="1"/>
-      <c r="M296" s="1"/>
-      <c r="N296" s="1"/>
-      <c r="O296" s="1"/>
-      <c r="P296" s="1"/>
-      <c r="Q296" s="1"/>
-      <c r="R296" s="1"/>
-      <c r="S296" s="1"/>
-      <c r="T296" s="1"/>
-      <c r="U296" s="1"/>
-      <c r="V296" s="1"/>
-      <c r="W296" s="1"/>
-    </row>
-    <row r="297" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="297" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="21"/>
       <c r="B297" s="21"/>
     </row>
-    <row r="298" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="21"/>
       <c r="B298" s="21"/>
     </row>
-    <row r="299" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="21"/>
       <c r="B299" s="21"/>
     </row>
-    <row r="300" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="21"/>
       <c r="B300" s="21"/>
     </row>
-    <row r="301" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="21"/>
       <c r="B301" s="21"/>
     </row>
-    <row r="302" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="21"/>
       <c r="B302" s="21"/>
     </row>
-    <row r="303" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="21"/>
       <c r="B303" s="21"/>
     </row>
-    <row r="304" spans="1:23" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="21"/>
       <c r="B304" s="21"/>
     </row>
@@ -23759,7 +23347,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
@@ -23767,16 +23355,15 @@
     <brk id="19" max="3" man="1"/>
     <brk id="154" max="3" man="1"/>
   </rowBreaks>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC255F8-7200-D84E-9D73-DDE699449625}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q191"/>
+  <dimension ref="A1:Q190"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="60.33203125" style="95" customWidth="1"/>
@@ -23788,7 +23375,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -23811,7 +23399,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -23825,39 +23413,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -25295,7 +24883,7 @@
       <c r="D184" s="19"/>
       <c r="E184" s="19"/>
     </row>
-    <row r="185" spans="1:6" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D185" s="19"/>
       <c r="E185" s="19"/>
     </row>
@@ -25319,22 +24907,17 @@
       <c r="D190" s="19"/>
       <c r="E190" s="19"/>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D191" s="19"/>
-      <c r="E191" s="19"/>
-    </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F00C344-2D59-6945-A5F8-608B01C1260C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -25350,7 +24933,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -25373,7 +24957,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -25387,39 +24971,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -26887,16 +26471,1577 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q191"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="60.33203125" style="95" customWidth="1"/>
+    <col min="2" max="2" width="60.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="64.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="66.1640625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="86.33203125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="100" customWidth="1"/>
+    <col min="7" max="7" width="5.33203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:17" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="33">
+        <v>46113</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D3" s="6">
+        <f>COUNTA(E7:E13510)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:17" ht="47.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="96"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+    </row>
+    <row r="8" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="96"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+    </row>
+    <row r="9" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="96"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="101"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="101"/>
+      <c r="M9" s="101"/>
+      <c r="N9" s="101"/>
+      <c r="O9" s="101"/>
+      <c r="P9" s="101"/>
+      <c r="Q9" s="101"/>
+    </row>
+    <row r="10" spans="1:17" s="101" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="96"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100"/>
+      <c r="H10" s="100"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
+      <c r="M10" s="100"/>
+      <c r="N10" s="100"/>
+      <c r="O10" s="100"/>
+      <c r="P10" s="100"/>
+      <c r="Q10" s="100"/>
+    </row>
+    <row r="11" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="96"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+    </row>
+    <row r="12" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="96"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+    </row>
+    <row r="13" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="96"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+    </row>
+    <row r="14" spans="1:17" s="100" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="96"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+    </row>
+    <row r="15" spans="1:17" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="96"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="100"/>
+    </row>
+    <row r="16" spans="1:17" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="102"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="100"/>
+    </row>
+    <row r="17" spans="1:6" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="102"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="100"/>
+    </row>
+    <row r="18" spans="1:6" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="102"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="100"/>
+    </row>
+    <row r="19" spans="1:6" s="17" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="102"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="100"/>
+    </row>
+    <row r="20" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="102"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="100"/>
+    </row>
+    <row r="21" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="102"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="100"/>
+    </row>
+    <row r="22" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="102"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="100"/>
+    </row>
+    <row r="23" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="102"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="100"/>
+    </row>
+    <row r="24" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="102"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="100"/>
+    </row>
+    <row r="25" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="102"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="100"/>
+    </row>
+    <row r="26" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="102"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="100"/>
+    </row>
+    <row r="27" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="102"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="100"/>
+    </row>
+    <row r="28" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="102"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="100"/>
+    </row>
+    <row r="29" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="102"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="100"/>
+    </row>
+    <row r="30" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="102"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="100"/>
+    </row>
+    <row r="31" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="102"/>
+      <c r="B31" s="103"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="100"/>
+    </row>
+    <row r="32" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="102"/>
+      <c r="B32" s="103"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="100"/>
+    </row>
+    <row r="33" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="102"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="100"/>
+    </row>
+    <row r="34" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="102"/>
+      <c r="B34" s="103"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="100"/>
+    </row>
+    <row r="35" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="102"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="100"/>
+    </row>
+    <row r="36" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="102"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="104"/>
+      <c r="E36" s="104"/>
+      <c r="F36" s="100"/>
+    </row>
+    <row r="37" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="102"/>
+      <c r="B37" s="103"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="100"/>
+    </row>
+    <row r="38" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="102"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="100"/>
+    </row>
+    <row r="39" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="102"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="100"/>
+    </row>
+    <row r="40" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="102"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="108"/>
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="100"/>
+    </row>
+    <row r="41" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="102"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="107"/>
+      <c r="D41" s="104"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="100"/>
+    </row>
+    <row r="42" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="102"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="108"/>
+      <c r="D42" s="104"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="100"/>
+    </row>
+    <row r="43" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="102"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="100"/>
+    </row>
+    <row r="44" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="102"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="108"/>
+      <c r="D44" s="104"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="100"/>
+    </row>
+    <row r="45" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="102"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="108"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="100"/>
+    </row>
+    <row r="46" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="102"/>
+      <c r="B46" s="103"/>
+      <c r="C46" s="108"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="100"/>
+    </row>
+    <row r="47" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="102"/>
+      <c r="B47" s="103"/>
+      <c r="C47" s="108"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="100"/>
+    </row>
+    <row r="48" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="102"/>
+      <c r="B48" s="103"/>
+      <c r="C48" s="108"/>
+      <c r="D48" s="104"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="100"/>
+    </row>
+    <row r="49" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="102"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="108"/>
+      <c r="D49" s="104"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="100"/>
+    </row>
+    <row r="50" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="102"/>
+      <c r="B50" s="103"/>
+      <c r="C50" s="108"/>
+      <c r="D50" s="104"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="100"/>
+    </row>
+    <row r="51" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="102"/>
+      <c r="B51" s="103"/>
+      <c r="C51" s="108"/>
+      <c r="D51" s="104"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="100"/>
+    </row>
+    <row r="52" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="102"/>
+      <c r="B52" s="103"/>
+      <c r="C52" s="108"/>
+      <c r="D52" s="104"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="100"/>
+    </row>
+    <row r="53" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="102"/>
+      <c r="B53" s="103"/>
+      <c r="C53" s="108"/>
+      <c r="D53" s="104"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="100"/>
+    </row>
+    <row r="54" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="102"/>
+      <c r="B54" s="103"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="104"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="100"/>
+    </row>
+    <row r="55" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="102"/>
+      <c r="B55" s="103"/>
+      <c r="C55" s="108"/>
+      <c r="D55" s="104"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="100"/>
+    </row>
+    <row r="56" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="102"/>
+      <c r="B56" s="103"/>
+      <c r="C56" s="108"/>
+      <c r="D56" s="104"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="100"/>
+    </row>
+    <row r="57" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="102"/>
+      <c r="B57" s="103"/>
+      <c r="C57" s="108"/>
+      <c r="D57" s="104"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="100"/>
+    </row>
+    <row r="58" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="102"/>
+      <c r="B58" s="103"/>
+      <c r="C58" s="108"/>
+      <c r="D58" s="104"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="100"/>
+    </row>
+    <row r="59" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="102"/>
+      <c r="B59" s="103"/>
+      <c r="C59" s="108"/>
+      <c r="D59" s="104"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="100"/>
+    </row>
+    <row r="60" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="102"/>
+      <c r="B60" s="103"/>
+      <c r="C60" s="108"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="100"/>
+    </row>
+    <row r="61" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="102"/>
+      <c r="B61" s="103"/>
+      <c r="C61" s="108"/>
+      <c r="D61" s="104"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="100"/>
+    </row>
+    <row r="62" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="102"/>
+      <c r="B62" s="103"/>
+      <c r="C62" s="108"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="100"/>
+    </row>
+    <row r="63" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="102"/>
+      <c r="B63" s="103"/>
+      <c r="C63" s="108"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="100"/>
+    </row>
+    <row r="64" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="102"/>
+      <c r="B64" s="103"/>
+      <c r="C64" s="108"/>
+      <c r="D64" s="104"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="100"/>
+    </row>
+    <row r="65" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="102"/>
+      <c r="B65" s="103"/>
+      <c r="C65" s="108"/>
+      <c r="D65" s="104"/>
+      <c r="E65" s="104"/>
+      <c r="F65" s="100"/>
+    </row>
+    <row r="66" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="96"/>
+      <c r="B66" s="97"/>
+      <c r="C66" s="98"/>
+      <c r="D66" s="99"/>
+      <c r="E66" s="99"/>
+      <c r="F66" s="100"/>
+    </row>
+    <row r="67" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="96"/>
+      <c r="B67" s="97"/>
+      <c r="C67" s="98"/>
+      <c r="D67" s="99"/>
+      <c r="E67" s="99"/>
+      <c r="F67" s="100"/>
+    </row>
+    <row r="68" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="96"/>
+      <c r="B68" s="97"/>
+      <c r="C68" s="98"/>
+      <c r="D68" s="99"/>
+      <c r="E68" s="99"/>
+      <c r="F68" s="100"/>
+    </row>
+    <row r="69" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="96"/>
+      <c r="B69" s="97"/>
+      <c r="C69" s="98"/>
+      <c r="D69" s="99"/>
+      <c r="E69" s="99"/>
+      <c r="F69" s="100"/>
+    </row>
+    <row r="70" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="96"/>
+      <c r="B70" s="97"/>
+      <c r="C70" s="98"/>
+      <c r="D70" s="99"/>
+      <c r="E70" s="99"/>
+      <c r="F70" s="100"/>
+    </row>
+    <row r="71" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="96"/>
+      <c r="B71" s="97"/>
+      <c r="C71" s="98"/>
+      <c r="D71" s="99"/>
+      <c r="E71" s="99"/>
+      <c r="F71" s="100"/>
+    </row>
+    <row r="72" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="96"/>
+      <c r="B72" s="97"/>
+      <c r="C72" s="98"/>
+      <c r="D72" s="99"/>
+      <c r="E72" s="99"/>
+      <c r="F72" s="100"/>
+    </row>
+    <row r="73" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="96"/>
+      <c r="B73" s="97"/>
+      <c r="C73" s="98"/>
+      <c r="D73" s="99"/>
+      <c r="E73" s="99"/>
+      <c r="F73" s="100"/>
+    </row>
+    <row r="74" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="96"/>
+      <c r="B74" s="97"/>
+      <c r="C74" s="98"/>
+      <c r="D74" s="99"/>
+      <c r="E74" s="99"/>
+      <c r="F74" s="100"/>
+    </row>
+    <row r="75" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="102"/>
+      <c r="B75" s="103"/>
+      <c r="C75" s="98"/>
+      <c r="D75" s="99"/>
+      <c r="E75" s="99"/>
+      <c r="F75" s="100"/>
+    </row>
+    <row r="76" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="102"/>
+      <c r="B76" s="103"/>
+      <c r="C76" s="98"/>
+      <c r="D76" s="99"/>
+      <c r="E76" s="99"/>
+      <c r="F76" s="100"/>
+    </row>
+    <row r="77" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="102"/>
+      <c r="B77" s="103"/>
+      <c r="C77" s="98"/>
+      <c r="D77" s="104"/>
+      <c r="E77" s="104"/>
+      <c r="F77" s="100"/>
+    </row>
+    <row r="78" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="102"/>
+      <c r="B78" s="103"/>
+      <c r="C78" s="98"/>
+      <c r="D78" s="104"/>
+      <c r="E78" s="104"/>
+      <c r="F78" s="100"/>
+    </row>
+    <row r="79" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="102"/>
+      <c r="B79" s="103"/>
+      <c r="C79" s="98"/>
+      <c r="D79" s="104"/>
+      <c r="E79" s="104"/>
+      <c r="F79" s="100"/>
+    </row>
+    <row r="80" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="102"/>
+      <c r="B80" s="103"/>
+      <c r="C80" s="98"/>
+      <c r="D80" s="104"/>
+      <c r="E80" s="104"/>
+      <c r="F80" s="100"/>
+    </row>
+    <row r="81" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="102"/>
+      <c r="B81" s="103"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="104"/>
+      <c r="E81" s="104"/>
+      <c r="F81" s="100"/>
+    </row>
+    <row r="82" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="102"/>
+      <c r="B82" s="103"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="104"/>
+      <c r="E82" s="104"/>
+      <c r="F82" s="100"/>
+    </row>
+    <row r="83" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="102"/>
+      <c r="B83" s="103"/>
+      <c r="C83" s="105"/>
+      <c r="D83" s="104"/>
+      <c r="E83" s="104"/>
+      <c r="F83" s="100"/>
+    </row>
+    <row r="84" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="102"/>
+      <c r="B84" s="103"/>
+      <c r="C84" s="98"/>
+      <c r="D84" s="104"/>
+      <c r="E84" s="104"/>
+      <c r="F84" s="100"/>
+    </row>
+    <row r="85" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="102"/>
+      <c r="B85" s="103"/>
+      <c r="C85" s="105"/>
+      <c r="D85" s="104"/>
+      <c r="E85" s="104"/>
+      <c r="F85" s="100"/>
+    </row>
+    <row r="86" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="102"/>
+      <c r="B86" s="103"/>
+      <c r="C86" s="105"/>
+      <c r="D86" s="104"/>
+      <c r="E86" s="104"/>
+      <c r="F86" s="100"/>
+    </row>
+    <row r="87" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="102"/>
+      <c r="B87" s="103"/>
+      <c r="C87" s="98"/>
+      <c r="D87" s="104"/>
+      <c r="E87" s="104"/>
+      <c r="F87" s="100"/>
+    </row>
+    <row r="88" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="102"/>
+      <c r="B88" s="103"/>
+      <c r="C88" s="98"/>
+      <c r="D88" s="104"/>
+      <c r="E88" s="104"/>
+      <c r="F88" s="100"/>
+    </row>
+    <row r="89" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="102"/>
+      <c r="B89" s="103"/>
+      <c r="C89" s="107"/>
+      <c r="D89" s="104"/>
+      <c r="E89" s="104"/>
+      <c r="F89" s="100"/>
+    </row>
+    <row r="90" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="102"/>
+      <c r="B90" s="103"/>
+      <c r="C90" s="98"/>
+      <c r="D90" s="104"/>
+      <c r="E90" s="104"/>
+      <c r="F90" s="100"/>
+    </row>
+    <row r="91" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="102"/>
+      <c r="B91" s="103"/>
+      <c r="C91" s="107"/>
+      <c r="D91" s="104"/>
+      <c r="E91" s="104"/>
+      <c r="F91" s="100"/>
+    </row>
+    <row r="92" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="102"/>
+      <c r="B92" s="103"/>
+      <c r="C92" s="105"/>
+      <c r="D92" s="104"/>
+      <c r="E92" s="104"/>
+      <c r="F92" s="100"/>
+    </row>
+    <row r="93" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="102"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="105"/>
+      <c r="D93" s="104"/>
+      <c r="E93" s="104"/>
+      <c r="F93" s="100"/>
+    </row>
+    <row r="94" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="102"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="105"/>
+      <c r="D94" s="104"/>
+      <c r="E94" s="104"/>
+      <c r="F94" s="100"/>
+    </row>
+    <row r="95" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="102"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="105"/>
+      <c r="D95" s="104"/>
+      <c r="E95" s="104"/>
+      <c r="F95" s="100"/>
+    </row>
+    <row r="96" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="102"/>
+      <c r="B96" s="103"/>
+      <c r="C96" s="105"/>
+      <c r="D96" s="104"/>
+      <c r="E96" s="104"/>
+      <c r="F96" s="100"/>
+    </row>
+    <row r="97" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="102"/>
+      <c r="B97" s="103"/>
+      <c r="C97" s="98"/>
+      <c r="D97" s="104"/>
+      <c r="E97" s="104"/>
+      <c r="F97" s="100"/>
+    </row>
+    <row r="98" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="102"/>
+      <c r="B98" s="103"/>
+      <c r="C98" s="98"/>
+      <c r="D98" s="104"/>
+      <c r="E98" s="104"/>
+      <c r="F98" s="100"/>
+    </row>
+    <row r="99" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="102"/>
+      <c r="B99" s="103"/>
+      <c r="C99" s="108"/>
+      <c r="D99" s="104"/>
+      <c r="E99" s="104"/>
+      <c r="F99" s="100"/>
+    </row>
+    <row r="100" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="102"/>
+      <c r="B100" s="103"/>
+      <c r="C100" s="107"/>
+      <c r="D100" s="104"/>
+      <c r="E100" s="104"/>
+      <c r="F100" s="100"/>
+    </row>
+    <row r="101" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="102"/>
+      <c r="B101" s="103"/>
+      <c r="C101" s="108"/>
+      <c r="D101" s="104"/>
+      <c r="E101" s="104"/>
+      <c r="F101" s="100"/>
+    </row>
+    <row r="102" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="102"/>
+      <c r="B102" s="103"/>
+      <c r="C102" s="108"/>
+      <c r="D102" s="104"/>
+      <c r="E102" s="104"/>
+      <c r="F102" s="100"/>
+    </row>
+    <row r="103" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="102"/>
+      <c r="B103" s="103"/>
+      <c r="C103" s="108"/>
+      <c r="D103" s="104"/>
+      <c r="E103" s="104"/>
+      <c r="F103" s="100"/>
+    </row>
+    <row r="104" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="102"/>
+      <c r="B104" s="103"/>
+      <c r="C104" s="108"/>
+      <c r="D104" s="104"/>
+      <c r="E104" s="104"/>
+      <c r="F104" s="100"/>
+    </row>
+    <row r="105" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="102"/>
+      <c r="B105" s="103"/>
+      <c r="C105" s="108"/>
+      <c r="D105" s="104"/>
+      <c r="E105" s="104"/>
+      <c r="F105" s="100"/>
+    </row>
+    <row r="106" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A106" s="102"/>
+      <c r="B106" s="103"/>
+      <c r="C106" s="108"/>
+      <c r="D106" s="104"/>
+      <c r="E106" s="104"/>
+      <c r="F106" s="100"/>
+    </row>
+    <row r="107" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="102"/>
+      <c r="B107" s="103"/>
+      <c r="C107" s="108"/>
+      <c r="D107" s="104"/>
+      <c r="E107" s="104"/>
+      <c r="F107" s="100"/>
+    </row>
+    <row r="108" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A108" s="102"/>
+      <c r="B108" s="103"/>
+      <c r="C108" s="108"/>
+      <c r="D108" s="104"/>
+      <c r="E108" s="104"/>
+      <c r="F108" s="100"/>
+    </row>
+    <row r="109" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A109" s="102"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="108"/>
+      <c r="D109" s="104"/>
+      <c r="E109" s="104"/>
+      <c r="F109" s="100"/>
+    </row>
+    <row r="110" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A110" s="102"/>
+      <c r="B110" s="103"/>
+      <c r="C110" s="108"/>
+      <c r="D110" s="104"/>
+      <c r="E110" s="104"/>
+      <c r="F110" s="100"/>
+    </row>
+    <row r="111" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A111" s="102"/>
+      <c r="B111" s="103"/>
+      <c r="C111" s="108"/>
+      <c r="D111" s="104"/>
+      <c r="E111" s="104"/>
+      <c r="F111" s="100"/>
+    </row>
+    <row r="112" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A112" s="102"/>
+      <c r="B112" s="103"/>
+      <c r="C112" s="108"/>
+      <c r="D112" s="104"/>
+      <c r="E112" s="104"/>
+      <c r="F112" s="100"/>
+    </row>
+    <row r="113" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A113" s="102"/>
+      <c r="B113" s="103"/>
+      <c r="C113" s="108"/>
+      <c r="D113" s="104"/>
+      <c r="E113" s="104"/>
+      <c r="F113" s="100"/>
+    </row>
+    <row r="114" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="102"/>
+      <c r="B114" s="103"/>
+      <c r="C114" s="108"/>
+      <c r="D114" s="104"/>
+      <c r="E114" s="104"/>
+      <c r="F114" s="100"/>
+    </row>
+    <row r="115" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A115" s="102"/>
+      <c r="B115" s="103"/>
+      <c r="C115" s="108"/>
+      <c r="D115" s="104"/>
+      <c r="E115" s="104"/>
+      <c r="F115" s="100"/>
+    </row>
+    <row r="116" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A116" s="102"/>
+      <c r="B116" s="103"/>
+      <c r="C116" s="108"/>
+      <c r="D116" s="104"/>
+      <c r="E116" s="104"/>
+      <c r="F116" s="100"/>
+    </row>
+    <row r="117" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A117" s="102"/>
+      <c r="B117" s="103"/>
+      <c r="C117" s="108"/>
+      <c r="D117" s="104"/>
+      <c r="E117" s="104"/>
+      <c r="F117" s="100"/>
+    </row>
+    <row r="118" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A118" s="102"/>
+      <c r="B118" s="103"/>
+      <c r="C118" s="108"/>
+      <c r="D118" s="104"/>
+      <c r="E118" s="104"/>
+      <c r="F118" s="100"/>
+    </row>
+    <row r="119" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A119" s="102"/>
+      <c r="B119" s="103"/>
+      <c r="C119" s="108"/>
+      <c r="D119" s="104"/>
+      <c r="E119" s="104"/>
+      <c r="F119" s="100"/>
+    </row>
+    <row r="120" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A120" s="102"/>
+      <c r="B120" s="103"/>
+      <c r="C120" s="108"/>
+      <c r="D120" s="104"/>
+      <c r="E120" s="104"/>
+      <c r="F120" s="100"/>
+    </row>
+    <row r="121" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A121" s="102"/>
+      <c r="B121" s="103"/>
+      <c r="C121" s="108"/>
+      <c r="D121" s="104"/>
+      <c r="E121" s="104"/>
+      <c r="F121" s="100"/>
+    </row>
+    <row r="122" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A122" s="102"/>
+      <c r="B122" s="103"/>
+      <c r="C122" s="108"/>
+      <c r="D122" s="104"/>
+      <c r="E122" s="104"/>
+      <c r="F122" s="100"/>
+    </row>
+    <row r="123" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A123" s="102"/>
+      <c r="B123" s="103"/>
+      <c r="C123" s="108"/>
+      <c r="D123" s="104"/>
+      <c r="E123" s="104"/>
+      <c r="F123" s="100"/>
+    </row>
+    <row r="124" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A124" s="102"/>
+      <c r="B124" s="103"/>
+      <c r="C124" s="108"/>
+      <c r="D124" s="104"/>
+      <c r="E124" s="104"/>
+      <c r="F124" s="100"/>
+    </row>
+    <row r="125" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A125" s="96"/>
+      <c r="B125" s="97"/>
+      <c r="C125" s="98"/>
+      <c r="D125" s="99"/>
+      <c r="E125" s="99"/>
+      <c r="F125" s="100"/>
+    </row>
+    <row r="126" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A126" s="96"/>
+      <c r="B126" s="97"/>
+      <c r="C126" s="98"/>
+      <c r="D126" s="99"/>
+      <c r="E126" s="99"/>
+      <c r="F126" s="100"/>
+    </row>
+    <row r="127" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A127" s="96"/>
+      <c r="B127" s="97"/>
+      <c r="C127" s="98"/>
+      <c r="D127" s="99"/>
+      <c r="E127" s="99"/>
+      <c r="F127" s="100"/>
+    </row>
+    <row r="128" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A128" s="96"/>
+      <c r="B128" s="97"/>
+      <c r="C128" s="98"/>
+      <c r="D128" s="99"/>
+      <c r="E128" s="99"/>
+      <c r="F128" s="100"/>
+    </row>
+    <row r="129" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A129" s="96"/>
+      <c r="B129" s="97"/>
+      <c r="C129" s="98"/>
+      <c r="D129" s="99"/>
+      <c r="E129" s="99"/>
+      <c r="F129" s="100"/>
+    </row>
+    <row r="130" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="96"/>
+      <c r="B130" s="97"/>
+      <c r="C130" s="98"/>
+      <c r="D130" s="99"/>
+      <c r="E130" s="99"/>
+      <c r="F130" s="100"/>
+    </row>
+    <row r="131" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A131" s="96"/>
+      <c r="B131" s="97"/>
+      <c r="C131" s="98"/>
+      <c r="D131" s="99"/>
+      <c r="E131" s="99"/>
+      <c r="F131" s="100"/>
+    </row>
+    <row r="132" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A132" s="96"/>
+      <c r="B132" s="97"/>
+      <c r="C132" s="98"/>
+      <c r="D132" s="99"/>
+      <c r="E132" s="99"/>
+      <c r="F132" s="100"/>
+    </row>
+    <row r="133" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A133" s="96"/>
+      <c r="B133" s="97"/>
+      <c r="C133" s="98"/>
+      <c r="D133" s="99"/>
+      <c r="E133" s="99"/>
+      <c r="F133" s="100"/>
+    </row>
+    <row r="134" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A134" s="102"/>
+      <c r="B134" s="103"/>
+      <c r="C134" s="98"/>
+      <c r="D134" s="99"/>
+      <c r="E134" s="99"/>
+      <c r="F134" s="100"/>
+    </row>
+    <row r="135" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A135" s="102"/>
+      <c r="B135" s="103"/>
+      <c r="C135" s="98"/>
+      <c r="D135" s="99"/>
+      <c r="E135" s="99"/>
+      <c r="F135" s="100"/>
+    </row>
+    <row r="136" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A136" s="102"/>
+      <c r="B136" s="103"/>
+      <c r="C136" s="98"/>
+      <c r="D136" s="104"/>
+      <c r="E136" s="104"/>
+      <c r="F136" s="100"/>
+    </row>
+    <row r="137" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A137" s="102"/>
+      <c r="B137" s="103"/>
+      <c r="C137" s="98"/>
+      <c r="D137" s="104"/>
+      <c r="E137" s="104"/>
+      <c r="F137" s="100"/>
+    </row>
+    <row r="138" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A138" s="102"/>
+      <c r="B138" s="103"/>
+      <c r="C138" s="98"/>
+      <c r="D138" s="104"/>
+      <c r="E138" s="104"/>
+      <c r="F138" s="100"/>
+    </row>
+    <row r="139" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A139" s="102"/>
+      <c r="B139" s="103"/>
+      <c r="C139" s="98"/>
+      <c r="D139" s="104"/>
+      <c r="E139" s="104"/>
+      <c r="F139" s="100"/>
+    </row>
+    <row r="140" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A140" s="102"/>
+      <c r="B140" s="103"/>
+      <c r="C140" s="98"/>
+      <c r="D140" s="104"/>
+      <c r="E140" s="104"/>
+      <c r="F140" s="100"/>
+    </row>
+    <row r="141" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A141" s="102"/>
+      <c r="B141" s="103"/>
+      <c r="C141" s="98"/>
+      <c r="D141" s="104"/>
+      <c r="E141" s="104"/>
+      <c r="F141" s="100"/>
+    </row>
+    <row r="142" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A142" s="102"/>
+      <c r="B142" s="103"/>
+      <c r="C142" s="105"/>
+      <c r="D142" s="104"/>
+      <c r="E142" s="104"/>
+      <c r="F142" s="100"/>
+    </row>
+    <row r="143" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A143" s="102"/>
+      <c r="B143" s="103"/>
+      <c r="C143" s="98"/>
+      <c r="D143" s="104"/>
+      <c r="E143" s="104"/>
+      <c r="F143" s="100"/>
+    </row>
+    <row r="144" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A144" s="102"/>
+      <c r="B144" s="103"/>
+      <c r="C144" s="105"/>
+      <c r="D144" s="104"/>
+      <c r="E144" s="104"/>
+      <c r="F144" s="100"/>
+    </row>
+    <row r="145" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A145" s="102"/>
+      <c r="B145" s="103"/>
+      <c r="C145" s="105"/>
+      <c r="D145" s="104"/>
+      <c r="E145" s="104"/>
+      <c r="F145" s="100"/>
+    </row>
+    <row r="146" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A146" s="102"/>
+      <c r="B146" s="103"/>
+      <c r="C146" s="98"/>
+      <c r="D146" s="104"/>
+      <c r="E146" s="104"/>
+      <c r="F146" s="100"/>
+    </row>
+    <row r="147" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A147" s="102"/>
+      <c r="B147" s="103"/>
+      <c r="C147" s="98"/>
+      <c r="D147" s="104"/>
+      <c r="E147" s="104"/>
+      <c r="F147" s="100"/>
+    </row>
+    <row r="148" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A148" s="102"/>
+      <c r="B148" s="103"/>
+      <c r="C148" s="107"/>
+      <c r="D148" s="104"/>
+      <c r="E148" s="104"/>
+      <c r="F148" s="100"/>
+    </row>
+    <row r="149" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A149" s="102"/>
+      <c r="B149" s="103"/>
+      <c r="C149" s="98"/>
+      <c r="D149" s="104"/>
+      <c r="E149" s="104"/>
+      <c r="F149" s="100"/>
+    </row>
+    <row r="150" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A150" s="102"/>
+      <c r="B150" s="103"/>
+      <c r="C150" s="107"/>
+      <c r="D150" s="104"/>
+      <c r="E150" s="104"/>
+      <c r="F150" s="100"/>
+    </row>
+    <row r="151" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A151" s="102"/>
+      <c r="B151" s="103"/>
+      <c r="C151" s="105"/>
+      <c r="D151" s="104"/>
+      <c r="E151" s="104"/>
+      <c r="F151" s="100"/>
+    </row>
+    <row r="152" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A152" s="102"/>
+      <c r="B152" s="103"/>
+      <c r="C152" s="105"/>
+      <c r="D152" s="104"/>
+      <c r="E152" s="104"/>
+      <c r="F152" s="100"/>
+    </row>
+    <row r="153" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A153" s="102"/>
+      <c r="B153" s="103"/>
+      <c r="C153" s="105"/>
+      <c r="D153" s="104"/>
+      <c r="E153" s="104"/>
+      <c r="F153" s="100"/>
+    </row>
+    <row r="154" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A154" s="102"/>
+      <c r="B154" s="103"/>
+      <c r="C154" s="105"/>
+      <c r="D154" s="104"/>
+      <c r="E154" s="104"/>
+      <c r="F154" s="100"/>
+    </row>
+    <row r="155" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A155" s="102"/>
+      <c r="B155" s="103"/>
+      <c r="C155" s="105"/>
+      <c r="D155" s="104"/>
+      <c r="E155" s="104"/>
+      <c r="F155" s="100"/>
+    </row>
+    <row r="156" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A156" s="102"/>
+      <c r="B156" s="103"/>
+      <c r="C156" s="98"/>
+      <c r="D156" s="104"/>
+      <c r="E156" s="104"/>
+      <c r="F156" s="100"/>
+    </row>
+    <row r="157" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A157" s="102"/>
+      <c r="B157" s="103"/>
+      <c r="C157" s="98"/>
+      <c r="D157" s="104"/>
+      <c r="E157" s="104"/>
+      <c r="F157" s="100"/>
+    </row>
+    <row r="158" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A158" s="102"/>
+      <c r="B158" s="103"/>
+      <c r="C158" s="108"/>
+      <c r="D158" s="104"/>
+      <c r="E158" s="104"/>
+      <c r="F158" s="100"/>
+    </row>
+    <row r="159" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A159" s="102"/>
+      <c r="B159" s="103"/>
+      <c r="C159" s="107"/>
+      <c r="D159" s="104"/>
+      <c r="E159" s="104"/>
+      <c r="F159" s="100"/>
+    </row>
+    <row r="160" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A160" s="102"/>
+      <c r="B160" s="103"/>
+      <c r="C160" s="108"/>
+      <c r="D160" s="104"/>
+      <c r="E160" s="104"/>
+      <c r="F160" s="100"/>
+    </row>
+    <row r="161" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A161" s="102"/>
+      <c r="B161" s="103"/>
+      <c r="C161" s="108"/>
+      <c r="D161" s="104"/>
+      <c r="E161" s="104"/>
+      <c r="F161" s="100"/>
+    </row>
+    <row r="162" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A162" s="102"/>
+      <c r="B162" s="103"/>
+      <c r="C162" s="108"/>
+      <c r="D162" s="104"/>
+      <c r="E162" s="104"/>
+      <c r="F162" s="100"/>
+    </row>
+    <row r="163" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A163" s="102"/>
+      <c r="B163" s="103"/>
+      <c r="C163" s="108"/>
+      <c r="D163" s="104"/>
+      <c r="E163" s="104"/>
+      <c r="F163" s="100"/>
+    </row>
+    <row r="164" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A164" s="102"/>
+      <c r="B164" s="103"/>
+      <c r="C164" s="108"/>
+      <c r="D164" s="104"/>
+      <c r="E164" s="104"/>
+      <c r="F164" s="100"/>
+    </row>
+    <row r="165" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A165" s="102"/>
+      <c r="B165" s="103"/>
+      <c r="C165" s="108"/>
+      <c r="D165" s="104"/>
+      <c r="E165" s="104"/>
+      <c r="F165" s="100"/>
+    </row>
+    <row r="166" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A166" s="102"/>
+      <c r="B166" s="103"/>
+      <c r="C166" s="108"/>
+      <c r="D166" s="104"/>
+      <c r="E166" s="104"/>
+      <c r="F166" s="100"/>
+    </row>
+    <row r="167" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A167" s="102"/>
+      <c r="B167" s="103"/>
+      <c r="C167" s="108"/>
+      <c r="D167" s="104"/>
+      <c r="E167" s="104"/>
+      <c r="F167" s="100"/>
+    </row>
+    <row r="168" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A168" s="102"/>
+      <c r="B168" s="103"/>
+      <c r="C168" s="108"/>
+      <c r="D168" s="104"/>
+      <c r="E168" s="104"/>
+      <c r="F168" s="100"/>
+    </row>
+    <row r="169" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A169" s="102"/>
+      <c r="B169" s="103"/>
+      <c r="C169" s="108"/>
+      <c r="D169" s="104"/>
+      <c r="E169" s="104"/>
+      <c r="F169" s="100"/>
+    </row>
+    <row r="170" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A170" s="102"/>
+      <c r="B170" s="103"/>
+      <c r="C170" s="108"/>
+      <c r="D170" s="104"/>
+      <c r="E170" s="104"/>
+      <c r="F170" s="100"/>
+    </row>
+    <row r="171" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A171" s="102"/>
+      <c r="B171" s="103"/>
+      <c r="C171" s="108"/>
+      <c r="D171" s="104"/>
+      <c r="E171" s="104"/>
+      <c r="F171" s="100"/>
+    </row>
+    <row r="172" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A172" s="102"/>
+      <c r="B172" s="103"/>
+      <c r="C172" s="108"/>
+      <c r="D172" s="104"/>
+      <c r="E172" s="104"/>
+      <c r="F172" s="100"/>
+    </row>
+    <row r="173" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A173" s="102"/>
+      <c r="B173" s="103"/>
+      <c r="C173" s="108"/>
+      <c r="D173" s="104"/>
+      <c r="E173" s="104"/>
+      <c r="F173" s="100"/>
+    </row>
+    <row r="174" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A174" s="102"/>
+      <c r="B174" s="103"/>
+      <c r="C174" s="108"/>
+      <c r="D174" s="104"/>
+      <c r="E174" s="104"/>
+      <c r="F174" s="100"/>
+    </row>
+    <row r="175" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A175" s="102"/>
+      <c r="B175" s="103"/>
+      <c r="C175" s="108"/>
+      <c r="D175" s="104"/>
+      <c r="E175" s="104"/>
+      <c r="F175" s="100"/>
+    </row>
+    <row r="176" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A176" s="102"/>
+      <c r="B176" s="103"/>
+      <c r="C176" s="108"/>
+      <c r="D176" s="104"/>
+      <c r="E176" s="104"/>
+      <c r="F176" s="100"/>
+    </row>
+    <row r="177" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A177" s="102"/>
+      <c r="B177" s="103"/>
+      <c r="C177" s="108"/>
+      <c r="D177" s="104"/>
+      <c r="E177" s="104"/>
+      <c r="F177" s="100"/>
+    </row>
+    <row r="178" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A178" s="102"/>
+      <c r="B178" s="103"/>
+      <c r="C178" s="108"/>
+      <c r="D178" s="104"/>
+      <c r="E178" s="104"/>
+      <c r="F178" s="100"/>
+    </row>
+    <row r="179" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A179" s="102"/>
+      <c r="B179" s="103"/>
+      <c r="C179" s="108"/>
+      <c r="D179" s="104"/>
+      <c r="E179" s="104"/>
+      <c r="F179" s="100"/>
+    </row>
+    <row r="180" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A180" s="102"/>
+      <c r="B180" s="103"/>
+      <c r="C180" s="108"/>
+      <c r="D180" s="104"/>
+      <c r="E180" s="104"/>
+      <c r="F180" s="100"/>
+    </row>
+    <row r="181" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A181" s="102"/>
+      <c r="B181" s="103"/>
+      <c r="C181" s="108"/>
+      <c r="D181" s="104"/>
+      <c r="E181" s="104"/>
+      <c r="F181" s="100"/>
+    </row>
+    <row r="182" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A182" s="102"/>
+      <c r="B182" s="103"/>
+      <c r="C182" s="108"/>
+      <c r="D182" s="104"/>
+      <c r="E182" s="104"/>
+      <c r="F182" s="100"/>
+    </row>
+    <row r="183" spans="1:6" s="106" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A183" s="102"/>
+      <c r="B183" s="103"/>
+      <c r="C183" s="108"/>
+      <c r="D183" s="104"/>
+      <c r="E183" s="104"/>
+      <c r="F183" s="100"/>
+    </row>
+    <row r="184" spans="1:6" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D184" s="19"/>
+      <c r="E184" s="19"/>
+    </row>
+    <row r="185" spans="1:6" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D185" s="19"/>
+      <c r="E185" s="19"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D186" s="19"/>
+      <c r="E186" s="19"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D187" s="19"/>
+      <c r="E187" s="19"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D188" s="19"/>
+      <c r="E188" s="19"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D189" s="19"/>
+      <c r="E189" s="19"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D190" s="19"/>
+      <c r="E190" s="19"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D191" s="19"/>
+      <c r="E191" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;G</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26912,7 +28057,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -26931,7 +28077,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -26943,39 +28089,39 @@
       <c r="A4" s="1"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -28483,11 +29629,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -28508,7 +29653,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -28527,7 +29673,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13511)</f>
@@ -28539,39 +29685,39 @@
       <c r="A4" s="1"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -30078,16 +31224,15 @@
     <mergeCell ref="F31:H31"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -30103,7 +31248,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -30126,7 +31272,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13511)</f>
@@ -30140,39 +31286,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -31669,16 +32815,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -31694,7 +32839,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -31717,7 +32863,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -31731,39 +32877,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -33211,16 +34357,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9162A02A-28FF-214F-95DA-ECCB6CAA40D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -33236,7 +34381,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -33259,7 +34405,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -33273,39 +34419,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -34772,16 +35918,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987387B1-FADF-2046-97DC-637FBBCBB7F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -34797,7 +35942,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -34820,7 +35966,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13510)</f>
@@ -34834,39 +35980,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -36333,16 +37479,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E51B1864-29BC-A447-9A43-CA34DBC6A45E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -36358,7 +37503,8 @@
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" style="1" customWidth="1"/>
     <col min="9" max="12" width="5.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="13" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -36381,7 +37527,7 @@
         <v>46113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D3" s="6">
         <f>COUNTA(E7:E13512)</f>
@@ -36395,39 +37541,39 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -37913,10 +39059,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="23" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
--- a/Month YEAR - Body Motions.xlsx
+++ b/Month YEAR - Body Motions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyayas/VALD Automator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6271E9-60DA-0745-9369-F76B2458B77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A58FCDD-2E0D-CB49-B375-4ECEE175669B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="213">
   <si>
     <t>REPORT DATE:</t>
   </si>
@@ -701,6 +701,9 @@
   </si>
   <si>
     <t>تاريخ ارسال الجدول</t>
+  </si>
+  <si>
+    <t>ALQ - Al Rayyan</t>
   </si>
 </sst>
 </file>
@@ -1731,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P76"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
@@ -1767,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="89">
-        <f ca="1">SUM(C7:C25)</f>
+        <f ca="1">SUM(C7:C26)</f>
         <v>0</v>
       </c>
     </row>
@@ -1811,7 +1814,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="37">
-        <f t="shared" ref="B7:B25" ca="1" si="0">IFERROR(COUNTIFS(INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&gt;=" &amp; $B$3-7, INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&lt;=" &amp; $B$3),0)</f>
+        <f t="shared" ref="B7:B26" ca="1" si="0">IFERROR(COUNTIFS(INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&gt;=" &amp; $B$3-7, INDIRECT("'" &amp; $A7 &amp; "'!E:E"), "&lt;=" &amp; $B$3),0)</f>
         <v>0</v>
       </c>
       <c r="C7" s="36">
@@ -2094,7 +2097,7 @@
     </row>
     <row r="21" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="58" t="s">
-        <v>24</v>
+        <v>212</v>
       </c>
       <c r="B21" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2105,14 +2108,14 @@
         <v>0</v>
       </c>
       <c r="D21" s="36">
-        <f ca="1">C21+29</f>
-        <v>29</v>
+        <f ca="1">C21+0</f>
+        <v>0</v>
       </c>
       <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="31" t="s">
-        <v>25</v>
+      <c r="A22" s="58" t="s">
+        <v>24</v>
       </c>
       <c r="B22" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2123,14 +2126,14 @@
         <v>0</v>
       </c>
       <c r="D22" s="36">
-        <f ca="1">C22+20</f>
-        <v>20</v>
+        <f ca="1">C22+29</f>
+        <v>29</v>
       </c>
       <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="57" t="s">
-        <v>26</v>
+      <c r="A23" s="31" t="s">
+        <v>25</v>
       </c>
       <c r="B23" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2141,14 +2144,14 @@
         <v>0</v>
       </c>
       <c r="D23" s="36">
-        <f ca="1">C23+48</f>
-        <v>48</v>
+        <f ca="1">C23+20</f>
+        <v>20</v>
       </c>
       <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="31" t="s">
-        <v>27</v>
+      <c r="A24" s="57" t="s">
+        <v>26</v>
       </c>
       <c r="B24" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2159,14 +2162,14 @@
         <v>0</v>
       </c>
       <c r="D24" s="36">
-        <f ca="1">C24+16</f>
-        <v>16</v>
+        <f ca="1">C24+48</f>
+        <v>48</v>
       </c>
       <c r="E24" s="17"/>
     </row>
     <row r="25" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="57" t="s">
-        <v>28</v>
+      <c r="A25" s="31" t="s">
+        <v>27</v>
       </c>
       <c r="B25" s="37">
         <f t="shared" ca="1" si="0"/>
@@ -2177,16 +2180,27 @@
         <v>0</v>
       </c>
       <c r="D25" s="36">
-        <f ca="1">C25+11</f>
+        <f ca="1">C25+16</f>
+        <v>16</v>
+      </c>
+      <c r="E25" s="17"/>
+    </row>
+    <row r="26" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="37">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C26" s="36">
+        <f t="array" aca="1" ref="C26" ca="1">INDIRECT("'" &amp; A26 &amp; "'!D3")</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="36">
+        <f ca="1">C26+11</f>
         <v>11</v>
       </c>
-      <c r="E25" s="17"/>
-    </row>
-    <row r="26" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
       <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2516,6 +2530,7 @@
       <c r="B73" s="17"/>
       <c r="C73" s="35"/>
       <c r="D73" s="35"/>
+      <c r="E73" s="17"/>
     </row>
     <row r="74" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="17"/>
@@ -2534,6 +2549,12 @@
       <c r="B76" s="17"/>
       <c r="C76" s="35"/>
       <c r="D76" s="35"/>
+    </row>
+    <row r="77" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="17"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
